--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -496,18 +496,17 @@
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Спецификация витражей (по планам на отм. -6.000 и 0.000, марки выделены красным)</t>
+          <t>Спецификация витражей (по планам на отм. -6.000 и 0.000, марки выделены красным) — только позиции, входящие в КП</t>
         </is>
       </c>
     </row>
@@ -564,30 +563,25 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Литер Ж</t>
+          <t>Всего, шт</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Всего, шт</t>
+          <t>Площадь всего, м²</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Площадь всего, м²</t>
+          <t>Отметка</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Отметка</t>
+          <t>Дверь в составе (по чертежу)</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Дверь в составе (по чертежу)</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -599,42 +593,57 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Вн-1</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4750</v>
+        <v>4200</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3870</v>
+        <v>4820</v>
       </c>
       <c r="E4" s="4">
         <f>ROUND(C4*D4/1000000,2)</f>
         <v/>
       </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n">
+      <c r="F4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="3">
-        <f>SUM(F4:K4)</f>
-        <v/>
-      </c>
-      <c r="M4" s="5">
-        <f>ROUND(L4*E4,2)</f>
-        <v/>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
+      <c r="I4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="3">
+        <f>SUM(F4:J4)</f>
+        <v/>
+      </c>
+      <c r="L4" s="5">
+        <f>ROUND(K4*E4,2)</f>
+        <v/>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>Лит. Г: на чертеже 3 шт., в КП 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -642,14 +651,14 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Вн-2</t>
+          <t>Вн-7</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4750</v>
+        <v>3020</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3870</v>
+        <v>4820</v>
       </c>
       <c r="E5" s="4">
         <f>ROUND(C5*D5/1000000,2)</f>
@@ -659,25 +668,24 @@
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="3">
-        <f>SUM(F5:K5)</f>
-        <v/>
-      </c>
-      <c r="M5" s="5">
-        <f>ROUND(L5*E5,2)</f>
-        <v/>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
+      <c r="K5" s="3">
+        <f>SUM(F5:J5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="5">
+        <f>ROUND(K5*E5,2)</f>
+        <v/>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr"/>
       <c r="O5" s="6" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -685,42 +693,41 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Вн-3</t>
+          <t>Вн-8</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6100</v>
+        <v>2600</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3870</v>
+        <v>4820</v>
       </c>
       <c r="E6" s="4">
         <f>ROUND(C6*D6/1000000,2)</f>
         <v/>
       </c>
-      <c r="F6" s="3" t="n"/>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3">
-        <f>SUM(F6:K6)</f>
-        <v/>
-      </c>
-      <c r="M6" s="5">
-        <f>ROUND(L6*E6,2)</f>
-        <v/>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
+      <c r="K6" s="3">
+        <f>SUM(F6:J6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="5">
+        <f>ROUND(K6*E6,2)</f>
+        <v/>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr"/>
       <c r="O6" s="6" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -728,14 +735,14 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Вн-4</t>
+          <t>Вн-9</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5400</v>
+        <v>3870</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3470</v>
+        <v>4820</v>
       </c>
       <c r="E7" s="4">
         <f>ROUND(C7*D7/1000000,2)</f>
@@ -745,25 +752,28 @@
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="3">
-        <f>SUM(F7:K7)</f>
-        <v/>
-      </c>
-      <c r="M7" s="5">
-        <f>ROUND(L7*E7,2)</f>
-        <v/>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
+      <c r="K7" s="3">
+        <f>SUM(F7:J7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>ROUND(K7*E7,2)</f>
+        <v/>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>Д17*</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr"/>
-      <c r="P7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -771,14 +781,14 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Вн-5</t>
+          <t>Вн-10</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7800</v>
+        <v>4160</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3470</v>
+        <v>4820</v>
       </c>
       <c r="E8" s="4">
         <f>ROUND(C8*D8/1000000,2)</f>
@@ -787,30 +797,29 @@
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3">
-        <f>SUM(F8:K8)</f>
-        <v/>
-      </c>
-      <c r="M8" s="5">
-        <f>ROUND(L8*E8,2)</f>
-        <v/>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
+      <c r="K8" s="3">
+        <f>SUM(F8:J8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>ROUND(K8*E8,2)</f>
+        <v/>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>Д17*</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr"/>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>По договору площадь 26,52 м² (габарит 7800×3470 = 27,07 м²)</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -818,11 +827,11 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-11</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4200</v>
+        <v>2450</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>4820</v>
@@ -831,41 +840,28 @@
         <f>ROUND(C9*D9/1000000,2)</f>
         <v/>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="n">
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3">
-        <f>SUM(F9:K9)</f>
-        <v/>
-      </c>
-      <c r="M9" s="5">
-        <f>ROUND(L9*E9,2)</f>
-        <v/>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3">
+        <f>SUM(F9:J9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="5">
+        <f>ROUND(K9*E9,2)</f>
+        <v/>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -873,11 +869,11 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Вн-7</t>
+          <t>Вн-12</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3020</v>
+        <v>3370</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>4820</v>
@@ -889,26 +885,29 @@
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3">
-        <f>SUM(F10:K10)</f>
-        <v/>
-      </c>
-      <c r="M10" s="5">
-        <f>ROUND(L10*E10,2)</f>
-        <v/>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3">
+        <f>SUM(F10:J10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="5">
+        <f>ROUND(K10*E10,2)</f>
+        <v/>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
       <c r="O10" s="6" t="inlineStr"/>
-      <c r="P10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -916,11 +915,11 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Вн-8</t>
+          <t>Вн-13</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2600</v>
+        <v>3200</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>4820</v>
@@ -929,29 +928,28 @@
         <f>ROUND(C11*D11/1000000,2)</f>
         <v/>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3">
-        <f>SUM(F11:K11)</f>
-        <v/>
-      </c>
-      <c r="M11" s="5">
-        <f>ROUND(L11*E11,2)</f>
-        <v/>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="K11" s="3">
+        <f>SUM(F11:J11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="5">
+        <f>ROUND(K11*E11,2)</f>
+        <v/>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
+      <c r="N11" s="6" t="inlineStr"/>
       <c r="O11" s="6" t="inlineStr"/>
-      <c r="P11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -959,11 +957,11 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Вн-9</t>
+          <t>Вн-14</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3870</v>
+        <v>2485</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>4820</v>
@@ -972,33 +970,32 @@
         <f>ROUND(C12*D12/1000000,2)</f>
         <v/>
       </c>
-      <c r="F12" s="3" t="n"/>
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3">
-        <f>SUM(F12:K12)</f>
-        <v/>
-      </c>
-      <c r="M12" s="5">
-        <f>ROUND(L12*E12,2)</f>
-        <v/>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3">
+        <f>SUM(F12:J12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="5">
+        <f>ROUND(K12*E12,2)</f>
+        <v/>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
-      <c r="O12" s="6" t="inlineStr">
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>Д17*</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1006,11 +1003,11 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Вн-10</t>
+          <t>Вн-15</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>4160</v>
+        <v>1400</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>4820</v>
@@ -1019,33 +1016,34 @@
         <f>ROUND(C13*D13/1000000,2)</f>
         <v/>
       </c>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3">
-        <f>SUM(F13:K13)</f>
-        <v/>
-      </c>
-      <c r="M13" s="5">
-        <f>ROUND(L13*E13,2)</f>
-        <v/>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="K13" s="3">
+        <f>SUM(F13:J13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="5">
+        <f>ROUND(K13*E13,2)</f>
+        <v/>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>Д17*</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1053,11 +1051,11 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Вн-11</t>
+          <t>Вн-16</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2450</v>
+        <v>1200</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>4820</v>
@@ -1068,27 +1066,34 @@
       </c>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="H14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3">
-        <f>SUM(F14:K14)</f>
-        <v/>
-      </c>
-      <c r="M14" s="5">
-        <f>ROUND(L14*E14,2)</f>
-        <v/>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="K14" s="3">
+        <f>SUM(F14:J14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="5">
+        <f>ROUND(K14*E14,2)</f>
+        <v/>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
-      <c r="O14" s="6" t="inlineStr"/>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>Д35</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>1 шт. у лестницы на границе литеров В/Г отнесён к литеру В</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1096,11 +1101,11 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Вн-12</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>3370</v>
+        <v>4200</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>4820</v>
@@ -1110,32 +1115,41 @@
         <v/>
       </c>
       <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="G15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3">
-        <f>SUM(F15:K15)</f>
-        <v/>
-      </c>
-      <c r="M15" s="5">
-        <f>ROUND(L15*E15,2)</f>
-        <v/>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3">
+        <f>SUM(F15:J15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="5">
+        <f>ROUND(K15*E15,2)</f>
+        <v/>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr"/>
+          <t>Лит. Г: на чертеже 2 шт., в КП 1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1143,11 +1157,11 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Вн-13</t>
+          <t>Вн-18</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3200</v>
+        <v>2600</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>4820</v>
@@ -1157,28 +1171,31 @@
         <v/>
       </c>
       <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n">
+      <c r="G16" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3">
-        <f>SUM(F16:K16)</f>
-        <v/>
-      </c>
-      <c r="M16" s="5">
-        <f>ROUND(L16*E16,2)</f>
-        <v/>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="K16" s="3">
+        <f>SUM(F16:J16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="5">
+        <f>ROUND(K16*E16,2)</f>
+        <v/>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
       <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1186,11 +1203,11 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Вн-14</t>
+          <t>Вн-19</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2485</v>
+        <v>3000</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>4820</v>
@@ -1199,33 +1216,32 @@
         <f>ROUND(C17*D17/1000000,2)</f>
         <v/>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
+      <c r="H17" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3">
-        <f>SUM(F17:K17)</f>
-        <v/>
-      </c>
-      <c r="M17" s="5">
-        <f>ROUND(L17*E17,2)</f>
-        <v/>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="K17" s="3">
+        <f>SUM(F17:J17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="5">
+        <f>ROUND(K17*E17,2)</f>
+        <v/>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
-      <c r="O17" s="6" t="inlineStr">
+      <c r="N17" s="6" t="inlineStr">
         <is>
           <t>Д17*</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1233,11 +1249,11 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Вн-15</t>
+          <t>Вн-20</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1400</v>
+        <v>3900</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>4820</v>
@@ -1246,35 +1262,28 @@
         <f>ROUND(C18*D18/1000000,2)</f>
         <v/>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3">
-        <f>SUM(F18:K18)</f>
-        <v/>
-      </c>
-      <c r="M18" s="5">
-        <f>ROUND(L18*E18,2)</f>
-        <v/>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="K18" s="3">
+        <f>SUM(F18:J18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="5">
+        <f>ROUND(K18*E18,2)</f>
+        <v/>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1282,11 +1291,11 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Вн-16</t>
+          <t>Вн-21</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1200</v>
+        <v>2920</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>4820</v>
@@ -1297,35 +1306,26 @@
       </c>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3">
-        <f>SUM(F19:K19)</f>
-        <v/>
-      </c>
-      <c r="M19" s="5">
-        <f>ROUND(L19*E19,2)</f>
-        <v/>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="K19" s="3">
+        <f>SUM(F19:J19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="5">
+        <f>ROUND(K19*E19,2)</f>
+        <v/>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>-6.000</t>
         </is>
       </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>Д35</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>1 шт. у лестницы на границе литеров В/Г отнесён к литеру В</t>
-        </is>
-      </c>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1333,430 +1333,100 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-22</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4200</v>
+        <v>2150</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4820</v>
+        <v>2720</v>
       </c>
       <c r="E20" s="4">
         <f>ROUND(C20*D20/1000000,2)</f>
         <v/>
       </c>
-      <c r="F20" s="3" t="n"/>
+      <c r="F20" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="G20" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3">
-        <f>SUM(F20:K20)</f>
-        <v/>
-      </c>
-      <c r="M20" s="5">
-        <f>ROUND(L20*E20,2)</f>
-        <v/>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3">
+        <f>SUM(F20:J20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="5">
+        <f>ROUND(K20*E20,2)</f>
+        <v/>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>Д17*, Д35</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr"/>
+          <t>КП: 2070×2760. На чертеже 18 шт., в КП 11 (А5, Б5, В1)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Вн-18</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E21" s="4">
-        <f>ROUND(C21*D21/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3">
-        <f>SUM(F21:K21)</f>
-        <v/>
-      </c>
-      <c r="M21" s="5">
-        <f>ROUND(L21*E21,2)</f>
-        <v/>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Вн-19</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E22" s="4">
-        <f>ROUND(C22*D22/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3">
-        <f>SUM(F22:K22)</f>
-        <v/>
-      </c>
-      <c r="M22" s="5">
-        <f>ROUND(L22*E22,2)</f>
-        <v/>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr"/>
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="8">
+        <f>SUM(F4:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="8">
+        <f>SUM(G4:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="8">
+        <f>SUM(H4:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="8">
+        <f>SUM(I4:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="8">
+        <f>SUM(J4:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="8">
+        <f>SUM(K4:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="10">
+        <f>SUM(L4:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Вн-20</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>3900</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E23" s="4">
-        <f>ROUND(C23*D23/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3">
-        <f>SUM(F23:K23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="5">
-        <f>ROUND(L23*E23,2)</f>
-        <v/>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Вн-21</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>2920</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E24" s="4">
-        <f>ROUND(C24*D24/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3">
-        <f>SUM(F24:K24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="5">
-        <f>ROUND(L24*E24,2)</f>
-        <v/>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>2150</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>2720</v>
-      </c>
-      <c r="E25" s="4">
-        <f>ROUND(C25*D25/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3">
-        <f>SUM(F25:K25)</f>
-        <v/>
-      </c>
-      <c r="M25" s="5">
-        <f>ROUND(L25*E25,2)</f>
-        <v/>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>Д17*, Д22, Д35</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>КП: 2070×2760</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Вн-23</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>3540</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E26" s="4">
-        <f>ROUND(C26*D26/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3">
-        <f>SUM(F26:K26)</f>
-        <v/>
-      </c>
-      <c r="M26" s="5">
-        <f>ROUND(L26*E26,2)</f>
-        <v/>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Вн-24</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>2610</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E27" s="4">
-        <f>ROUND(C27*D27/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3">
-        <f>SUM(F27:K27)</f>
-        <v/>
-      </c>
-      <c r="M27" s="5">
-        <f>ROUND(L27*E27,2)</f>
-        <v/>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="8">
-        <f>SUM(F4:F27)</f>
-        <v/>
-      </c>
-      <c r="G28" s="8">
-        <f>SUM(G4:G27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="8">
-        <f>SUM(H4:H27)</f>
-        <v/>
-      </c>
-      <c r="I28" s="8">
-        <f>SUM(I4:I27)</f>
-        <v/>
-      </c>
-      <c r="J28" s="8">
-        <f>SUM(J4:J27)</f>
-        <v/>
-      </c>
-      <c r="K28" s="8">
-        <f>SUM(K4:K27)</f>
-        <v/>
-      </c>
-      <c r="L28" s="8">
-        <f>SUM(L4:L27)</f>
-        <v/>
-      </c>
-      <c r="M28" s="10">
-        <f>SUM(M4:M27)</f>
-        <v/>
-      </c>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Размеры — из таблицы заказчика (длина × высота). Количество — подсчёт марок на чертежах; литер определён по привязке витража к блокам литеров в модели.</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Размеры — из таблицы заказчика (длина × высота). Количество — по чертежам, но не больше, чем в КП; позиции, которых нет в КП, исключены.</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2009,102 +1679,102 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Итого литер А</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="8">
+        <f>SUM(F5:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="10">
+        <f>SUM(G5:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Литер Б</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="13" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Вн-23</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>3540</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E10" s="4">
-        <f>ROUND(C10*D10/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F10" s="3" t="n">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E12" s="4">
+        <f>ROUND(C12*D12/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5">
+        <f>ROUND(F12*E12,2)</f>
+        <v/>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E13" s="4">
+        <f>ROUND(C13*D13/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="5">
-        <f>ROUND(F10*E10,2)</f>
-        <v/>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Вн-24</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>2610</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>3020</v>
-      </c>
-      <c r="E11" s="4">
-        <f>ROUND(C11*D11/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5">
-        <f>ROUND(F11*E11,2)</f>
-        <v/>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Итого литер А</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="8">
-        <f>SUM(F5:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="10">
-        <f>SUM(G5:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Литер Б</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="13" t="n"/>
+      <c r="G13" s="5">
+        <f>ROUND(F13*E13,2)</f>
+        <v/>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -2112,7 +1782,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -2126,7 +1796,7 @@
         <v/>
       </c>
       <c r="F14" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5">
         <f>ROUND(F14*E14,2)</f>
@@ -2144,11 +1814,11 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Вн-15</t>
+          <t>Вн-18</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>4820</v>
@@ -2176,21 +1846,21 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-22</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4200</v>
+        <v>2150</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4820</v>
+        <v>2720</v>
       </c>
       <c r="E16" s="4">
         <f>ROUND(C16*D16/1000000,2)</f>
         <v/>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" s="5">
         <f>ROUND(F16*E16,2)</f>
@@ -2198,88 +1868,58 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>-6.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Вн-18</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E17" s="4">
-        <f>ROUND(C17*D17/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5">
-        <f>ROUND(F17*E17,2)</f>
-        <v/>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Итого литер Б</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="8">
+        <f>SUM(F12:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="10">
+        <f>SUM(G12:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>2150</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>2720</v>
-      </c>
-      <c r="E18" s="4">
-        <f>ROUND(C18*D18/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="5">
-        <f>ROUND(F18*E18,2)</f>
-        <v/>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Литер В</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Вн-23</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3540</v>
+        <v>4200</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3020</v>
+        <v>4820</v>
       </c>
       <c r="E19" s="4">
         <f>ROUND(C19*D19/1000000,2)</f>
@@ -2294,24 +1934,24 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-6.000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Вн-24</t>
+          <t>Вн-13</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2610</v>
+        <v>3200</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3020</v>
+        <v>4820</v>
       </c>
       <c r="E20" s="4">
         <f>ROUND(C20*D20/1000000,2)</f>
@@ -2326,43 +1966,73 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-6.000</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Итого литер Б</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="8">
-        <f>SUM(F14:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="10">
-        <f>SUM(G14:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="7" t="n"/>
+      <c r="A21" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E21" s="4">
+        <f>ROUND(C21*D21/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="5">
+        <f>ROUND(F21*E21,2)</f>
+        <v/>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Литер В</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="13" t="n"/>
+      <c r="A22" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E22" s="4">
+        <f>ROUND(C22*D22/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <f>ROUND(F22*E22,2)</f>
+        <v/>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -2370,11 +2040,11 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-19</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4200</v>
+        <v>3000</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>4820</v>
@@ -2384,7 +2054,7 @@
         <v/>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5">
         <f>ROUND(F23*E23,2)</f>
@@ -2402,14 +2072,14 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Вн-13</t>
+          <t>Вн-22</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>3200</v>
+        <v>2150</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4820</v>
+        <v>2720</v>
       </c>
       <c r="E24" s="4">
         <f>ROUND(C24*D24/1000000,2)</f>
@@ -2424,85 +2094,55 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>-6.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Вн-16</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E25" s="4">
-        <f>ROUND(C25*D25/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" s="5">
-        <f>ROUND(F25*E25,2)</f>
-        <v/>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Итого литер В</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="8">
+        <f>SUM(F19:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="10">
+        <f>SUM(G19:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Вн-17</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E26" s="4">
-        <f>ROUND(C26*D26/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="5">
-        <f>ROUND(F26*E26,2)</f>
-        <v/>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="n"/>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Литер Г</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Вн-19</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>4820</v>
@@ -2512,7 +2152,7 @@
         <v/>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5">
         <f>ROUND(F27*E27,2)</f>
@@ -2526,25 +2166,25 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Вн-22</t>
+          <t>Вн-10</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2150</v>
+        <v>4160</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2720</v>
+        <v>4820</v>
       </c>
       <c r="E28" s="4">
         <f>ROUND(C28*D28/1000000,2)</f>
         <v/>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G28" s="5">
         <f>ROUND(F28*E28,2)</f>
@@ -2552,43 +2192,73 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-6.000</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Итого литер В</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="8">
-        <f>SUM(F23:F28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="10">
-        <f>SUM(G23:G28)</f>
-        <v/>
-      </c>
-      <c r="H29" s="7" t="n"/>
+      <c r="A29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Вн-11</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2450</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E29" s="4">
+        <f>ROUND(C29*D29/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5">
+        <f>ROUND(F29*E29,2)</f>
+        <v/>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Литер Г</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="13" t="n"/>
+      <c r="A30" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Вн-12</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>3370</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E30" s="4">
+        <f>ROUND(C30*D30/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5">
+        <f>ROUND(F30*E30,2)</f>
+        <v/>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2596,7 +2266,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2610,7 +2280,7 @@
         <v/>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5">
         <f>ROUND(F31*E31,2)</f>
@@ -2628,11 +2298,11 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Вн-10</t>
+          <t>Вн-20</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>4160</v>
+        <v>3900</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>4820</v>
@@ -2660,11 +2330,11 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Вн-11</t>
+          <t>Вн-21</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2450</v>
+        <v>2920</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>4820</v>
@@ -2687,80 +2357,50 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Вн-12</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>3370</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E34" s="4">
-        <f>ROUND(C34*D34/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5">
-        <f>ROUND(F34*E34,2)</f>
-        <v/>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Итого литер Г</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="8">
+        <f>SUM(F27:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="10">
+        <f>SUM(G27:G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Вн-17</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E35" s="4">
-        <f>ROUND(C35*D35/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="5">
-        <f>ROUND(F35*E35,2)</f>
-        <v/>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Литер Д</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Вн-20</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>4820</v>
@@ -2770,7 +2410,7 @@
         <v/>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="5">
         <f>ROUND(F36*E36,2)</f>
@@ -2784,15 +2424,15 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Вн-21</t>
+          <t>Вн-7</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2920</v>
+        <v>3020</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4820</v>
@@ -2816,25 +2456,25 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Вн-22</t>
+          <t>Вн-9</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2150</v>
+        <v>3870</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>2720</v>
+        <v>4820</v>
       </c>
       <c r="E38" s="4">
         <f>ROUND(C38*D38/1000000,2)</f>
         <v/>
       </c>
       <c r="F38" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" s="5">
         <f>ROUND(F38*E38,2)</f>
@@ -2842,414 +2482,89 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-6.000</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Итого литер Г</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="8">
-        <f>SUM(F31:F38)</f>
-        <v/>
-      </c>
-      <c r="G39" s="10">
-        <f>SUM(G31:G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="7" t="n"/>
+      <c r="A39" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E39" s="4">
+        <f>ROUND(C39*D39/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5">
+        <f>ROUND(F39*E39,2)</f>
+        <v/>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n"/>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Литер Д</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="15" t="n"/>
-      <c r="H40" s="13" t="n"/>
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Итого литер Д</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="8">
+        <f>SUM(F36:F39)</f>
+        <v/>
+      </c>
+      <c r="G40" s="10">
+        <f>SUM(G36:G39)</f>
+        <v/>
+      </c>
+      <c r="H40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E41" s="4">
-        <f>ROUND(C41*D41/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="5">
-        <f>ROUND(F41*E41,2)</f>
-        <v/>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Вн-7</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>3020</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E42" s="4">
-        <f>ROUND(C42*D42/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5">
-        <f>ROUND(F42*E42,2)</f>
-        <v/>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Вн-9</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>3870</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E43" s="4">
-        <f>ROUND(C43*D43/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5">
-        <f>ROUND(F43*E43,2)</f>
-        <v/>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Вн-17</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E44" s="4">
-        <f>ROUND(C44*D44/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5">
-        <f>ROUND(F44*E44,2)</f>
-        <v/>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n"/>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Итого литер Д</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="8">
-        <f>SUM(F41:F44)</f>
-        <v/>
-      </c>
-      <c r="G45" s="10">
-        <f>SUM(G41:G44)</f>
-        <v/>
-      </c>
-      <c r="H45" s="7" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>Литер Ж (паркинг)</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="15" t="n"/>
-      <c r="H46" s="13" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Вн-1</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>4750</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>3870</v>
-      </c>
-      <c r="E47" s="4">
-        <f>ROUND(C47*D47/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5">
-        <f>ROUND(F47*E47,2)</f>
-        <v/>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Вн-2</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>4750</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>3870</v>
-      </c>
-      <c r="E48" s="4">
-        <f>ROUND(C48*D48/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5">
-        <f>ROUND(F48*E48,2)</f>
-        <v/>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Вн-3</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>6100</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>3870</v>
-      </c>
-      <c r="E49" s="4">
-        <f>ROUND(C49*D49/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5">
-        <f>ROUND(F49*E49,2)</f>
-        <v/>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Вн-4</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>5400</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>3470</v>
-      </c>
-      <c r="E50" s="4">
-        <f>ROUND(C50*D50/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5">
-        <f>ROUND(F50*E50,2)</f>
-        <v/>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Вн-5</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>3470</v>
-      </c>
-      <c r="E51" s="4">
-        <f>ROUND(C51*D51/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5">
-        <f>ROUND(F51*E51,2)</f>
-        <v/>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n"/>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Итого литер Ж</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="8">
-        <f>SUM(F47:F51)</f>
-        <v/>
-      </c>
-      <c r="G52" s="10">
-        <f>SUM(G47:G51)</f>
-        <v/>
-      </c>
-      <c r="H52" s="7" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n"/>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>ВСЕГО</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="16">
-        <f>F12+F21+F29+F39+F45+F52</f>
-        <v/>
-      </c>
-      <c r="G53" s="17">
-        <f>G12+G21+G29+G39+G45+G52</f>
-        <v/>
-      </c>
-      <c r="H53" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="16">
+        <f>F10+F17+F25+F34+F40</f>
+        <v/>
+      </c>
+      <c r="G41" s="17">
+        <f>G10+G17+G25+G34+G40</f>
+        <v/>
+      </c>
+      <c r="H41" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B13:H13"/>
+  <mergeCells count="5">
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B11:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3261,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3271,12 +2586,13 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Каждая марка на чертежах (координаты — точка выноски в координатах модели, мм)</t>
+          <t>Витражи на чертежах, входящие в КП (координаты — точка выноски, мм). «1 из 3» — на чертеже больше, чем в КП; какие именно — по КП не определить</t>
         </is>
       </c>
     </row>
@@ -3314,6 +2630,11 @@
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Y, мм</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>В КП</t>
         </is>
       </c>
     </row>
@@ -3347,6 +2668,11 @@
       <c r="G4" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -3378,6 +2704,11 @@
       <c r="G5" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -3409,6 +2740,11 @@
       <c r="G6" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -3436,6 +2772,11 @@
       <c r="G7" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -3467,6 +2808,11 @@
       <c r="G8" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -3498,6 +2844,11 @@
       <c r="G9" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -3529,6 +2880,11 @@
       <c r="G10" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -3560,6 +2916,11 @@
       <c r="G11" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -3591,6 +2952,11 @@
       <c r="G12" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -3622,6 +2988,11 @@
       <c r="G13" s="19" t="n">
         <v>-240189</v>
       </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -3649,6 +3020,11 @@
       <c r="G14" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -3680,6 +3056,11 @@
       <c r="G15" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -3711,6 +3092,11 @@
       <c r="G16" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -3738,6 +3124,11 @@
       <c r="G17" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -3769,6 +3160,11 @@
       <c r="G18" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -3800,6 +3196,11 @@
       <c r="G19" s="19" t="n">
         <v>-240238</v>
       </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -3831,6 +3232,11 @@
       <c r="G20" s="19" t="n">
         <v>-240238</v>
       </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -3862,6 +3268,11 @@
       <c r="G21" s="19" t="n">
         <v>-240123</v>
       </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -3889,6 +3300,11 @@
       <c r="G22" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -3920,6 +3336,11 @@
       <c r="G23" s="19" t="n">
         <v>-240209</v>
       </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -3951,6 +3372,11 @@
       <c r="G24" s="19" t="n">
         <v>-227349</v>
       </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>1 из 3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -3982,6 +3408,11 @@
       <c r="G25" s="19" t="n">
         <v>-240130</v>
       </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>1 из 3</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -4013,6 +3444,11 @@
       <c r="G26" s="19" t="n">
         <v>-240130</v>
       </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>1 из 3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -4044,6 +3480,11 @@
       <c r="G27" s="19" t="n">
         <v>-203499</v>
       </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -4071,6 +3512,11 @@
       <c r="G28" s="19" t="n">
         <v>-213004</v>
       </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -4102,6 +3548,11 @@
       <c r="G29" s="19" t="n">
         <v>-217364</v>
       </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -4129,6 +3580,11 @@
       <c r="G30" s="19" t="n">
         <v>-237749</v>
       </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>1 из 2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -4156,6 +3612,11 @@
       <c r="G31" s="19" t="n">
         <v>-240108</v>
       </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>1 из 2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -4183,6 +3644,11 @@
       <c r="G32" s="19" t="n">
         <v>-221999</v>
       </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -4210,6 +3676,11 @@
       <c r="G33" s="19" t="n">
         <v>-231909</v>
       </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -4237,6 +3708,11 @@
       <c r="G34" s="19" t="n">
         <v>-179543</v>
       </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -4264,6 +3740,11 @@
       <c r="G35" s="19" t="n">
         <v>-169143</v>
       </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -4291,6 +3772,11 @@
       <c r="G36" s="19" t="n">
         <v>-174933</v>
       </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -4322,6 +3808,11 @@
       <c r="G37" s="19" t="n">
         <v>-195128</v>
       </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -4349,6 +3840,11 @@
       <c r="G38" s="19" t="n">
         <v>-189943</v>
       </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -4380,6 +3876,11 @@
       <c r="G39" s="19" t="n">
         <v>2824</v>
       </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -4411,6 +3912,11 @@
       <c r="G40" s="19" t="n">
         <v>2691</v>
       </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -4442,6 +3948,11 @@
       <c r="G41" s="19" t="n">
         <v>2943</v>
       </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -4473,6 +3984,11 @@
       <c r="G42" s="19" t="n">
         <v>2886</v>
       </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -4504,6 +4020,11 @@
       <c r="G43" s="19" t="n">
         <v>2773</v>
       </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -4516,20 +4037,29 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Вн-23</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
       <c r="F44" s="19" t="n">
-        <v>96564</v>
+        <v>79305</v>
       </c>
       <c r="G44" s="19" t="n">
-        <v>23905</v>
+        <v>3099</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -4543,20 +4073,29 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Вн-24</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
       <c r="F45" s="19" t="n">
-        <v>98072</v>
+        <v>72445</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>24342</v>
+        <v>3048</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -4584,10 +4123,15 @@
         </is>
       </c>
       <c r="F46" s="19" t="n">
-        <v>79305</v>
+        <v>64804</v>
       </c>
       <c r="G46" s="19" t="n">
-        <v>3099</v>
+        <v>2917</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -4615,10 +4159,15 @@
         </is>
       </c>
       <c r="F47" s="19" t="n">
-        <v>72445</v>
+        <v>59604</v>
       </c>
       <c r="G47" s="19" t="n">
-        <v>3048</v>
+        <v>2985</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -4646,10 +4195,15 @@
         </is>
       </c>
       <c r="F48" s="19" t="n">
-        <v>64804</v>
+        <v>53064</v>
       </c>
       <c r="G48" s="19" t="n">
-        <v>2917</v>
+        <v>2948</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -4663,7 +4217,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -4673,14 +4227,19 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д35</t>
         </is>
       </c>
       <c r="F49" s="19" t="n">
-        <v>59604</v>
+        <v>45611</v>
       </c>
       <c r="G49" s="19" t="n">
-        <v>2985</v>
+        <v>3036</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>1 из 4</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -4694,7 +4253,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -4708,10 +4267,15 @@
         </is>
       </c>
       <c r="F50" s="19" t="n">
-        <v>53064</v>
+        <v>39399</v>
       </c>
       <c r="G50" s="19" t="n">
-        <v>2948</v>
+        <v>2969</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>1 из 4</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -4725,20 +4289,29 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Вн-23</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
       <c r="F51" s="19" t="n">
-        <v>62982</v>
+        <v>33459</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>23879</v>
+        <v>3046</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>1 из 4</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -4752,403 +4325,29 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Вн-24</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
       <c r="F52" s="19" t="n">
-        <v>64490</v>
+        <v>26027</v>
       </c>
       <c r="G52" s="19" t="n">
-        <v>24316</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Д35</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="n">
-        <v>45611</v>
-      </c>
-      <c r="G53" s="19" t="n">
-        <v>3036</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="F54" s="19" t="n">
-        <v>39399</v>
-      </c>
-      <c r="G54" s="19" t="n">
-        <v>2969</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="F55" s="19" t="n">
-        <v>33459</v>
-      </c>
-      <c r="G55" s="19" t="n">
-        <v>3046</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="F56" s="19" t="n">
-        <v>26027</v>
-      </c>
-      <c r="G56" s="19" t="n">
         <v>2978</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Д22</t>
-        </is>
-      </c>
-      <c r="F57" s="19" t="n">
-        <v>15931</v>
-      </c>
-      <c r="G57" s="19" t="n">
-        <v>3068</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="F58" s="19" t="n">
-        <v>6042</v>
-      </c>
-      <c r="G58" s="19" t="n">
-        <v>3010</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="F59" s="19" t="n">
-        <v>3447</v>
-      </c>
-      <c r="G59" s="19" t="n">
-        <v>15647</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Д17*</t>
-        </is>
-      </c>
-      <c r="F60" s="19" t="n">
-        <v>3479</v>
-      </c>
-      <c r="G60" s="19" t="n">
-        <v>23560</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Ж</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Вн-1</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="19" t="n">
-        <v>49698</v>
-      </c>
-      <c r="G61" s="19" t="n">
-        <v>61096</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Ж</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Вн-2</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="19" t="n">
-        <v>49724</v>
-      </c>
-      <c r="G62" s="19" t="n">
-        <v>57677</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Ж</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Вн-3</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="19" t="n">
-        <v>49680</v>
-      </c>
-      <c r="G63" s="19" t="n">
-        <v>54743</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Ж</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Вн-4</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="19" t="n">
-        <v>50629</v>
-      </c>
-      <c r="G64" s="19" t="n">
-        <v>47022</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>План на отм. 0.000</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Ж</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Вн-5</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="19" t="n">
-        <v>56334</v>
-      </c>
-      <c r="G65" s="19" t="n">
-        <v>47106</v>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>1 из 4</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="По литерам" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Привязка к чертежам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="В КП, не вошло" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4353,4 +4354,609 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Позиции КП, не вошедшие в спецификацию (нет на чертежах или на чертежах меньше, чем в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Литер</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Площадь 1 шт, м²</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>В КП, шт</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Вошло в спецификацию, шт</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Не вошло, шт</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Площадь не вошедшего, м²</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Причина</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="F4" s="4">
+        <f>ROUND(D4*E4/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3">
+        <f>G4-H4</f>
+        <v/>
+      </c>
+      <c r="J4" s="5">
+        <f>ROUND(I4*F4,2)</f>
+        <v/>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>на чертежах 3 шт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="F5" s="4">
+        <f>ROUND(D5*E5/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3">
+        <f>G5-H5</f>
+        <v/>
+      </c>
+      <c r="J5" s="5">
+        <f>ROUND(I5*F5,2)</f>
+        <v/>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>на чертежах 3 шт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Вн-10</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4160</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="F6" s="4">
+        <f>ROUND(D6*E6/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <f>G6-H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="5">
+        <f>ROUND(I6*F6,2)</f>
+        <v/>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>нет на чертежах</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4130</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F7" s="4">
+        <f>ROUND(D7*E7/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <f>G7-H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>ROUND(I7*F7,2)</f>
+        <v/>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>4060</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F8" s="4">
+        <f>ROUND(D8*E8/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <f>G8-H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>ROUND(I8*F8,2)</f>
+        <v/>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F9" s="4">
+        <f>ROUND(D9*E9/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <f>G9-H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="5">
+        <f>ROUND(I9*F9,2)</f>
+        <v/>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F10" s="4">
+        <f>ROUND(D10*E10/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <f>G10-H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="5">
+        <f>ROUND(I10*F10,2)</f>
+        <v/>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4020</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F11" s="4">
+        <f>ROUND(D11*E11/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <f>G11-H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="5">
+        <f>ROUND(I11*F11,2)</f>
+        <v/>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F12" s="4">
+        <f>ROUND(D12*E12/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <f>G12-H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="5">
+        <f>ROUND(I12*F12,2)</f>
+        <v/>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2860</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F13" s="4">
+        <f>ROUND(D13*E13/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <f>G13-H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="5">
+        <f>ROUND(I13*F13,2)</f>
+        <v/>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2920</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F14" s="4">
+        <f>ROUND(D14*E14/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <f>G14-H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="5">
+        <f>ROUND(I14*F14,2)</f>
+        <v/>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="8">
+        <f>SUM(G4:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="8">
+        <f>SUM(H4:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="8">
+        <f>SUM(I4:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="10">
+        <f>SUM(J4:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0"/>
+</worksheet>
 </file>
--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -2593,7 +2593,14 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Витражи на чертежах, входящие в КП (координаты — точка выноски, мм). «1 из 3» — на чертеже больше, чем в КП; какие именно — по КП не определить</t>
+          <t>Витражи на чертежах, входящие в КП (координаты — точка выноски, мм)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>«1 из 3» — на чертеже больше, чем в КП; какие именно — по КП не определить</t>
         </is>
       </c>
     </row>

--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Площадь 1 шт, м²</t>
+          <t>Площадь 1 шт по КП, м²</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Площадь всего, м²</t>
+          <t>Площадь по КП, м²</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -604,7 +604,7 @@
         <v>4820</v>
       </c>
       <c r="E4" s="4">
-        <f>ROUND(C4*D4/1000000,2)</f>
+        <f>ROUND(L4/K4,2)</f>
         <v/>
       </c>
       <c r="F4" s="3" t="n">
@@ -617,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2</v>
@@ -626,9 +626,8 @@
         <f>SUM(F4:J4)</f>
         <v/>
       </c>
-      <c r="L4" s="5">
-        <f>ROUND(K4*E4,2)</f>
-        <v/>
+      <c r="L4" s="5" t="n">
+        <v>239.46</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -642,7 +641,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Лит. Г: на чертеже 3 шт., в КП 1</t>
+          <t>Лит. Г: 1 шт. по КП Г + по 1 шт. из КП лит. А и Б (там в КП по 4, на чертеже по 3)</t>
         </is>
       </c>
     </row>
@@ -662,7 +661,7 @@
         <v>4820</v>
       </c>
       <c r="E5" s="4">
-        <f>ROUND(C5*D5/1000000,2)</f>
+        <f>ROUND(L5/K5,2)</f>
         <v/>
       </c>
       <c r="F5" s="3" t="n"/>
@@ -676,9 +675,8 @@
         <f>SUM(F5:J5)</f>
         <v/>
       </c>
-      <c r="L5" s="5">
-        <f>ROUND(K5*E5,2)</f>
-        <v/>
+      <c r="L5" s="5" t="n">
+        <v>19.97</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -704,7 +702,7 @@
         <v>4820</v>
       </c>
       <c r="E6" s="4">
-        <f>ROUND(C6*D6/1000000,2)</f>
+        <f>ROUND(L6/K6,2)</f>
         <v/>
       </c>
       <c r="F6" s="3" t="n">
@@ -718,9 +716,8 @@
         <f>SUM(F6:J6)</f>
         <v/>
       </c>
-      <c r="L6" s="5">
-        <f>ROUND(K6*E6,2)</f>
-        <v/>
+      <c r="L6" s="5" t="n">
+        <v>12.34</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -746,7 +743,7 @@
         <v>4820</v>
       </c>
       <c r="E7" s="4">
-        <f>ROUND(C7*D7/1000000,2)</f>
+        <f>ROUND(L7/K7,2)</f>
         <v/>
       </c>
       <c r="F7" s="3" t="n"/>
@@ -760,9 +757,8 @@
         <f>SUM(F7:J7)</f>
         <v/>
       </c>
-      <c r="L7" s="5">
-        <f>ROUND(K7*E7,2)</f>
-        <v/>
+      <c r="L7" s="5" t="n">
+        <v>19.68</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -792,7 +788,7 @@
         <v>4820</v>
       </c>
       <c r="E8" s="4">
-        <f>ROUND(C8*D8/1000000,2)</f>
+        <f>ROUND(L8/K8,2)</f>
         <v/>
       </c>
       <c r="F8" s="3" t="n"/>
@@ -806,9 +802,8 @@
         <f>SUM(F8:J8)</f>
         <v/>
       </c>
-      <c r="L8" s="5">
-        <f>ROUND(K8*E8,2)</f>
-        <v/>
+      <c r="L8" s="5" t="n">
+        <v>19.97</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -838,7 +833,7 @@
         <v>4820</v>
       </c>
       <c r="E9" s="4">
-        <f>ROUND(C9*D9/1000000,2)</f>
+        <f>ROUND(L9/K9,2)</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n"/>
@@ -852,9 +847,8 @@
         <f>SUM(F9:J9)</f>
         <v/>
       </c>
-      <c r="L9" s="5">
-        <f>ROUND(K9*E9,2)</f>
-        <v/>
+      <c r="L9" s="5" t="n">
+        <v>11.09</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -880,7 +874,7 @@
         <v>4820</v>
       </c>
       <c r="E10" s="4">
-        <f>ROUND(C10*D10/1000000,2)</f>
+        <f>ROUND(L10/K10,2)</f>
         <v/>
       </c>
       <c r="F10" s="3" t="n"/>
@@ -894,9 +888,8 @@
         <f>SUM(F10:J10)</f>
         <v/>
       </c>
-      <c r="L10" s="5">
-        <f>ROUND(K10*E10,2)</f>
-        <v/>
+      <c r="L10" s="5" t="n">
+        <v>15.6</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -926,7 +919,7 @@
         <v>4820</v>
       </c>
       <c r="E11" s="4">
-        <f>ROUND(C11*D11/1000000,2)</f>
+        <f>ROUND(L11/K11,2)</f>
         <v/>
       </c>
       <c r="F11" s="3" t="n"/>
@@ -940,9 +933,8 @@
         <f>SUM(F11:J11)</f>
         <v/>
       </c>
-      <c r="L11" s="5">
-        <f>ROUND(K11*E11,2)</f>
-        <v/>
+      <c r="L11" s="5" t="n">
+        <v>14.74</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -968,7 +960,7 @@
         <v>4820</v>
       </c>
       <c r="E12" s="4">
-        <f>ROUND(C12*D12/1000000,2)</f>
+        <f>ROUND(L12/K12,2)</f>
         <v/>
       </c>
       <c r="F12" s="3" t="n">
@@ -982,9 +974,8 @@
         <f>SUM(F12:J12)</f>
         <v/>
       </c>
-      <c r="L12" s="5">
-        <f>ROUND(K12*E12,2)</f>
-        <v/>
+      <c r="L12" s="5" t="n">
+        <v>11.14</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1014,7 +1005,7 @@
         <v>4820</v>
       </c>
       <c r="E13" s="4">
-        <f>ROUND(C13*D13/1000000,2)</f>
+        <f>ROUND(L13/K13,2)</f>
         <v/>
       </c>
       <c r="F13" s="3" t="n">
@@ -1030,9 +1021,8 @@
         <f>SUM(F13:J13)</f>
         <v/>
       </c>
-      <c r="L13" s="5">
-        <f>ROUND(K13*E13,2)</f>
-        <v/>
+      <c r="L13" s="5" t="n">
+        <v>11.62</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1062,7 +1052,7 @@
         <v>4820</v>
       </c>
       <c r="E14" s="4">
-        <f>ROUND(C14*D14/1000000,2)</f>
+        <f>ROUND(L14/K14,2)</f>
         <v/>
       </c>
       <c r="F14" s="3" t="n"/>
@@ -1076,9 +1066,8 @@
         <f>SUM(F14:J14)</f>
         <v/>
       </c>
-      <c r="L14" s="5">
-        <f>ROUND(K14*E14,2)</f>
-        <v/>
+      <c r="L14" s="5" t="n">
+        <v>18.57</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1112,7 +1101,7 @@
         <v>4820</v>
       </c>
       <c r="E15" s="4">
-        <f>ROUND(C15*D15/1000000,2)</f>
+        <f>ROUND(L15/K15,2)</f>
         <v/>
       </c>
       <c r="F15" s="3" t="n"/>
@@ -1132,9 +1121,8 @@
         <f>SUM(F15:J15)</f>
         <v/>
       </c>
-      <c r="L15" s="5">
-        <f>ROUND(K15*E15,2)</f>
-        <v/>
+      <c r="L15" s="5" t="n">
+        <v>77.13</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1168,7 +1156,7 @@
         <v>4820</v>
       </c>
       <c r="E16" s="4">
-        <f>ROUND(C16*D16/1000000,2)</f>
+        <f>ROUND(L16/K16,2)</f>
         <v/>
       </c>
       <c r="F16" s="3" t="n"/>
@@ -1182,9 +1170,8 @@
         <f>SUM(F16:J16)</f>
         <v/>
       </c>
-      <c r="L16" s="5">
-        <f>ROUND(K16*E16,2)</f>
-        <v/>
+      <c r="L16" s="5" t="n">
+        <v>11.9</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1214,7 +1201,7 @@
         <v>4820</v>
       </c>
       <c r="E17" s="4">
-        <f>ROUND(C17*D17/1000000,2)</f>
+        <f>ROUND(L17/K17,2)</f>
         <v/>
       </c>
       <c r="F17" s="3" t="n"/>
@@ -1228,9 +1215,8 @@
         <f>SUM(F17:J17)</f>
         <v/>
       </c>
-      <c r="L17" s="5">
-        <f>ROUND(K17*E17,2)</f>
-        <v/>
+      <c r="L17" s="5" t="n">
+        <v>24.67</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1260,7 +1246,7 @@
         <v>4820</v>
       </c>
       <c r="E18" s="4">
-        <f>ROUND(C18*D18/1000000,2)</f>
+        <f>ROUND(L18/K18,2)</f>
         <v/>
       </c>
       <c r="F18" s="3" t="n"/>
@@ -1274,9 +1260,8 @@
         <f>SUM(F18:J18)</f>
         <v/>
       </c>
-      <c r="L18" s="5">
-        <f>ROUND(K18*E18,2)</f>
-        <v/>
+      <c r="L18" s="5" t="n">
+        <v>18.43</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1302,7 +1287,7 @@
         <v>4820</v>
       </c>
       <c r="E19" s="4">
-        <f>ROUND(C19*D19/1000000,2)</f>
+        <f>ROUND(L19/K19,2)</f>
         <v/>
       </c>
       <c r="F19" s="3" t="n"/>
@@ -1316,9 +1301,8 @@
         <f>SUM(F19:J19)</f>
         <v/>
       </c>
-      <c r="L19" s="5">
-        <f>ROUND(K19*E19,2)</f>
-        <v/>
+      <c r="L19" s="5" t="n">
+        <v>14.02</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1344,7 +1328,7 @@
         <v>2720</v>
       </c>
       <c r="E20" s="4">
-        <f>ROUND(C20*D20/1000000,2)</f>
+        <f>ROUND(L20/K20,2)</f>
         <v/>
       </c>
       <c r="F20" s="3" t="n">
@@ -1362,9 +1346,8 @@
         <f>SUM(F20:J20)</f>
         <v/>
       </c>
-      <c r="L20" s="5">
-        <f>ROUND(K20*E20,2)</f>
-        <v/>
+      <c r="L20" s="5" t="n">
+        <v>62.85</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1427,7 +1410,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Размеры — из таблицы заказчика (длина × высота). Количество — по чертежам, но не больше, чем в КП; позиции, которых нет в КП, исключены.</t>
+          <t>Размеры — из таблицы заказчика (длина × высота). Количество — по чертежам, но не больше, чем в КП. Площади — по КП (площадь 1 шт — средняя).</t>
         </is>
       </c>
     </row>
@@ -1443,11 +1426,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -1486,7 +1469,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Площадь 1 шт, м²</t>
+          <t>Площадь 1 шт по КП, м²</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1496,7 +1479,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Площадь всего, м²</t>
+          <t>Площадь по КП, м²</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1535,15 +1518,14 @@
         <v>4820</v>
       </c>
       <c r="E5" s="4">
-        <f>ROUND(C5*D5/1000000,2)</f>
+        <f>ROUND(G5/F5,2)</f>
         <v/>
       </c>
       <c r="F5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="5">
-        <f>ROUND(F5*E5,2)</f>
-        <v/>
+      <c r="G5" s="5" t="n">
+        <v>59.68</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1567,15 +1549,14 @@
         <v>4820</v>
       </c>
       <c r="E6" s="4">
-        <f>ROUND(C6*D6/1000000,2)</f>
+        <f>ROUND(G6/F6,2)</f>
         <v/>
       </c>
       <c r="F6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="5">
-        <f>ROUND(F6*E6,2)</f>
-        <v/>
+      <c r="G6" s="5" t="n">
+        <v>12.34</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -1599,15 +1580,14 @@
         <v>4820</v>
       </c>
       <c r="E7" s="4">
-        <f>ROUND(C7*D7/1000000,2)</f>
+        <f>ROUND(G7/F7,2)</f>
         <v/>
       </c>
       <c r="F7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="5">
-        <f>ROUND(F7*E7,2)</f>
-        <v/>
+      <c r="G7" s="5" t="n">
+        <v>11.14</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1631,15 +1611,14 @@
         <v>4820</v>
       </c>
       <c r="E8" s="4">
-        <f>ROUND(C8*D8/1000000,2)</f>
+        <f>ROUND(G8/F8,2)</f>
         <v/>
       </c>
       <c r="F8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="5">
-        <f>ROUND(F8*E8,2)</f>
-        <v/>
+      <c r="G8" s="5" t="n">
+        <v>5.62</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1663,15 +1642,14 @@
         <v>2720</v>
       </c>
       <c r="E9" s="4">
-        <f>ROUND(C9*D9/1000000,2)</f>
+        <f>ROUND(G9/F9,2)</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="5">
-        <f>ROUND(F9*E9,2)</f>
-        <v/>
+      <c r="G9" s="5" t="n">
+        <v>28.57</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -1729,15 +1707,14 @@
         <v>4820</v>
       </c>
       <c r="E12" s="4">
-        <f>ROUND(C12*D12/1000000,2)</f>
+        <f>ROUND(G12/F12,2)</f>
         <v/>
       </c>
       <c r="F12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="5">
-        <f>ROUND(F12*E12,2)</f>
-        <v/>
+      <c r="G12" s="5" t="n">
+        <v>59.86</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -1761,15 +1738,14 @@
         <v>4820</v>
       </c>
       <c r="E13" s="4">
-        <f>ROUND(C13*D13/1000000,2)</f>
+        <f>ROUND(G13/F13,2)</f>
         <v/>
       </c>
       <c r="F13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="5">
-        <f>ROUND(F13*E13,2)</f>
-        <v/>
+      <c r="G13" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -1793,15 +1769,14 @@
         <v>4820</v>
       </c>
       <c r="E14" s="4">
-        <f>ROUND(C14*D14/1000000,2)</f>
+        <f>ROUND(G14/F14,2)</f>
         <v/>
       </c>
       <c r="F14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="5">
-        <f>ROUND(F14*E14,2)</f>
-        <v/>
+      <c r="G14" s="5" t="n">
+        <v>19.49</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -1825,15 +1800,14 @@
         <v>4820</v>
       </c>
       <c r="E15" s="4">
-        <f>ROUND(C15*D15/1000000,2)</f>
+        <f>ROUND(G15/F15,2)</f>
         <v/>
       </c>
       <c r="F15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="5">
-        <f>ROUND(F15*E15,2)</f>
-        <v/>
+      <c r="G15" s="5" t="n">
+        <v>11.9</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -1857,15 +1831,14 @@
         <v>2720</v>
       </c>
       <c r="E16" s="4">
-        <f>ROUND(C16*D16/1000000,2)</f>
+        <f>ROUND(G16/F16,2)</f>
         <v/>
       </c>
       <c r="F16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="5">
-        <f>ROUND(F16*E16,2)</f>
-        <v/>
+      <c r="G16" s="5" t="n">
+        <v>28.57</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -1923,15 +1896,14 @@
         <v>4820</v>
       </c>
       <c r="E19" s="4">
-        <f>ROUND(C19*D19/1000000,2)</f>
+        <f>ROUND(G19/F19,2)</f>
         <v/>
       </c>
       <c r="F19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="5">
-        <f>ROUND(F19*E19,2)</f>
-        <v/>
+      <c r="G19" s="5" t="n">
+        <v>19.63</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -1955,15 +1927,14 @@
         <v>4820</v>
       </c>
       <c r="E20" s="4">
-        <f>ROUND(C20*D20/1000000,2)</f>
+        <f>ROUND(G20/F20,2)</f>
         <v/>
       </c>
       <c r="F20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="5">
-        <f>ROUND(F20*E20,2)</f>
-        <v/>
+      <c r="G20" s="5" t="n">
+        <v>14.74</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -1987,15 +1958,14 @@
         <v>4820</v>
       </c>
       <c r="E21" s="4">
-        <f>ROUND(C21*D21/1000000,2)</f>
+        <f>ROUND(G21/F21,2)</f>
         <v/>
       </c>
       <c r="F21" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="5">
-        <f>ROUND(F21*E21,2)</f>
-        <v/>
+      <c r="G21" s="5" t="n">
+        <v>18.57</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -2019,15 +1989,14 @@
         <v>4820</v>
       </c>
       <c r="E22" s="4">
-        <f>ROUND(C22*D22/1000000,2)</f>
+        <f>ROUND(G22/F22,2)</f>
         <v/>
       </c>
       <c r="F22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="5">
-        <f>ROUND(F22*E22,2)</f>
-        <v/>
+      <c r="G22" s="5" t="n">
+        <v>19.68</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -2051,15 +2020,14 @@
         <v>4820</v>
       </c>
       <c r="E23" s="4">
-        <f>ROUND(C23*D23/1000000,2)</f>
+        <f>ROUND(G23/F23,2)</f>
         <v/>
       </c>
       <c r="F23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="5">
-        <f>ROUND(F23*E23,2)</f>
-        <v/>
+      <c r="G23" s="5" t="n">
+        <v>24.67</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -2083,15 +2051,14 @@
         <v>2720</v>
       </c>
       <c r="E24" s="4">
-        <f>ROUND(C24*D24/1000000,2)</f>
+        <f>ROUND(G24/F24,2)</f>
         <v/>
       </c>
       <c r="F24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="5">
-        <f>ROUND(F24*E24,2)</f>
-        <v/>
+      <c r="G24" s="5" t="n">
+        <v>5.71</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -2149,15 +2116,14 @@
         <v>4820</v>
       </c>
       <c r="E27" s="4">
-        <f>ROUND(C27*D27/1000000,2)</f>
+        <f>ROUND(G27/F27,2)</f>
         <v/>
       </c>
       <c r="F27" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="5">
-        <f>ROUND(F27*E27,2)</f>
-        <v/>
+      <c r="G27" s="5" t="n">
+        <v>20.45</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -2171,25 +2137,24 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Вн-10</t>
+          <t>Вн-6 (из КП лит. А)</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4160</v>
+        <v>4200</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>4820</v>
       </c>
       <c r="E28" s="4">
-        <f>ROUND(C28*D28/1000000,2)</f>
+        <f>ROUND(G28/F28,2)</f>
         <v/>
       </c>
       <c r="F28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="5">
-        <f>ROUND(F28*E28,2)</f>
-        <v/>
+      <c r="G28" s="5" t="n">
+        <v>19.9</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -2203,25 +2168,24 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Вн-11</t>
+          <t>Вн-6 (из КП лит. Б)</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2450</v>
+        <v>4200</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>4820</v>
       </c>
       <c r="E29" s="4">
-        <f>ROUND(C29*D29/1000000,2)</f>
+        <f>ROUND(G29/F29,2)</f>
         <v/>
       </c>
       <c r="F29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="5">
-        <f>ROUND(F29*E29,2)</f>
-        <v/>
+      <c r="G29" s="5" t="n">
+        <v>19.96</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -2235,25 +2199,24 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Вн-12</t>
+          <t>Вн-10</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3370</v>
+        <v>4160</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>4820</v>
       </c>
       <c r="E30" s="4">
-        <f>ROUND(C30*D30/1000000,2)</f>
+        <f>ROUND(G30/F30,2)</f>
         <v/>
       </c>
       <c r="F30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="5">
-        <f>ROUND(F30*E30,2)</f>
-        <v/>
+      <c r="G30" s="5" t="n">
+        <v>19.97</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -2267,25 +2230,24 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-11</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>4200</v>
+        <v>2450</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>4820</v>
       </c>
       <c r="E31" s="4">
-        <f>ROUND(C31*D31/1000000,2)</f>
+        <f>ROUND(G31/F31,2)</f>
         <v/>
       </c>
       <c r="F31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="5">
-        <f>ROUND(F31*E31,2)</f>
-        <v/>
+      <c r="G31" s="5" t="n">
+        <v>11.09</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -2299,25 +2261,24 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Вн-20</t>
+          <t>Вн-12</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>3900</v>
+        <v>3370</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>4820</v>
       </c>
       <c r="E32" s="4">
-        <f>ROUND(C32*D32/1000000,2)</f>
+        <f>ROUND(G32/F32,2)</f>
         <v/>
       </c>
       <c r="F32" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="5">
-        <f>ROUND(F32*E32,2)</f>
-        <v/>
+      <c r="G32" s="5" t="n">
+        <v>15.6</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -2331,25 +2292,24 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Вн-21</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2920</v>
+        <v>4200</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>4820</v>
       </c>
       <c r="E33" s="4">
-        <f>ROUND(C33*D33/1000000,2)</f>
+        <f>ROUND(G33/F33,2)</f>
         <v/>
       </c>
       <c r="F33" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="5">
-        <f>ROUND(F33*E33,2)</f>
-        <v/>
+      <c r="G33" s="5" t="n">
+        <v>19.82</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -2358,102 +2318,100 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n"/>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="A34" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Вн-20</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3900</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E34" s="4">
+        <f>ROUND(G34/F34,2)</f>
+        <v/>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Вн-21</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>2920</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E35" s="4">
+        <f>ROUND(G35/F35,2)</f>
+        <v/>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Итого литер Г</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="8">
-        <f>SUM(F27:F33)</f>
-        <v/>
-      </c>
-      <c r="G34" s="10">
-        <f>SUM(G27:G33)</f>
-        <v/>
-      </c>
-      <c r="H34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n"/>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="8">
+        <f>SUM(F27:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="10">
+        <f>SUM(G27:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Литер Д</t>
         </is>
       </c>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="15" t="n"/>
-      <c r="H35" s="13" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E36" s="4">
-        <f>ROUND(C36*D36/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" s="5">
-        <f>ROUND(F36*E36,2)</f>
-        <v/>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Вн-7</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>3020</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E37" s="4">
-        <f>ROUND(C37*D37/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5">
-        <f>ROUND(F37*E37,2)</f>
-        <v/>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="13" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -2461,25 +2419,24 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Вн-9</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>3870</v>
+        <v>4200</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>4820</v>
       </c>
       <c r="E38" s="4">
-        <f>ROUND(C38*D38/1000000,2)</f>
+        <f>ROUND(G38/F38,2)</f>
         <v/>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5">
-        <f>ROUND(F38*E38,2)</f>
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>39.98</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -2493,25 +2450,24 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-7</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>4200</v>
+        <v>3020</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>4820</v>
       </c>
       <c r="E39" s="4">
-        <f>ROUND(C39*D39/1000000,2)</f>
+        <f>ROUND(G39/F39,2)</f>
         <v/>
       </c>
       <c r="F39" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="5">
-        <f>ROUND(F39*E39,2)</f>
-        <v/>
+      <c r="G39" s="5" t="n">
+        <v>19.97</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -2520,52 +2476,114 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n"/>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="A40" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>3870</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E40" s="4">
+        <f>ROUND(G40/F40,2)</f>
+        <v/>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E41" s="4">
+        <f>ROUND(G41/F41,2)</f>
+        <v/>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Итого литер Д</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="8">
-        <f>SUM(F36:F39)</f>
-        <v/>
-      </c>
-      <c r="G40" s="10">
-        <f>SUM(G36:G39)</f>
-        <v/>
-      </c>
-      <c r="H40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="8">
+        <f>SUM(F38:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="10">
+        <f>SUM(G38:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n"/>
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>ВСЕГО</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="16">
-        <f>F10+F17+F25+F34+F40</f>
-        <v/>
-      </c>
-      <c r="G41" s="17">
-        <f>G10+G17+G25+G34+G40</f>
-        <v/>
-      </c>
-      <c r="H41" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="16">
+        <f>F10+F17+F25+F36+F42</f>
+        <v/>
+      </c>
+      <c r="G43" s="17">
+        <f>G10+G17+G25+G36+G42</f>
+        <v/>
+      </c>
+      <c r="H43" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B35:H35"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3382,7 +3400,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>1 из 3</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3436,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>1 из 3</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3472,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>1 из 3</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4420,7 +4438,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Площадь 1 шт, м²</t>
+          <t>Площадь 1 шт по КП, м²</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -4455,29 +4473,28 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Д</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-10</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4200</v>
+        <v>4160</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>4820</v>
       </c>
-      <c r="F4" s="4">
-        <f>ROUND(D4*E4/1000000,2)</f>
-        <v/>
+      <c r="F4" s="4" t="n">
+        <v>20.16</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3">
         <f>G4-H4</f>
@@ -4489,7 +4506,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>на чертежах 3 шт.</t>
+          <t>нет на чертежах</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4516,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>без литера</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -4508,20 +4525,20 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4200</v>
+        <v>4130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4820</v>
+        <v>4800</v>
       </c>
       <c r="F5" s="4">
         <f>ROUND(D5*E5/1000000,2)</f>
         <v/>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
         <f>G5-H5</f>
@@ -4533,7 +4550,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>на чертежах 3 шт.</t>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
         </is>
       </c>
     </row>
@@ -4543,19 +4560,19 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Д</t>
+          <t>без литера</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Вн-10</t>
+          <t>Вн-9</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4160</v>
+        <v>4060</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4820</v>
+        <v>4800</v>
       </c>
       <c r="F6" s="4">
         <f>ROUND(D6*E6/1000000,2)</f>
@@ -4577,7 +4594,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>нет на чертежах</t>
+          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
         </is>
       </c>
     </row>
@@ -4592,11 +4609,11 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-16</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4130</v>
+        <v>1320</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>4800</v>
@@ -4636,11 +4653,11 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Вн-9</t>
+          <t>Вн-16</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4060</v>
+        <v>1020</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>4800</v>
@@ -4680,11 +4697,11 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Вн-16</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1320</v>
+        <v>4020</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>4800</v>
@@ -4724,11 +4741,11 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Вн-16</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1020</v>
+        <v>3750</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>4800</v>
@@ -4768,11 +4785,11 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-19</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4020</v>
+        <v>2860</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>4800</v>
@@ -4812,11 +4829,11 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-19</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3750</v>
+        <v>2920</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>4800</v>
@@ -4846,121 +4863,33 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>без литера</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Вн-19</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>2860</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F13" s="4">
-        <f>ROUND(D13*E13/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <f>G13-H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="5">
-        <f>ROUND(I13*F13,2)</f>
-        <v/>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>без литера</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Вн-19</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>2920</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F14" s="4">
-        <f>ROUND(D14*E14/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <f>G14-H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="5">
-        <f>ROUND(I14*F14,2)</f>
-        <v/>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>остаток КП без литера, по размеру к строкам договора не подходит</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="8">
-        <f>SUM(G4:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="8">
-        <f>SUM(H4:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="8">
-        <f>SUM(I4:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="10">
-        <f>SUM(J4:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="11" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="8">
+        <f>SUM(G4:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="8">
+        <f>SUM(H4:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="8">
+        <f>SUM(I4:I12)</f>
+        <v/>
+      </c>
+      <c r="J13" s="10">
+        <f>SUM(J4:J12)</f>
+        <v/>
+      </c>
+      <c r="K13" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="По литерам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Привязка к чертежам" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="В КП, не вошло" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По литерам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Привязка к чертежам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="В КП, не вошло" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сверка с КП" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,6 +120,14 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1446,7 +1455,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>№</t>
@@ -1525,7 +1534,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>59.68</v>
+        <v>59.76</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1714,7 +1723,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>59.86</v>
+        <v>58.46</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2146,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Вн-6 (из КП лит. А)</t>
+          <t>Вн-6 (из КП лит. А, 4130)</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -2154,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2177,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Вн-6 (из КП лит. Б)</t>
+          <t>Вн-6 (из КП лит. Б, 4450)</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -2185,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>19.96</v>
+        <v>21.36</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -4895,4 +4904,3387 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Сверка с КП. В спецификации площадь по КП = ширина × высота из КП (как в таблице заказчика)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>«Площадь в КП» — цифра из самого КП: она меньше, т.к. двери посчитаны отдельными КП от 13.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>1. Позиции КП на витражи</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>КП</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>№ в КП</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Кол-во, шт</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>Площадь по размерам КП, м²</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>Площадь в КП, м²</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>Разница, м²</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Куда отнесено</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Блок А 06.04</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4150</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4">
+        <f>ROUND(E5*F5*G5/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="J5" s="4">
+        <f>H5-I5</f>
+        <v/>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Блок А 06.04</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Вн-8</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2570</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4">
+        <f>ROUND(E6*F6*G6/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="J6" s="4">
+        <f>H6-I6</f>
+        <v/>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Блок А 06.04</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4">
+        <f>ROUND(E7*F7*G7/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J7" s="4">
+        <f>H7-I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Блок А 06.04</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Вн-14</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2320</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4">
+        <f>ROUND(E8*F8*G8/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="J8" s="4">
+        <f>H8-I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Блок Б 06.04</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>4040</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4">
+        <f>ROUND(E9*F9*G9/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="J9" s="4">
+        <f>H9-I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Блок Б 06.04</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>4060</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4">
+        <f>ROUND(E10*F10*G10/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="J10" s="4">
+        <f>H10-I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Блок Б 06.04</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>4060</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4">
+        <f>ROUND(E11*F11*G11/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="J11" s="4">
+        <f>H11-I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Блок Б 06.04</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4">
+        <f>ROUND(E12*F12*G12/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="J12" s="4">
+        <f>H12-I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Блок Б 06.04</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Вн-18</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2480</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <f>ROUND(E13*F13*G13/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J13" s="4">
+        <f>H13-I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Блок Б 06.04</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>4080</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <f>ROUND(E14*F14*G14/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="J14" s="4">
+        <f>H14-I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>КП без шапки 06.04 (лит. Д)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Вн-10</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4">
+        <f>ROUND(E15*F15*G15/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="J15" s="4">
+        <f>H15-I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>КП без шапки 06.04 (лит. Д)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>4100</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4">
+        <f>ROUND(E16*F16*G16/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="J16" s="4">
+        <f>H16-I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>КП без шапки 06.04 (лит. Д)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>3780</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <f>ROUND(E17*F17*G17/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="J17" s="4">
+        <f>H17-I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>КП без шапки 06.04 (лит. Д)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>4140</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4">
+        <f>ROUND(E18*F18*G18/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="J18" s="4">
+        <f>H18-I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>КП без шапки 06.04 (лит. Д)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Вн-7</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>4160</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4">
+        <f>ROUND(E19*F19*G19/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="J19" s="4">
+        <f>H19-I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>КП без шапки 06.04 (лит. Д)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>4190</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4">
+        <f>ROUND(E20*F20*G20/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J20" s="4">
+        <f>H20-I20</f>
+        <v/>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Блок В 06.04 (1)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4">
+        <f>ROUND(E21*F21*G21/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" s="4">
+        <f>H21-I21</f>
+        <v/>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Блок В 06.04 (1)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>5180</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <f>ROUND(E22*F22*G22/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J22" s="4">
+        <f>H22-I22</f>
+        <v/>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Блок В 06.04 (2)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>4090</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4">
+        <f>ROUND(E23*F23*G23/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="J23" s="4">
+        <f>H23-I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Блок В 06.04 (2)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>4100</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4">
+        <f>ROUND(E24*F24*G24/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="J24" s="4">
+        <f>H24-I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Блок В 06.04 (2)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4">
+        <f>ROUND(E25*F25*G25/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J25" s="4">
+        <f>H25-I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Блок В 06.04 (2)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2570</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="4">
+        <f>ROUND(E26*F26*G26/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="J26" s="4">
+        <f>H26-I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22 06.04</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="4">
+        <f>ROUND(E27*F27*G27/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="J27" s="4">
+        <f>H27-I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22 06.04</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="4">
+        <f>ROUND(E28*F28*G28/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="J28" s="4">
+        <f>H28-I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22 06.04</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>2760</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4">
+        <f>ROUND(E29*F29*G29/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J29" s="4">
+        <f>H29-I29</f>
+        <v/>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4">
+        <f>ROUND(E30*F30*G30/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="J30" s="4">
+        <f>H30-I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2920</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4">
+        <f>ROUND(E31*F31*G31/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="J31" s="4">
+        <f>H31-I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Вн-13</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>3070</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
+        <f>ROUND(E32*F32*G32/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="J32" s="4">
+        <f>H32-I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4">
+        <f>ROUND(E33*F33*G33/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J33" s="4">
+        <f>H33-I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4">
+        <f>ROUND(E34*F34*G34/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J34" s="4">
+        <f>H34-I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>4130</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4">
+        <f>ROUND(E35*F35*G35/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="J35" s="4">
+        <f>H35-I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Г (перенос из А)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>4130</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="4">
+        <f>ROUND(E36*F36*G36/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="J36" s="4">
+        <f>H36-I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>4450</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4">
+        <f>ROUND(E37*F37*G37/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="J37" s="4">
+        <f>H37-I37</f>
+        <v/>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Г (перенос из Б)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>4020</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4">
+        <f>ROUND(E38*F38*G38/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="J38" s="4">
+        <f>H38-I38</f>
+        <v/>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Вн-21</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2920</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4">
+        <f>ROUND(E39*F39*G39/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J39" s="4">
+        <f>H39-I39</f>
+        <v/>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>4260</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4">
+        <f>ROUND(E40*F40*G40/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="J40" s="4">
+        <f>H40-I40</f>
+        <v/>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Вн-20</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>3840</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4">
+        <f>ROUND(E41*F41*G41/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="J41" s="4">
+        <f>H41-I41</f>
+        <v/>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Вн-12</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>3250</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4">
+        <f>ROUND(E42*F42*G42/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="J42" s="4">
+        <f>H42-I42</f>
+        <v/>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Вн-11</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="4">
+        <f>ROUND(E43*F43*G43/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="J43" s="4">
+        <f>H43-I43</f>
+        <v/>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Вн-10</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>4160</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4">
+        <f>ROUND(E44*F44*G44/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="J44" s="4">
+        <f>H44-I44</f>
+        <v/>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>4060</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4">
+        <f>ROUND(E45*F45*G45/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="J45" s="4">
+        <f>H45-I45</f>
+        <v/>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4">
+        <f>ROUND(E46*F46*G46/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="J46" s="4">
+        <f>H46-I46</f>
+        <v/>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Режиссёр 1-18 25.09</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>4130</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4">
+        <f>ROUND(E47*F47*G47/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="J47" s="4">
+        <f>H47-I47</f>
+        <v/>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>не вошло</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="8">
+        <f>SUM(G5:G47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="22">
+        <f>SUM(H5:H47)</f>
+        <v/>
+      </c>
+      <c r="I48" s="22">
+        <f>SUM(I5:I47)</f>
+        <v/>
+      </c>
+      <c r="J48" s="22">
+        <f>SUM(J5:J47)</f>
+        <v/>
+      </c>
+      <c r="K48" s="21" t="n"/>
+    </row>
+    <row r="49">
+      <c r="H49" s="23" t="n"/>
+      <c r="I49" s="23" t="n"/>
+      <c r="J49" s="23" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>2. Двери к витражам (КП от 13.04.2026) — в спецификацию не добавлены, для справки</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="n"/>
+      <c r="I50" s="23" t="n"/>
+      <c r="J50" s="23" t="n"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>КП</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Литер</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Кол-во, шт</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>Площадь по размерам, м²</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
+        <is>
+          <t>Площадь в КП, м²</t>
+        </is>
+      </c>
+      <c r="J51" s="23" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>№9 А</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="4">
+        <f>ROUND(E52*F52*G52/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J52" s="23" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>№9 А</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Вн-14</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4">
+        <f>ROUND(E53*F53*G53/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J53" s="23" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>№9 А</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4">
+        <f>ROUND(E54*F54*G54/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J54" s="23" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>№11 Б</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="4">
+        <f>ROUND(E55*F55*G55/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J55" s="23" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>№11 Б</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Вн-18</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4">
+        <f>ROUND(E56*F56*G56/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J56" s="23" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>№11 Б</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1186</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4">
+        <f>ROUND(E57*F57*G57/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J57" s="23" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>№14 (Д)</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Вн-10</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4">
+        <f>ROUND(E58*F58*G58/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J58" s="23" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>№14 (Д)</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="4">
+        <f>ROUND(E59*F59*G59/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J59" s="23" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>№14 (Д)</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4">
+        <f>ROUND(E60*F60*G60/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J60" s="23" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>№12 В</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4">
+        <f>ROUND(E61*F61*G61/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J61" s="23" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>№12 В</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="4">
+        <f>ROUND(E62*F62*G62/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J62" s="23" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>№12 В</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1176</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4">
+        <f>ROUND(E63*F63*G63/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J63" s="23" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>№15 Вн-22</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>А, Б, В</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>2193</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H64" s="4">
+        <f>ROUND(E64*F64*G64/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="J64" s="23" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="n"/>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="21" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="8">
+        <f>SUM(G52:G64)</f>
+        <v/>
+      </c>
+      <c r="H65" s="22">
+        <f>SUM(H52:H64)</f>
+        <v/>
+      </c>
+      <c r="I65" s="22">
+        <f>SUM(I52:I64)</f>
+        <v/>
+      </c>
+      <c r="J65" s="23" t="n"/>
+    </row>
+    <row r="66">
+      <c r="H66" s="23" t="n"/>
+      <c r="I66" s="23" t="n"/>
+      <c r="J66" s="23" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>3. Что поправлено в спецификации</t>
+        </is>
+      </c>
+      <c r="H67" s="23" t="n"/>
+      <c r="I67" s="23" t="n"/>
+      <c r="J67" s="23" t="n"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Литер</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Было, м²</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Стало (по КП), м²</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Разница, м²</t>
+        </is>
+      </c>
+      <c r="H68" s="23" t="n"/>
+      <c r="I68" s="23" t="n"/>
+      <c r="J68" s="23" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="F69" s="4">
+        <f>ROUND(E69-D69,2)</f>
+        <v/>
+      </c>
+      <c r="H69" s="23" t="n"/>
+      <c r="I69" s="23" t="n"/>
+      <c r="J69" s="23" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Вн-8</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="F70" s="4">
+        <f>ROUND(E70-D70,2)</f>
+        <v/>
+      </c>
+      <c r="H70" s="23" t="n"/>
+      <c r="I70" s="23" t="n"/>
+      <c r="J70" s="23" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Вн-14</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="F71" s="4">
+        <f>ROUND(E71-D71,2)</f>
+        <v/>
+      </c>
+      <c r="H71" s="23" t="n"/>
+      <c r="I71" s="23" t="n"/>
+      <c r="J71" s="23" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="F72" s="4">
+        <f>ROUND(E72-D72,2)</f>
+        <v/>
+      </c>
+      <c r="H72" s="23" t="n"/>
+      <c r="I72" s="23" t="n"/>
+      <c r="J72" s="23" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="F73" s="4">
+        <f>ROUND(E73-D73,2)</f>
+        <v/>
+      </c>
+      <c r="H73" s="23" t="n"/>
+      <c r="I73" s="23" t="n"/>
+      <c r="J73" s="23" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="F74" s="4">
+        <f>ROUND(E74-D74,2)</f>
+        <v/>
+      </c>
+      <c r="H74" s="23" t="n"/>
+      <c r="I74" s="23" t="n"/>
+      <c r="J74" s="23" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" s="4">
+        <f>ROUND(E75-D75,2)</f>
+        <v/>
+      </c>
+      <c r="H75" s="23" t="n"/>
+      <c r="I75" s="23" t="n"/>
+      <c r="J75" s="23" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="F76" s="4">
+        <f>ROUND(E76-D76,2)</f>
+        <v/>
+      </c>
+      <c r="H76" s="23" t="n"/>
+      <c r="I76" s="23" t="n"/>
+      <c r="J76" s="23" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Вн-18</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F77" s="4">
+        <f>ROUND(E77-D77,2)</f>
+        <v/>
+      </c>
+      <c r="H77" s="23" t="n"/>
+      <c r="I77" s="23" t="n"/>
+      <c r="J77" s="23" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="F78" s="4">
+        <f>ROUND(E78-D78,2)</f>
+        <v/>
+      </c>
+      <c r="H78" s="23" t="n"/>
+      <c r="I78" s="23" t="n"/>
+      <c r="J78" s="23" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="F79" s="4">
+        <f>ROUND(E79-D79,2)</f>
+        <v/>
+      </c>
+      <c r="H79" s="23" t="n"/>
+      <c r="I79" s="23" t="n"/>
+      <c r="J79" s="23" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Вн-13</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="F80" s="4">
+        <f>ROUND(E80-D80,2)</f>
+        <v/>
+      </c>
+      <c r="H80" s="23" t="n"/>
+      <c r="I80" s="23" t="n"/>
+      <c r="J80" s="23" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="F81" s="4">
+        <f>ROUND(E81-D81,2)</f>
+        <v/>
+      </c>
+      <c r="H81" s="23" t="n"/>
+      <c r="I81" s="23" t="n"/>
+      <c r="J81" s="23" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="F82" s="4">
+        <f>ROUND(E82-D82,2)</f>
+        <v/>
+      </c>
+      <c r="H82" s="23" t="n"/>
+      <c r="I82" s="23" t="n"/>
+      <c r="J82" s="23" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="F83" s="4">
+        <f>ROUND(E83-D83,2)</f>
+        <v/>
+      </c>
+      <c r="H83" s="23" t="n"/>
+      <c r="I83" s="23" t="n"/>
+      <c r="J83" s="23" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F84" s="4">
+        <f>ROUND(E84-D84,2)</f>
+        <v/>
+      </c>
+      <c r="H84" s="23" t="n"/>
+      <c r="I84" s="23" t="n"/>
+      <c r="J84" s="23" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="F85" s="4">
+        <f>ROUND(E85-D85,2)</f>
+        <v/>
+      </c>
+      <c r="H85" s="23" t="n"/>
+      <c r="I85" s="23" t="n"/>
+      <c r="J85" s="23" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Вн-10</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="F86" s="4">
+        <f>ROUND(E86-D86,2)</f>
+        <v/>
+      </c>
+      <c r="H86" s="23" t="n"/>
+      <c r="I86" s="23" t="n"/>
+      <c r="J86" s="23" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Вн-11</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="F87" s="4">
+        <f>ROUND(E87-D87,2)</f>
+        <v/>
+      </c>
+      <c r="H87" s="23" t="n"/>
+      <c r="I87" s="23" t="n"/>
+      <c r="J87" s="23" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Вн-12</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F88" s="4">
+        <f>ROUND(E88-D88,2)</f>
+        <v/>
+      </c>
+      <c r="H88" s="23" t="n"/>
+      <c r="I88" s="23" t="n"/>
+      <c r="J88" s="23" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="F89" s="4">
+        <f>ROUND(E89-D89,2)</f>
+        <v/>
+      </c>
+      <c r="H89" s="23" t="n"/>
+      <c r="I89" s="23" t="n"/>
+      <c r="J89" s="23" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Вн-20</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="F90" s="4">
+        <f>ROUND(E90-D90,2)</f>
+        <v/>
+      </c>
+      <c r="H90" s="23" t="n"/>
+      <c r="I90" s="23" t="n"/>
+      <c r="J90" s="23" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Вн-21</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="F91" s="4">
+        <f>ROUND(E91-D91,2)</f>
+        <v/>
+      </c>
+      <c r="H91" s="23" t="n"/>
+      <c r="I91" s="23" t="n"/>
+      <c r="J91" s="23" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="F92" s="4">
+        <f>ROUND(E92-D92,2)</f>
+        <v/>
+      </c>
+      <c r="H92" s="23" t="n"/>
+      <c r="I92" s="23" t="n"/>
+      <c r="J92" s="23" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Вн-7</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="F93" s="4">
+        <f>ROUND(E93-D93,2)</f>
+        <v/>
+      </c>
+      <c r="H93" s="23" t="n"/>
+      <c r="I93" s="23" t="n"/>
+      <c r="J93" s="23" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="F94" s="4">
+        <f>ROUND(E94-D94,2)</f>
+        <v/>
+      </c>
+      <c r="H94" s="23" t="n"/>
+      <c r="I94" s="23" t="n"/>
+      <c r="J94" s="23" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="F95" s="4">
+        <f>ROUND(E95-D95,2)</f>
+        <v/>
+      </c>
+      <c r="H95" s="23" t="n"/>
+      <c r="I95" s="23" t="n"/>
+      <c r="J95" s="23" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="n"/>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="n"/>
+      <c r="D96" s="22">
+        <f>SUM(D69:D95)</f>
+        <v/>
+      </c>
+      <c r="E96" s="22">
+        <f>SUM(E69:E95)</f>
+        <v/>
+      </c>
+      <c r="F96" s="22">
+        <f>SUM(F69:F95)</f>
+        <v/>
+      </c>
+      <c r="H96" s="23" t="n"/>
+      <c r="I96" s="23" t="n"/>
+      <c r="J96" s="23" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0"/>
+</worksheet>
 </file>
--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По литерам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Привязка к чертежам" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="В КП, не вошло" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сверка с КП" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сверка с ВДЦ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По литерам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Привязка к чертежам" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="В КП, не вошло" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сверка с КП" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +38,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,6 +111,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1433,6 +1455,2248 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Сверка спецификации с ВДЦ (Приложение № 2, лист «Корректировка»). К закрытию — меньшее из ВДЦ и спецификации, площадь по размерам ВДЦ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Строка ВДЦ — номер строки «Изготовление и монтаж» на листе «Корректировка»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="62" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Литер</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Размер по ВДЦ, мм</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Строка ВДЦ</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>По ВДЦ, шт</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>По ВДЦ, м²</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>По спецификации, шт</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Площадь по КП, м²</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>К закрытию, шт</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>К закрытию по ВДЦ, м²</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Не закрыто по ВДЦ, шт</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Сверх ВДЦ, шт</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Замечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="13">
+        <f>4.2*4.82*4</f>
+        <v/>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="J4" s="12">
+        <f>MIN(F4,N(H4))</f>
+        <v/>
+      </c>
+      <c r="K4" s="13">
+        <f>ROUND(G4/F4*J4,2)</f>
+        <v/>
+      </c>
+      <c r="L4" s="12">
+        <f>F4-J4</f>
+        <v/>
+      </c>
+      <c r="M4" s="12">
+        <f>N(H4)-J4</f>
+        <v/>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>1 шт. из КП перенесена в лит. Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Вн-8</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2600×4820</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <f>2.6*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="J5" s="3">
+        <f>MIN(F5,N(H5))</f>
+        <v/>
+      </c>
+      <c r="K5" s="5">
+        <f>ROUND(G5/F5*J5,2)</f>
+        <v/>
+      </c>
+      <c r="L5" s="3">
+        <f>F5-J5</f>
+        <v/>
+      </c>
+      <c r="M5" s="3">
+        <f>N(H5)-J5</f>
+        <v/>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Вн-14</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2485×4820</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <f>2.485*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="J6" s="3">
+        <f>MIN(F6,N(H6))</f>
+        <v/>
+      </c>
+      <c r="K6" s="5">
+        <f>ROUND(G6/F6*J6,2)</f>
+        <v/>
+      </c>
+      <c r="L6" s="3">
+        <f>F6-J6</f>
+        <v/>
+      </c>
+      <c r="M6" s="3">
+        <f>N(H6)-J6</f>
+        <v/>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 2320×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>1400×4820</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <f>1.4*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="J7" s="3">
+        <f>MIN(F7,N(H7))</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>ROUND(G7/F7*J7,2)</f>
+        <v/>
+      </c>
+      <c r="L7" s="3">
+        <f>F7-J7</f>
+        <v/>
+      </c>
+      <c r="M7" s="3">
+        <f>N(H7)-J7</f>
+        <v/>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 1170×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2150×2720</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="5">
+        <f>2.15*2.72*5</f>
+        <v/>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="J8" s="3">
+        <f>MIN(F8,N(H8))</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>ROUND(G8/F8*J8,2)</f>
+        <v/>
+      </c>
+      <c r="L8" s="3">
+        <f>F8-J8</f>
+        <v/>
+      </c>
+      <c r="M8" s="3">
+        <f>N(H8)-J8</f>
+        <v/>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Вн-23</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>3540×3020</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13">
+        <f>3.54*3.02*1</f>
+        <v/>
+      </c>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="12">
+        <f>MIN(F9,N(H9))</f>
+        <v/>
+      </c>
+      <c r="K9" s="13">
+        <f>ROUND(G9/F9*J9,2)</f>
+        <v/>
+      </c>
+      <c r="L9" s="12">
+        <f>F9-J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="12">
+        <f>N(H9)-J9</f>
+        <v/>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Вн-24</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>2610×3020</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="13">
+        <f>2.61*3.02*1</f>
+        <v/>
+      </c>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="12">
+        <f>MIN(F10,N(H10))</f>
+        <v/>
+      </c>
+      <c r="K10" s="13">
+        <f>ROUND(G10/F10*J10,2)</f>
+        <v/>
+      </c>
+      <c r="L10" s="12">
+        <f>F10-J10</f>
+        <v/>
+      </c>
+      <c r="M10" s="12">
+        <f>N(H10)-J10</f>
+        <v/>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="13">
+        <f>4.2*4.82*4</f>
+        <v/>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="J11" s="12">
+        <f>MIN(F11,N(H11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="13">
+        <f>ROUND(G11/F11*J11,2)</f>
+        <v/>
+      </c>
+      <c r="L11" s="12">
+        <f>F11-J11</f>
+        <v/>
+      </c>
+      <c r="M11" s="12">
+        <f>N(H11)-J11</f>
+        <v/>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>1 шт. из КП перенесена в лит. Г</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1400×4820</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <f>1.4*4.82</f>
+        <v/>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="3">
+        <f>MIN(F12,N(H12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="5">
+        <f>ROUND(G12/F12*J12,2)</f>
+        <v/>
+      </c>
+      <c r="L12" s="3">
+        <f>F12-J12</f>
+        <v/>
+      </c>
+      <c r="M12" s="3">
+        <f>N(H12)-J12</f>
+        <v/>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 1250×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
+        <f>4.2*4.82</f>
+        <v/>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="J13" s="3">
+        <f>MIN(F13,N(H13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="5">
+        <f>ROUND(G13/F13*J13,2)</f>
+        <v/>
+      </c>
+      <c r="L13" s="3">
+        <f>F13-J13</f>
+        <v/>
+      </c>
+      <c r="M13" s="3">
+        <f>N(H13)-J13</f>
+        <v/>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Вн-18</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2600×4820</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <f>2.6*4.82</f>
+        <v/>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J14" s="3">
+        <f>MIN(F14,N(H14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="5">
+        <f>ROUND(G14/F14*J14,2)</f>
+        <v/>
+      </c>
+      <c r="L14" s="3">
+        <f>F14-J14</f>
+        <v/>
+      </c>
+      <c r="M14" s="3">
+        <f>N(H14)-J14</f>
+        <v/>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 2480×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2150×2720</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="5">
+        <f>2.15*2.72*5</f>
+        <v/>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="J15" s="3">
+        <f>MIN(F15,N(H15))</f>
+        <v/>
+      </c>
+      <c r="K15" s="5">
+        <f>ROUND(G15/F15*J15,2)</f>
+        <v/>
+      </c>
+      <c r="L15" s="3">
+        <f>F15-J15</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
+        <f>N(H15)-J15</f>
+        <v/>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Вн-23</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>3540×3020</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="13">
+        <f>3.54*3.02*1</f>
+        <v/>
+      </c>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="12">
+        <f>MIN(F16,N(H16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="13">
+        <f>ROUND(G16/F16*J16,2)</f>
+        <v/>
+      </c>
+      <c r="L16" s="12">
+        <f>F16-J16</f>
+        <v/>
+      </c>
+      <c r="M16" s="12">
+        <f>N(H16)-J16</f>
+        <v/>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Вн-24</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2610×3020</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="13">
+        <f>2.61*3.02*1</f>
+        <v/>
+      </c>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="12">
+        <f>MIN(F17,N(H17))</f>
+        <v/>
+      </c>
+      <c r="K17" s="13">
+        <f>ROUND(G17/F17*J17,2)</f>
+        <v/>
+      </c>
+      <c r="L17" s="12">
+        <f>F17-J17</f>
+        <v/>
+      </c>
+      <c r="M17" s="12">
+        <f>N(H17)-J17</f>
+        <v/>
+      </c>
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
+        <f>4.2*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="J18" s="3">
+        <f>MIN(F18,N(H18))</f>
+        <v/>
+      </c>
+      <c r="K18" s="5">
+        <f>ROUND(G18/F18*J18,2)</f>
+        <v/>
+      </c>
+      <c r="L18" s="3">
+        <f>F18-J18</f>
+        <v/>
+      </c>
+      <c r="M18" s="3">
+        <f>N(H18)-J18</f>
+        <v/>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Вн-13</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>3200×4820</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <f>3.2*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="J19" s="3">
+        <f>MIN(F19,N(H19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="5">
+        <f>ROUND(G19/F19*J19,2)</f>
+        <v/>
+      </c>
+      <c r="L19" s="3">
+        <f>F19-J19</f>
+        <v/>
+      </c>
+      <c r="M19" s="3">
+        <f>N(H19)-J19</f>
+        <v/>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>1200×4820</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="13">
+        <f>1.2*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="J20" s="12">
+        <f>MIN(F20,N(H20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="13">
+        <f>ROUND(G20/F20*J20,2)</f>
+        <v/>
+      </c>
+      <c r="L20" s="12">
+        <f>F20-J20</f>
+        <v/>
+      </c>
+      <c r="M20" s="12">
+        <f>N(H20)-J20</f>
+        <v/>
+      </c>
+      <c r="N20" s="14" t="inlineStr">
+        <is>
+          <t>по чертежу и КП 3 шт., в ВДЦ 1; размер по КП 1060×5180, 1240×4800, 1370×5200 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="12">
+        <f>N(H21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="14" t="inlineStr">
+        <is>
+          <t>в ВДЦ лит. В нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>3000×4820</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="5">
+        <f>3*4.82*2</f>
+        <v/>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="J22" s="3">
+        <f>MIN(F22,N(H22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="5">
+        <f>ROUND(G22/F22*J22,2)</f>
+        <v/>
+      </c>
+      <c r="L22" s="3">
+        <f>F22-J22</f>
+        <v/>
+      </c>
+      <c r="M22" s="3">
+        <f>N(H22)-J22</f>
+        <v/>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 2570×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2150×2720</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="13">
+        <f>2.15*2.72*4</f>
+        <v/>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="J23" s="12">
+        <f>MIN(F23,N(H23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="13">
+        <f>ROUND(G23/F23*J23,2)</f>
+        <v/>
+      </c>
+      <c r="L23" s="12">
+        <f>F23-J23</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>N(H23)-J23</f>
+        <v/>
+      </c>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>в ВДЦ 4, в спецификации 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="13">
+        <f>4.2*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="J24" s="12">
+        <f>MIN(F24,N(H24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="13">
+        <f>ROUND(G24/F24*J24,2)</f>
+        <v/>
+      </c>
+      <c r="L24" s="12">
+        <f>F24-J24</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>N(H24)-J24</f>
+        <v/>
+      </c>
+      <c r="N24" s="14" t="inlineStr">
+        <is>
+          <t>2 шт. перенесены из КП лит. А и Б; в ВДЦ лит. Г — 1 шт., зато в ВДЦ А и Б по 4 шт. (не закрыто по 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Вн-10</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>4160×4820</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
+        <f>4.16*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="J25" s="3">
+        <f>MIN(F25,N(H25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="5">
+        <f>ROUND(G25/F25*J25,2)</f>
+        <v/>
+      </c>
+      <c r="L25" s="3">
+        <f>F25-J25</f>
+        <v/>
+      </c>
+      <c r="M25" s="3">
+        <f>N(H25)-J25</f>
+        <v/>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Вн-11</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2450×4820</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5">
+        <f>2.45*4.82</f>
+        <v/>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J26" s="3">
+        <f>MIN(F26,N(H26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="5">
+        <f>ROUND(G26/F26*J26,2)</f>
+        <v/>
+      </c>
+      <c r="L26" s="3">
+        <f>F26-J26</f>
+        <v/>
+      </c>
+      <c r="M26" s="3">
+        <f>N(H26)-J26</f>
+        <v/>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 2310×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Вн-12</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>3370×4820</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5">
+        <f>3.37*4.82</f>
+        <v/>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J27" s="3">
+        <f>MIN(F27,N(H27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="5">
+        <f>ROUND(G27/F27*J27,2)</f>
+        <v/>
+      </c>
+      <c r="L27" s="3">
+        <f>F27-J27</f>
+        <v/>
+      </c>
+      <c r="M27" s="3">
+        <f>N(H27)-J27</f>
+        <v/>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5">
+        <f>4.2*4.82</f>
+        <v/>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="J28" s="3">
+        <f>MIN(F28,N(H28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="5">
+        <f>ROUND(G28/F28*J28,2)</f>
+        <v/>
+      </c>
+      <c r="L28" s="3">
+        <f>F28-J28</f>
+        <v/>
+      </c>
+      <c r="M28" s="3">
+        <f>N(H28)-J28</f>
+        <v/>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Вн-20</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>3900×4820</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5">
+        <f>3.9*4.82</f>
+        <v/>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="J29" s="3">
+        <f>MIN(F29,N(H29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="5">
+        <f>ROUND(G29/F29*J29,2)</f>
+        <v/>
+      </c>
+      <c r="L29" s="3">
+        <f>F29-J29</f>
+        <v/>
+      </c>
+      <c r="M29" s="3">
+        <f>N(H29)-J29</f>
+        <v/>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Вн-21</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2920×4820</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5">
+        <f>2.92*4.82</f>
+        <v/>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="J30" s="3">
+        <f>MIN(F30,N(H30))</f>
+        <v/>
+      </c>
+      <c r="K30" s="5">
+        <f>ROUND(G30/F30*J30,2)</f>
+        <v/>
+      </c>
+      <c r="L30" s="3">
+        <f>F30-J30</f>
+        <v/>
+      </c>
+      <c r="M30" s="3">
+        <f>N(H30)-J30</f>
+        <v/>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2150×2720</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="13">
+        <f>2.15*2.72*4</f>
+        <v/>
+      </c>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="12">
+        <f>MIN(F31,N(H31))</f>
+        <v/>
+      </c>
+      <c r="K31" s="13">
+        <f>ROUND(G31/F31*J31,2)</f>
+        <v/>
+      </c>
+      <c r="L31" s="12">
+        <f>F31-J31</f>
+        <v/>
+      </c>
+      <c r="M31" s="12">
+        <f>N(H31)-J31</f>
+        <v/>
+      </c>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="5">
+        <f>4.2*4.82*2</f>
+        <v/>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="J32" s="3">
+        <f>MIN(F32,N(H32))</f>
+        <v/>
+      </c>
+      <c r="K32" s="5">
+        <f>ROUND(G32/F32*J32,2)</f>
+        <v/>
+      </c>
+      <c r="L32" s="3">
+        <f>F32-J32</f>
+        <v/>
+      </c>
+      <c r="M32" s="3">
+        <f>N(H32)-J32</f>
+        <v/>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Вн-7</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>3020×4820</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5">
+        <f>3.02*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="J33" s="3">
+        <f>MIN(F33,N(H33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="5">
+        <f>ROUND(G33/F33*J33,2)</f>
+        <v/>
+      </c>
+      <c r="L33" s="3">
+        <f>F33-J33</f>
+        <v/>
+      </c>
+      <c r="M33" s="3">
+        <f>N(H33)-J33</f>
+        <v/>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 4160×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>3870×4820</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5">
+        <f>3.87*4.82</f>
+        <v/>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="J34" s="3">
+        <f>MIN(F34,N(H34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="5">
+        <f>ROUND(G34/F34*J34,2)</f>
+        <v/>
+      </c>
+      <c r="L34" s="3">
+        <f>F34-J34</f>
+        <v/>
+      </c>
+      <c r="M34" s="3">
+        <f>N(H34)-J34</f>
+        <v/>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 4100×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5">
+        <f>4.2*4.82</f>
+        <v/>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="J35" s="3">
+        <f>MIN(F35,N(H35))</f>
+        <v/>
+      </c>
+      <c r="K35" s="5">
+        <f>ROUND(G35/F35*J35,2)</f>
+        <v/>
+      </c>
+      <c r="L35" s="3">
+        <f>F35-J35</f>
+        <v/>
+      </c>
+      <c r="M35" s="3">
+        <f>N(H35)-J35</f>
+        <v/>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>кол-во совпадает; размер по КП 3780×4800 — отличается от ВДЦ более чем на 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Вн-1</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>4750×3870</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>136</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="13">
+        <f>4.75*3.87</f>
+        <v/>
+      </c>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="13" t="n"/>
+      <c r="J36" s="12">
+        <f>MIN(F36,N(H36))</f>
+        <v/>
+      </c>
+      <c r="K36" s="13">
+        <f>ROUND(G36/F36*J36,2)</f>
+        <v/>
+      </c>
+      <c r="L36" s="12">
+        <f>F36-J36</f>
+        <v/>
+      </c>
+      <c r="M36" s="12">
+        <f>N(H36)-J36</f>
+        <v/>
+      </c>
+      <c r="N36" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Вн-2</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>4750×3870</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="13">
+        <f>4.75*3.87</f>
+        <v/>
+      </c>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="13" t="n"/>
+      <c r="J37" s="12">
+        <f>MIN(F37,N(H37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="13">
+        <f>ROUND(G37/F37*J37,2)</f>
+        <v/>
+      </c>
+      <c r="L37" s="12">
+        <f>F37-J37</f>
+        <v/>
+      </c>
+      <c r="M37" s="12">
+        <f>N(H37)-J37</f>
+        <v/>
+      </c>
+      <c r="N37" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Вн-3</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>6100×3870</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="13">
+        <f>6.1*3.87</f>
+        <v/>
+      </c>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="12">
+        <f>MIN(F38,N(H38))</f>
+        <v/>
+      </c>
+      <c r="K38" s="13">
+        <f>ROUND(G38/F38*J38,2)</f>
+        <v/>
+      </c>
+      <c r="L38" s="12">
+        <f>F38-J38</f>
+        <v/>
+      </c>
+      <c r="M38" s="12">
+        <f>N(H38)-J38</f>
+        <v/>
+      </c>
+      <c r="N38" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Вн-4</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>5400×3470</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="13">
+        <f>5.4*3.47*1</f>
+        <v/>
+      </c>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="12">
+        <f>MIN(F39,N(H39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="13">
+        <f>ROUND(G39/F39*J39,2)</f>
+        <v/>
+      </c>
+      <c r="L39" s="12">
+        <f>F39-J39</f>
+        <v/>
+      </c>
+      <c r="M39" s="12">
+        <f>N(H39)-J39</f>
+        <v/>
+      </c>
+      <c r="N39" s="14" t="inlineStr">
+        <is>
+          <t>нет в спецификации (нет в КП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Вн-5</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>7800×3470</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="13">
+        <f>7.8*3.4</f>
+        <v/>
+      </c>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="13" t="n"/>
+      <c r="J40" s="12">
+        <f>MIN(F40,N(H40))</f>
+        <v/>
+      </c>
+      <c r="K40" s="13">
+        <f>ROUND(G40/F40*J40,2)</f>
+        <v/>
+      </c>
+      <c r="L40" s="12">
+        <f>F40-J40</f>
+        <v/>
+      </c>
+      <c r="M40" s="12">
+        <f>N(H40)-J40</f>
+        <v/>
+      </c>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>в ВДЦ площадь =7.8*3.4 (26,52), а в названии 7800х3470 (27,07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="8">
+        <f>SUM(F4:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="10">
+        <f>SUM(G4:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="8">
+        <f>SUM(H4:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="10">
+        <f>SUM(I4:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="8">
+        <f>SUM(J4:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="10">
+        <f>SUM(K4:K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="8">
+        <f>SUM(L4:L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="8">
+        <f>SUM(M4:M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="11" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Вариант: 2 шт. Вн-6 лит. Г закрыть по строкам ВДЦ лит. А и Б (там не закрыто по 1 шт.) — дополнительно, м²:</t>
+        </is>
+      </c>
+      <c r="K43" s="16">
+        <f>ROUND(4.2*4.82*2,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Итого к закрытию с этим вариантом, м²:</t>
+        </is>
+      </c>
+      <c r="K44" s="16">
+        <f>K41+K43</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="B44:J44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H43"/>
@@ -1499,17 +3763,17 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Литер А</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="13" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="19" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1688,17 +3952,17 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Литер Б</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="13" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="19" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1877,17 +4141,17 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Литер В</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="13" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="19" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -2097,17 +4361,17 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Литер Г</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="13" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="19" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -2410,17 +4674,17 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>Литер Д</t>
         </is>
       </c>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="15" t="n"/>
-      <c r="H37" s="13" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="21" t="n"/>
+      <c r="H37" s="19" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -2568,7 +4832,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>ВСЕГО</t>
         </is>
@@ -2576,11 +4840,11 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="4" t="n"/>
-      <c r="F43" s="16">
+      <c r="F43" s="22">
         <f>F10+F17+F25+F36+F42</f>
         <v/>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="23">
         <f>G10+G17+G25+G36+G42</f>
         <v/>
       </c>
@@ -2598,7 +4862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2618,7 +4882,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Витражи на чертежах, входящие в КП (координаты — точка выноски, мм)</t>
         </is>
@@ -2697,10 +4961,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="25" t="n">
         <v>129957</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2733,10 +4997,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="25" t="n">
         <v>140357</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2769,10 +5033,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="25" t="n">
         <v>150757</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2801,10 +5065,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="25" t="n">
         <v>144757</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2837,10 +5101,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="25" t="n">
         <v>134299</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -2873,10 +5137,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="25" t="n">
         <v>136557</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -2909,10 +5173,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="25" t="n">
         <v>118357</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2945,10 +5209,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="25" t="n">
         <v>96357</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -2981,10 +5245,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="25" t="n">
         <v>106757</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -3017,10 +5281,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="25" t="n">
         <v>103802</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="25" t="n">
         <v>-240189</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -3049,10 +5313,10 @@
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="25" t="n">
         <v>111957</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -3085,10 +5349,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="25" t="n">
         <v>101557</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3121,10 +5385,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="25" t="n">
         <v>85312</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -3153,10 +5417,10 @@
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="25" t="n">
         <v>62827</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -3189,10 +5453,10 @@
           <t>Д35</t>
         </is>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="25" t="n">
         <v>75379</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -3225,10 +5489,10 @@
           <t>Д35</t>
         </is>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="25" t="n">
         <v>58219</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="25" t="n">
         <v>-240238</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3261,10 +5525,10 @@
           <t>Д35</t>
         </is>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="25" t="n">
         <v>60392</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="25" t="n">
         <v>-240238</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -3297,10 +5561,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="25" t="n">
         <v>78410</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G21" s="25" t="n">
         <v>-240123</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3329,10 +5593,10 @@
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="25" t="n">
         <v>66863</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G22" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3365,10 +5629,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="25" t="n">
         <v>72058</v>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G23" s="25" t="n">
         <v>-240209</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3401,10 +5665,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="25" t="n">
         <v>38425</v>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="25" t="n">
         <v>-227349</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -3437,10 +5701,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="25" t="n">
         <v>43228</v>
       </c>
-      <c r="G25" s="19" t="n">
+      <c r="G25" s="25" t="n">
         <v>-240130</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -3473,10 +5737,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="25" t="n">
         <v>53628</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="25" t="n">
         <v>-240130</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3509,10 +5773,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="25" t="n">
         <v>38425</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G27" s="25" t="n">
         <v>-203499</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -3541,10 +5805,10 @@
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="25" t="n">
         <v>38425</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G28" s="25" t="n">
         <v>-213004</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -3577,10 +5841,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="25" t="n">
         <v>38425</v>
       </c>
-      <c r="G29" s="19" t="n">
+      <c r="G29" s="25" t="n">
         <v>-217364</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -3609,10 +5873,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="25" t="n">
         <v>38425</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="25" t="n">
         <v>-237749</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -3641,10 +5905,10 @@
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="25" t="n">
         <v>47835</v>
       </c>
-      <c r="G31" s="19" t="n">
+      <c r="G31" s="25" t="n">
         <v>-240108</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -3673,10 +5937,10 @@
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="25" t="n">
         <v>38425</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G32" s="25" t="n">
         <v>-221999</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -3705,10 +5969,10 @@
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="19" t="n">
+      <c r="F33" s="25" t="n">
         <v>38425</v>
       </c>
-      <c r="G33" s="19" t="n">
+      <c r="G33" s="25" t="n">
         <v>-231909</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -3737,10 +6001,10 @@
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="25" t="n">
         <v>38538</v>
       </c>
-      <c r="G34" s="19" t="n">
+      <c r="G34" s="25" t="n">
         <v>-179543</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -3769,10 +6033,10 @@
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="19" t="n">
+      <c r="F35" s="25" t="n">
         <v>38538</v>
       </c>
-      <c r="G35" s="19" t="n">
+      <c r="G35" s="25" t="n">
         <v>-169143</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -3801,10 +6065,10 @@
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="19" t="n">
+      <c r="F36" s="25" t="n">
         <v>38538</v>
       </c>
-      <c r="G36" s="19" t="n">
+      <c r="G36" s="25" t="n">
         <v>-174933</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -3837,10 +6101,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F37" s="19" t="n">
+      <c r="F37" s="25" t="n">
         <v>38538</v>
       </c>
-      <c r="G37" s="19" t="n">
+      <c r="G37" s="25" t="n">
         <v>-195128</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -3869,10 +6133,10 @@
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="19" t="n">
+      <c r="F38" s="25" t="n">
         <v>38538</v>
       </c>
-      <c r="G38" s="19" t="n">
+      <c r="G38" s="25" t="n">
         <v>-189943</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -3905,10 +6169,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F39" s="19" t="n">
+      <c r="F39" s="25" t="n">
         <v>112864</v>
       </c>
-      <c r="G39" s="19" t="n">
+      <c r="G39" s="25" t="n">
         <v>2824</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -3941,10 +6205,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F40" s="19" t="n">
+      <c r="F40" s="25" t="n">
         <v>106184</v>
       </c>
-      <c r="G40" s="19" t="n">
+      <c r="G40" s="25" t="n">
         <v>2691</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -3977,10 +6241,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F41" s="19" t="n">
+      <c r="F41" s="25" t="n">
         <v>100327</v>
       </c>
-      <c r="G41" s="19" t="n">
+      <c r="G41" s="25" t="n">
         <v>2943</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -4013,10 +6277,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F42" s="19" t="n">
+      <c r="F42" s="25" t="n">
         <v>93122</v>
       </c>
-      <c r="G42" s="19" t="n">
+      <c r="G42" s="25" t="n">
         <v>2886</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -4049,10 +6313,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F43" s="19" t="n">
+      <c r="F43" s="25" t="n">
         <v>86467</v>
       </c>
-      <c r="G43" s="19" t="n">
+      <c r="G43" s="25" t="n">
         <v>2773</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -4085,10 +6349,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F44" s="19" t="n">
+      <c r="F44" s="25" t="n">
         <v>79305</v>
       </c>
-      <c r="G44" s="19" t="n">
+      <c r="G44" s="25" t="n">
         <v>3099</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -4121,10 +6385,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F45" s="19" t="n">
+      <c r="F45" s="25" t="n">
         <v>72445</v>
       </c>
-      <c r="G45" s="19" t="n">
+      <c r="G45" s="25" t="n">
         <v>3048</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -4157,10 +6421,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F46" s="19" t="n">
+      <c r="F46" s="25" t="n">
         <v>64804</v>
       </c>
-      <c r="G46" s="19" t="n">
+      <c r="G46" s="25" t="n">
         <v>2917</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -4193,10 +6457,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F47" s="19" t="n">
+      <c r="F47" s="25" t="n">
         <v>59604</v>
       </c>
-      <c r="G47" s="19" t="n">
+      <c r="G47" s="25" t="n">
         <v>2985</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -4229,10 +6493,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F48" s="19" t="n">
+      <c r="F48" s="25" t="n">
         <v>53064</v>
       </c>
-      <c r="G48" s="19" t="n">
+      <c r="G48" s="25" t="n">
         <v>2948</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -4265,10 +6529,10 @@
           <t>Д35</t>
         </is>
       </c>
-      <c r="F49" s="19" t="n">
+      <c r="F49" s="25" t="n">
         <v>45611</v>
       </c>
-      <c r="G49" s="19" t="n">
+      <c r="G49" s="25" t="n">
         <v>3036</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -4301,10 +6565,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F50" s="19" t="n">
+      <c r="F50" s="25" t="n">
         <v>39399</v>
       </c>
-      <c r="G50" s="19" t="n">
+      <c r="G50" s="25" t="n">
         <v>2969</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -4337,10 +6601,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F51" s="19" t="n">
+      <c r="F51" s="25" t="n">
         <v>33459</v>
       </c>
-      <c r="G51" s="19" t="n">
+      <c r="G51" s="25" t="n">
         <v>3046</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -4373,10 +6637,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F52" s="19" t="n">
+      <c r="F52" s="25" t="n">
         <v>26027</v>
       </c>
-      <c r="G52" s="19" t="n">
+      <c r="G52" s="25" t="n">
         <v>2978</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -4390,7 +6654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4906,7 +7170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4929,7 +7193,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Сверка с КП. В спецификации площадь по КП = ширина × высота из КП (как в таблице заказчика)</t>
         </is>
@@ -4943,7 +7207,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>1. Позиции КП на витражи</t>
         </is>
@@ -4985,17 +7249,17 @@
           <t>Кол-во, шт</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>Площадь по размерам КП, м²</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t>Площадь в КП, м²</t>
         </is>
       </c>
-      <c r="J4" s="20" t="inlineStr">
+      <c r="J4" s="26" t="inlineStr">
         <is>
           <t>Разница, м²</t>
         </is>
@@ -6856,48 +9120,48 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="n"/>
+      <c r="A48" s="27" t="n"/>
       <c r="B48" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
+      <c r="C48" s="27" t="n"/>
+      <c r="D48" s="27" t="n"/>
+      <c r="E48" s="27" t="n"/>
+      <c r="F48" s="27" t="n"/>
       <c r="G48" s="8">
         <f>SUM(G5:G47)</f>
         <v/>
       </c>
-      <c r="H48" s="22">
+      <c r="H48" s="28">
         <f>SUM(H5:H47)</f>
         <v/>
       </c>
-      <c r="I48" s="22">
+      <c r="I48" s="28">
         <f>SUM(I5:I47)</f>
         <v/>
       </c>
-      <c r="J48" s="22">
+      <c r="J48" s="28">
         <f>SUM(J5:J47)</f>
         <v/>
       </c>
-      <c r="K48" s="21" t="n"/>
+      <c r="K48" s="27" t="n"/>
     </row>
     <row r="49">
-      <c r="H49" s="23" t="n"/>
-      <c r="I49" s="23" t="n"/>
-      <c r="J49" s="23" t="n"/>
+      <c r="H49" s="29" t="n"/>
+      <c r="I49" s="29" t="n"/>
+      <c r="J49" s="29" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="24" t="inlineStr">
         <is>
           <t>2. Двери к витражам (КП от 13.04.2026) — в спецификацию не добавлены, для справки</t>
         </is>
       </c>
-      <c r="H50" s="23" t="n"/>
-      <c r="I50" s="23" t="n"/>
-      <c r="J50" s="23" t="n"/>
+      <c r="H50" s="29" t="n"/>
+      <c r="I50" s="29" t="n"/>
+      <c r="J50" s="29" t="n"/>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -6935,17 +9199,17 @@
           <t>Кол-во, шт</t>
         </is>
       </c>
-      <c r="H51" s="20" t="inlineStr">
+      <c r="H51" s="26" t="inlineStr">
         <is>
           <t>Площадь по размерам, м²</t>
         </is>
       </c>
-      <c r="I51" s="20" t="inlineStr">
+      <c r="I51" s="26" t="inlineStr">
         <is>
           <t>Площадь в КП, м²</t>
         </is>
       </c>
-      <c r="J51" s="23" t="n"/>
+      <c r="J51" s="29" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -6982,7 +9246,7 @@
       <c r="I52" s="4" t="n">
         <v>9.75</v>
       </c>
-      <c r="J52" s="23" t="n"/>
+      <c r="J52" s="29" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -7019,7 +9283,7 @@
       <c r="I53" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J53" s="23" t="n"/>
+      <c r="J53" s="29" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -7056,7 +9320,7 @@
       <c r="I54" s="4" t="n">
         <v>2.69</v>
       </c>
-      <c r="J54" s="23" t="n"/>
+      <c r="J54" s="29" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -7093,7 +9357,7 @@
       <c r="I55" s="4" t="n">
         <v>9.75</v>
       </c>
-      <c r="J55" s="23" t="n"/>
+      <c r="J55" s="29" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -7130,7 +9394,7 @@
       <c r="I56" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J56" s="23" t="n"/>
+      <c r="J56" s="29" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -7167,7 +9431,7 @@
       <c r="I57" s="4" t="n">
         <v>2.89</v>
       </c>
-      <c r="J57" s="23" t="n"/>
+      <c r="J57" s="29" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -7204,7 +9468,7 @@
       <c r="I58" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J58" s="23" t="n"/>
+      <c r="J58" s="29" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -7241,7 +9505,7 @@
       <c r="I59" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="J59" s="23" t="n"/>
+      <c r="J59" s="29" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -7278,7 +9542,7 @@
       <c r="I60" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J60" s="23" t="n"/>
+      <c r="J60" s="29" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -7315,7 +9579,7 @@
       <c r="I61" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J61" s="23" t="n"/>
+      <c r="J61" s="29" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -7352,7 +9616,7 @@
       <c r="I62" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="J62" s="23" t="n"/>
+      <c r="J62" s="29" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -7389,7 +9653,7 @@
       <c r="I63" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="J63" s="23" t="n"/>
+      <c r="J63" s="29" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -7426,47 +9690,47 @@
       <c r="I64" s="4" t="n">
         <v>32.23</v>
       </c>
-      <c r="J64" s="23" t="n"/>
+      <c r="J64" s="29" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="21" t="n"/>
+      <c r="A65" s="27" t="n"/>
       <c r="B65" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="21" t="n"/>
+      <c r="C65" s="27" t="n"/>
+      <c r="D65" s="27" t="n"/>
+      <c r="E65" s="27" t="n"/>
+      <c r="F65" s="27" t="n"/>
       <c r="G65" s="8">
         <f>SUM(G52:G64)</f>
         <v/>
       </c>
-      <c r="H65" s="22">
+      <c r="H65" s="28">
         <f>SUM(H52:H64)</f>
         <v/>
       </c>
-      <c r="I65" s="22">
+      <c r="I65" s="28">
         <f>SUM(I52:I64)</f>
         <v/>
       </c>
-      <c r="J65" s="23" t="n"/>
+      <c r="J65" s="29" t="n"/>
     </row>
     <row r="66">
-      <c r="H66" s="23" t="n"/>
-      <c r="I66" s="23" t="n"/>
-      <c r="J66" s="23" t="n"/>
+      <c r="H66" s="29" t="n"/>
+      <c r="I66" s="29" t="n"/>
+      <c r="J66" s="29" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="24" t="inlineStr">
         <is>
           <t>3. Что поправлено в спецификации</t>
         </is>
       </c>
-      <c r="H67" s="23" t="n"/>
-      <c r="I67" s="23" t="n"/>
-      <c r="J67" s="23" t="n"/>
+      <c r="H67" s="29" t="n"/>
+      <c r="I67" s="29" t="n"/>
+      <c r="J67" s="29" t="n"/>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -7499,9 +9763,9 @@
           <t>Разница, м²</t>
         </is>
       </c>
-      <c r="H68" s="23" t="n"/>
-      <c r="I68" s="23" t="n"/>
-      <c r="J68" s="23" t="n"/>
+      <c r="H68" s="29" t="n"/>
+      <c r="I68" s="29" t="n"/>
+      <c r="J68" s="29" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -7527,9 +9791,9 @@
         <f>ROUND(E69-D69,2)</f>
         <v/>
       </c>
-      <c r="H69" s="23" t="n"/>
-      <c r="I69" s="23" t="n"/>
-      <c r="J69" s="23" t="n"/>
+      <c r="H69" s="29" t="n"/>
+      <c r="I69" s="29" t="n"/>
+      <c r="J69" s="29" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -7555,9 +9819,9 @@
         <f>ROUND(E70-D70,2)</f>
         <v/>
       </c>
-      <c r="H70" s="23" t="n"/>
-      <c r="I70" s="23" t="n"/>
-      <c r="J70" s="23" t="n"/>
+      <c r="H70" s="29" t="n"/>
+      <c r="I70" s="29" t="n"/>
+      <c r="J70" s="29" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -7583,9 +9847,9 @@
         <f>ROUND(E71-D71,2)</f>
         <v/>
       </c>
-      <c r="H71" s="23" t="n"/>
-      <c r="I71" s="23" t="n"/>
-      <c r="J71" s="23" t="n"/>
+      <c r="H71" s="29" t="n"/>
+      <c r="I71" s="29" t="n"/>
+      <c r="J71" s="29" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -7611,9 +9875,9 @@
         <f>ROUND(E72-D72,2)</f>
         <v/>
       </c>
-      <c r="H72" s="23" t="n"/>
-      <c r="I72" s="23" t="n"/>
-      <c r="J72" s="23" t="n"/>
+      <c r="H72" s="29" t="n"/>
+      <c r="I72" s="29" t="n"/>
+      <c r="J72" s="29" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -7639,9 +9903,9 @@
         <f>ROUND(E73-D73,2)</f>
         <v/>
       </c>
-      <c r="H73" s="23" t="n"/>
-      <c r="I73" s="23" t="n"/>
-      <c r="J73" s="23" t="n"/>
+      <c r="H73" s="29" t="n"/>
+      <c r="I73" s="29" t="n"/>
+      <c r="J73" s="29" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -7667,9 +9931,9 @@
         <f>ROUND(E74-D74,2)</f>
         <v/>
       </c>
-      <c r="H74" s="23" t="n"/>
-      <c r="I74" s="23" t="n"/>
-      <c r="J74" s="23" t="n"/>
+      <c r="H74" s="29" t="n"/>
+      <c r="I74" s="29" t="n"/>
+      <c r="J74" s="29" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -7695,9 +9959,9 @@
         <f>ROUND(E75-D75,2)</f>
         <v/>
       </c>
-      <c r="H75" s="23" t="n"/>
-      <c r="I75" s="23" t="n"/>
-      <c r="J75" s="23" t="n"/>
+      <c r="H75" s="29" t="n"/>
+      <c r="I75" s="29" t="n"/>
+      <c r="J75" s="29" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -7723,9 +9987,9 @@
         <f>ROUND(E76-D76,2)</f>
         <v/>
       </c>
-      <c r="H76" s="23" t="n"/>
-      <c r="I76" s="23" t="n"/>
-      <c r="J76" s="23" t="n"/>
+      <c r="H76" s="29" t="n"/>
+      <c r="I76" s="29" t="n"/>
+      <c r="J76" s="29" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -7751,9 +10015,9 @@
         <f>ROUND(E77-D77,2)</f>
         <v/>
       </c>
-      <c r="H77" s="23" t="n"/>
-      <c r="I77" s="23" t="n"/>
-      <c r="J77" s="23" t="n"/>
+      <c r="H77" s="29" t="n"/>
+      <c r="I77" s="29" t="n"/>
+      <c r="J77" s="29" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -7779,9 +10043,9 @@
         <f>ROUND(E78-D78,2)</f>
         <v/>
       </c>
-      <c r="H78" s="23" t="n"/>
-      <c r="I78" s="23" t="n"/>
-      <c r="J78" s="23" t="n"/>
+      <c r="H78" s="29" t="n"/>
+      <c r="I78" s="29" t="n"/>
+      <c r="J78" s="29" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -7807,9 +10071,9 @@
         <f>ROUND(E79-D79,2)</f>
         <v/>
       </c>
-      <c r="H79" s="23" t="n"/>
-      <c r="I79" s="23" t="n"/>
-      <c r="J79" s="23" t="n"/>
+      <c r="H79" s="29" t="n"/>
+      <c r="I79" s="29" t="n"/>
+      <c r="J79" s="29" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -7835,9 +10099,9 @@
         <f>ROUND(E80-D80,2)</f>
         <v/>
       </c>
-      <c r="H80" s="23" t="n"/>
-      <c r="I80" s="23" t="n"/>
-      <c r="J80" s="23" t="n"/>
+      <c r="H80" s="29" t="n"/>
+      <c r="I80" s="29" t="n"/>
+      <c r="J80" s="29" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -7863,9 +10127,9 @@
         <f>ROUND(E81-D81,2)</f>
         <v/>
       </c>
-      <c r="H81" s="23" t="n"/>
-      <c r="I81" s="23" t="n"/>
-      <c r="J81" s="23" t="n"/>
+      <c r="H81" s="29" t="n"/>
+      <c r="I81" s="29" t="n"/>
+      <c r="J81" s="29" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -7891,9 +10155,9 @@
         <f>ROUND(E82-D82,2)</f>
         <v/>
       </c>
-      <c r="H82" s="23" t="n"/>
-      <c r="I82" s="23" t="n"/>
-      <c r="J82" s="23" t="n"/>
+      <c r="H82" s="29" t="n"/>
+      <c r="I82" s="29" t="n"/>
+      <c r="J82" s="29" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
@@ -7919,9 +10183,9 @@
         <f>ROUND(E83-D83,2)</f>
         <v/>
       </c>
-      <c r="H83" s="23" t="n"/>
-      <c r="I83" s="23" t="n"/>
-      <c r="J83" s="23" t="n"/>
+      <c r="H83" s="29" t="n"/>
+      <c r="I83" s="29" t="n"/>
+      <c r="J83" s="29" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -7947,9 +10211,9 @@
         <f>ROUND(E84-D84,2)</f>
         <v/>
       </c>
-      <c r="H84" s="23" t="n"/>
-      <c r="I84" s="23" t="n"/>
-      <c r="J84" s="23" t="n"/>
+      <c r="H84" s="29" t="n"/>
+      <c r="I84" s="29" t="n"/>
+      <c r="J84" s="29" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -7975,9 +10239,9 @@
         <f>ROUND(E85-D85,2)</f>
         <v/>
       </c>
-      <c r="H85" s="23" t="n"/>
-      <c r="I85" s="23" t="n"/>
-      <c r="J85" s="23" t="n"/>
+      <c r="H85" s="29" t="n"/>
+      <c r="I85" s="29" t="n"/>
+      <c r="J85" s="29" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -8003,9 +10267,9 @@
         <f>ROUND(E86-D86,2)</f>
         <v/>
       </c>
-      <c r="H86" s="23" t="n"/>
-      <c r="I86" s="23" t="n"/>
-      <c r="J86" s="23" t="n"/>
+      <c r="H86" s="29" t="n"/>
+      <c r="I86" s="29" t="n"/>
+      <c r="J86" s="29" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
@@ -8031,9 +10295,9 @@
         <f>ROUND(E87-D87,2)</f>
         <v/>
       </c>
-      <c r="H87" s="23" t="n"/>
-      <c r="I87" s="23" t="n"/>
-      <c r="J87" s="23" t="n"/>
+      <c r="H87" s="29" t="n"/>
+      <c r="I87" s="29" t="n"/>
+      <c r="J87" s="29" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -8059,9 +10323,9 @@
         <f>ROUND(E88-D88,2)</f>
         <v/>
       </c>
-      <c r="H88" s="23" t="n"/>
-      <c r="I88" s="23" t="n"/>
-      <c r="J88" s="23" t="n"/>
+      <c r="H88" s="29" t="n"/>
+      <c r="I88" s="29" t="n"/>
+      <c r="J88" s="29" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
@@ -8087,9 +10351,9 @@
         <f>ROUND(E89-D89,2)</f>
         <v/>
       </c>
-      <c r="H89" s="23" t="n"/>
-      <c r="I89" s="23" t="n"/>
-      <c r="J89" s="23" t="n"/>
+      <c r="H89" s="29" t="n"/>
+      <c r="I89" s="29" t="n"/>
+      <c r="J89" s="29" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
@@ -8115,9 +10379,9 @@
         <f>ROUND(E90-D90,2)</f>
         <v/>
       </c>
-      <c r="H90" s="23" t="n"/>
-      <c r="I90" s="23" t="n"/>
-      <c r="J90" s="23" t="n"/>
+      <c r="H90" s="29" t="n"/>
+      <c r="I90" s="29" t="n"/>
+      <c r="J90" s="29" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
@@ -8143,9 +10407,9 @@
         <f>ROUND(E91-D91,2)</f>
         <v/>
       </c>
-      <c r="H91" s="23" t="n"/>
-      <c r="I91" s="23" t="n"/>
-      <c r="J91" s="23" t="n"/>
+      <c r="H91" s="29" t="n"/>
+      <c r="I91" s="29" t="n"/>
+      <c r="J91" s="29" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
@@ -8171,9 +10435,9 @@
         <f>ROUND(E92-D92,2)</f>
         <v/>
       </c>
-      <c r="H92" s="23" t="n"/>
-      <c r="I92" s="23" t="n"/>
-      <c r="J92" s="23" t="n"/>
+      <c r="H92" s="29" t="n"/>
+      <c r="I92" s="29" t="n"/>
+      <c r="J92" s="29" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
@@ -8199,9 +10463,9 @@
         <f>ROUND(E93-D93,2)</f>
         <v/>
       </c>
-      <c r="H93" s="23" t="n"/>
-      <c r="I93" s="23" t="n"/>
-      <c r="J93" s="23" t="n"/>
+      <c r="H93" s="29" t="n"/>
+      <c r="I93" s="29" t="n"/>
+      <c r="J93" s="29" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -8227,9 +10491,9 @@
         <f>ROUND(E94-D94,2)</f>
         <v/>
       </c>
-      <c r="H94" s="23" t="n"/>
-      <c r="I94" s="23" t="n"/>
-      <c r="J94" s="23" t="n"/>
+      <c r="H94" s="29" t="n"/>
+      <c r="I94" s="29" t="n"/>
+      <c r="J94" s="29" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
@@ -8255,33 +10519,33 @@
         <f>ROUND(E95-D95,2)</f>
         <v/>
       </c>
-      <c r="H95" s="23" t="n"/>
-      <c r="I95" s="23" t="n"/>
-      <c r="J95" s="23" t="n"/>
+      <c r="H95" s="29" t="n"/>
+      <c r="I95" s="29" t="n"/>
+      <c r="J95" s="29" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="21" t="n"/>
+      <c r="A96" s="27" t="n"/>
       <c r="B96" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C96" s="21" t="n"/>
-      <c r="D96" s="22">
+      <c r="C96" s="27" t="n"/>
+      <c r="D96" s="28">
         <f>SUM(D69:D95)</f>
         <v/>
       </c>
-      <c r="E96" s="22">
+      <c r="E96" s="28">
         <f>SUM(E69:E95)</f>
         <v/>
       </c>
-      <c r="F96" s="22">
+      <c r="F96" s="28">
         <f>SUM(F69:F95)</f>
         <v/>
       </c>
-      <c r="H96" s="23" t="n"/>
-      <c r="I96" s="23" t="n"/>
-      <c r="J96" s="23" t="n"/>
+      <c r="H96" s="29" t="n"/>
+      <c r="I96" s="29" t="n"/>
+      <c r="J96" s="29" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сверка с ВДЦ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Закрытие по ВДЦ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По литерам" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Привязка к чертежам" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="В КП, не вошло" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сверка с КП" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Двери" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Привязка к чертежам" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="В КП, не вошло" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сверка с КП" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,6 +113,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -121,13 +123,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,15 +136,13 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -639,16 +635,16 @@
         <v/>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2</v>
@@ -672,7 +668,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Лит. Г: 1 шт. по КП Г + по 1 шт. из КП лит. А и Б (там в КП по 4, на чертеже по 3)</t>
+          <t>На чертеже А3, Б3, Г3. Две шт. из лит. Г (КП 1-18 №6, №8) записаны в объёмы лит. А и Б — по ВДЦ А4, Б4, Г1</t>
         </is>
       </c>
     </row>
@@ -1457,228 +1453,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Сверка спецификации с ВДЦ (Приложение № 2, лист «Корректировка»). К закрытию — меньшее из ВДЦ и спецификации, площадь по размерам ВДЦ</t>
+          <t>Закрытие по ВДЦ (Приложение № 2, лист «Корректировка»): к закрытию — меньшее из ВДЦ и КП, площадь по размерам ВДЦ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Строка ВДЦ — номер строки «Изготовление и монтаж» на листе «Корректировка»</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="62" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+          <t>Строка ВДЦ — номер строки «Изготовление и монтаж» на листе «Корректировка». Жёлтым — количество не совпадает с ВДЦ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>1. Витражи</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Литер</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Марка</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Размер по ВДЦ, мм</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Строка ВДЦ</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>По ВДЦ, шт</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>По ВДЦ, м²</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>По спецификации, шт</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Площадь по КП, м²</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>По КП / спецификации, шт</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>К закрытию, шт</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>К закрытию по ВДЦ, м²</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>К закрытию, м²</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Не закрыто по ВДЦ, шт</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Сверх ВДЦ, шт</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Замечание</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>4200×4820</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="13">
-        <f>4.2*4.82*4</f>
-        <v/>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="J4" s="12">
-        <f>MIN(F4,N(H4))</f>
-        <v/>
-      </c>
-      <c r="K4" s="13">
-        <f>ROUND(G4/F4*J4,2)</f>
-        <v/>
-      </c>
-      <c r="L4" s="12">
-        <f>F4-J4</f>
-        <v/>
-      </c>
-      <c r="M4" s="12">
-        <f>N(H4)-J4</f>
-        <v/>
-      </c>
-      <c r="N4" s="14" t="inlineStr">
-        <is>
-          <t>1 шт. из КП перенесена в лит. Г</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Вн-8</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2600×4820</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5">
-        <f>2.6*4.82*1</f>
-        <v/>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="J5" s="3">
-        <f>MIN(F5,N(H5))</f>
-        <v/>
-      </c>
-      <c r="K5" s="5">
-        <f>ROUND(G5/F5*J5,2)</f>
-        <v/>
-      </c>
-      <c r="L5" s="3">
-        <f>F5-J5</f>
-        <v/>
-      </c>
-      <c r="M5" s="3">
-        <f>N(H5)-J5</f>
-        <v/>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -1687,55 +1570,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Вн-14</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2485×4820</t>
+          <t>4200×4820</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6" s="5">
-        <f>2.485*4.82*1</f>
+        <f>4.2*4.82*4</f>
         <v/>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="J6" s="3">
+        <v>4</v>
+      </c>
+      <c r="I6" s="3">
         <f>MIN(F6,N(H6))</f>
         <v/>
       </c>
-      <c r="K6" s="5">
-        <f>ROUND(G6/F6*J6,2)</f>
+      <c r="J6" s="5">
+        <f>ROUND(G6/F6*I6,2)</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>F6-I6</f>
         <v/>
       </c>
       <c r="L6" s="3">
-        <f>F6-J6</f>
-        <v/>
-      </c>
-      <c r="M6" s="3">
-        <f>N(H6)-J6</f>
-        <v/>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 2320×4800 — отличается от ВДЦ более чем на 5%</t>
+        <f>N(H6)-I6</f>
+        <v/>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>1 шт. установлена в лит. Г (КП 1-18 №6), объём записан в лит. А</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -1744,332 +1624,318 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Вн-15</t>
+          <t>Вн-8</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1400×4820</t>
+          <t>2600×4820</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="5">
-        <f>1.4*4.82*1</f>
+        <f>2.6*4.82*1</f>
         <v/>
       </c>
       <c r="H7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="I7" s="3">
         <f>MIN(F7,N(H7))</f>
         <v/>
       </c>
-      <c r="K7" s="5">
-        <f>ROUND(G7/F7*J7,2)</f>
+      <c r="J7" s="5">
+        <f>ROUND(G7/F7*I7,2)</f>
+        <v/>
+      </c>
+      <c r="K7" s="3">
+        <f>F7-I7</f>
         <v/>
       </c>
       <c r="L7" s="3">
-        <f>F7-J7</f>
-        <v/>
-      </c>
-      <c r="M7" s="3">
-        <f>N(H7)-J7</f>
-        <v/>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 1170×4800 — отличается от ВДЦ более чем на 5%</t>
+        <f>N(H7)-I7</f>
+        <v/>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Вн-14</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2485×4820</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <f>2.485*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <f>MIN(F8,N(H8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>ROUND(G8/F8*I8,2)</f>
+        <v/>
+      </c>
+      <c r="K8" s="3">
+        <f>F8-I8</f>
+        <v/>
+      </c>
+      <c r="L8" s="3">
+        <f>N(H8)-I8</f>
+        <v/>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1400×4820</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <f>1.4*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <f>MIN(F9,N(H9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="5">
+        <f>ROUND(G9/F9*I9,2)</f>
+        <v/>
+      </c>
+      <c r="K9" s="3">
+        <f>F9-I9</f>
+        <v/>
+      </c>
+      <c r="L9" s="3">
+        <f>N(H9)-I9</f>
+        <v/>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Вн-22</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>2150×2720</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G10" s="5">
         <f>2.15*2.72*5</f>
         <v/>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="J8" s="3">
-        <f>MIN(F8,N(H8))</f>
-        <v/>
-      </c>
-      <c r="K8" s="5">
-        <f>ROUND(G8/F8*J8,2)</f>
-        <v/>
-      </c>
-      <c r="L8" s="3">
-        <f>F8-J8</f>
-        <v/>
-      </c>
-      <c r="M8" s="3">
-        <f>N(H8)-J8</f>
-        <v/>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="I10" s="3">
+        <f>MIN(F10,N(H10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="5">
+        <f>ROUND(G10/F10*I10,2)</f>
+        <v/>
+      </c>
+      <c r="K10" s="3">
+        <f>F10-I10</f>
+        <v/>
+      </c>
+      <c r="L10" s="3">
+        <f>N(H10)-I10</f>
+        <v/>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>КП на 11 шт. распределён по позициям ВДЦ: А5, Б5, В1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Вн-23</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>3540×3020</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="F9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="14">
         <f>3.54*3.02*1</f>
         <v/>
       </c>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="12">
-        <f>MIN(F9,N(H9))</f>
-        <v/>
-      </c>
-      <c r="K9" s="13">
-        <f>ROUND(G9/F9*J9,2)</f>
-        <v/>
-      </c>
-      <c r="L9" s="12">
-        <f>F9-J9</f>
-        <v/>
-      </c>
-      <c r="M9" s="12">
-        <f>N(H9)-J9</f>
-        <v/>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13">
+        <f>MIN(F11,N(H11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>ROUND(G11/F11*I11,2)</f>
+        <v/>
+      </c>
+      <c r="K11" s="13">
+        <f>F11-I11</f>
+        <v/>
+      </c>
+      <c r="L11" s="13">
+        <f>N(H11)-I11</f>
+        <v/>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Вн-24</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>2610×3020</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E12" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="F10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="13">
+      <c r="F12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="14">
         <f>2.61*3.02*1</f>
         <v/>
       </c>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="12">
-        <f>MIN(F10,N(H10))</f>
-        <v/>
-      </c>
-      <c r="K10" s="13">
-        <f>ROUND(G10/F10*J10,2)</f>
-        <v/>
-      </c>
-      <c r="L10" s="12">
-        <f>F10-J10</f>
-        <v/>
-      </c>
-      <c r="M10" s="12">
-        <f>N(H10)-J10</f>
-        <v/>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>4200×4820</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" s="13">
-        <f>4.2*4.82*4</f>
-        <v/>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="J11" s="12">
-        <f>MIN(F11,N(H11))</f>
-        <v/>
-      </c>
-      <c r="K11" s="13">
-        <f>ROUND(G11/F11*J11,2)</f>
-        <v/>
-      </c>
-      <c r="L11" s="12">
-        <f>F11-J11</f>
-        <v/>
-      </c>
-      <c r="M11" s="12">
-        <f>N(H11)-J11</f>
-        <v/>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>1 шт. из КП перенесена в лит. Г</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Вн-15</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>1400×4820</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5">
-        <f>1.4*4.82</f>
-        <v/>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13">
         <f>MIN(F12,N(H12))</f>
         <v/>
       </c>
-      <c r="K12" s="5">
-        <f>ROUND(G12/F12*J12,2)</f>
-        <v/>
-      </c>
-      <c r="L12" s="3">
-        <f>F12-J12</f>
-        <v/>
-      </c>
-      <c r="M12" s="3">
-        <f>N(H12)-J12</f>
-        <v/>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 1250×4800 — отличается от ВДЦ более чем на 5%</t>
+      <c r="J12" s="14">
+        <f>ROUND(G12/F12*I12,2)</f>
+        <v/>
+      </c>
+      <c r="K12" s="13">
+        <f>F12-I12</f>
+        <v/>
+      </c>
+      <c r="L12" s="13">
+        <f>N(H12)-I12</f>
+        <v/>
+      </c>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -2078,7 +1944,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2087,46 +1953,43 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" s="5">
-        <f>4.2*4.82</f>
+        <f>4.2*4.82*4</f>
         <v/>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="J13" s="3">
+        <v>4</v>
+      </c>
+      <c r="I13" s="3">
         <f>MIN(F13,N(H13))</f>
         <v/>
       </c>
-      <c r="K13" s="5">
-        <f>ROUND(G13/F13*J13,2)</f>
+      <c r="J13" s="5">
+        <f>ROUND(G13/F13*I13,2)</f>
+        <v/>
+      </c>
+      <c r="K13" s="3">
+        <f>F13-I13</f>
         <v/>
       </c>
       <c r="L13" s="3">
-        <f>F13-J13</f>
-        <v/>
-      </c>
-      <c r="M13" s="3">
-        <f>N(H13)-J13</f>
-        <v/>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
+        <f>N(H13)-I13</f>
+        <v/>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>1 шт. установлена в лит. Г (КП 1-18 №8), объём записан в лит. Б</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -2135,660 +1998,628 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Вн-18</t>
+          <t>Вн-15</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>2600×4820</t>
+          <t>1400×4820</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="5">
-        <f>2.6*4.82</f>
+        <f>1.4*4.82</f>
         <v/>
       </c>
       <c r="H14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
         <f>MIN(F14,N(H14))</f>
         <v/>
       </c>
-      <c r="K14" s="5">
-        <f>ROUND(G14/F14*J14,2)</f>
+      <c r="J14" s="5">
+        <f>ROUND(G14/F14*I14,2)</f>
+        <v/>
+      </c>
+      <c r="K14" s="3">
+        <f>F14-I14</f>
         <v/>
       </c>
       <c r="L14" s="3">
-        <f>F14-J14</f>
-        <v/>
-      </c>
-      <c r="M14" s="3">
-        <f>N(H14)-J14</f>
-        <v/>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 2480×4800 — отличается от ВДЦ более чем на 5%</t>
+        <f>N(H14)-I14</f>
+        <v/>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Вн-17</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>4200×4820</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <f>4.2*4.82</f>
+        <v/>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
+        <f>MIN(F15,N(H15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="5">
+        <f>ROUND(G15/F15*I15,2)</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>F15-I15</f>
+        <v/>
+      </c>
+      <c r="L15" s="3">
+        <f>N(H15)-I15</f>
+        <v/>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Вн-18</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2600×4820</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <f>2.6*4.82</f>
+        <v/>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
+        <f>MIN(F16,N(H16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="5">
+        <f>ROUND(G16/F16*I16,2)</f>
+        <v/>
+      </c>
+      <c r="K16" s="3">
+        <f>F16-I16</f>
+        <v/>
+      </c>
+      <c r="L16" s="3">
+        <f>N(H16)-I16</f>
+        <v/>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Вн-22</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>2150×2720</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G17" s="5">
         <f>2.15*2.72*5</f>
         <v/>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="J15" s="3">
-        <f>MIN(F15,N(H15))</f>
-        <v/>
-      </c>
-      <c r="K15" s="5">
-        <f>ROUND(G15/F15*J15,2)</f>
-        <v/>
-      </c>
-      <c r="L15" s="3">
-        <f>F15-J15</f>
-        <v/>
-      </c>
-      <c r="M15" s="3">
-        <f>N(H15)-J15</f>
-        <v/>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="I17" s="3">
+        <f>MIN(F17,N(H17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="5">
+        <f>ROUND(G17/F17*I17,2)</f>
+        <v/>
+      </c>
+      <c r="K17" s="3">
+        <f>F17-I17</f>
+        <v/>
+      </c>
+      <c r="L17" s="3">
+        <f>N(H17)-I17</f>
+        <v/>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>КП на 11 шт. распределён по позициям ВДЦ: А5, Б5, В1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Вн-23</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>3540×3020</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="F16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="F18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="14">
         <f>3.54*3.02*1</f>
         <v/>
       </c>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="12">
-        <f>MIN(F16,N(H16))</f>
-        <v/>
-      </c>
-      <c r="K16" s="13">
-        <f>ROUND(G16/F16*J16,2)</f>
-        <v/>
-      </c>
-      <c r="L16" s="12">
-        <f>F16-J16</f>
-        <v/>
-      </c>
-      <c r="M16" s="12">
-        <f>N(H16)-J16</f>
-        <v/>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13">
+        <f>MIN(F18,N(H18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="14">
+        <f>ROUND(G18/F18*I18,2)</f>
+        <v/>
+      </c>
+      <c r="K18" s="13">
+        <f>F18-I18</f>
+        <v/>
+      </c>
+      <c r="L18" s="13">
+        <f>N(H18)-I18</f>
+        <v/>
+      </c>
+      <c r="M18" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Вн-24</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>2610×3020</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E19" s="13" t="n">
         <v>54</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="13">
+      <c r="F19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="14">
         <f>2.61*3.02*1</f>
         <v/>
       </c>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="12">
-        <f>MIN(F17,N(H17))</f>
-        <v/>
-      </c>
-      <c r="K17" s="13">
-        <f>ROUND(G17/F17*J17,2)</f>
-        <v/>
-      </c>
-      <c r="L17" s="12">
-        <f>F17-J17</f>
-        <v/>
-      </c>
-      <c r="M17" s="12">
-        <f>N(H17)-J17</f>
-        <v/>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13">
+        <f>MIN(F19,N(H19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="14">
+        <f>ROUND(G19/F19*I19,2)</f>
+        <v/>
+      </c>
+      <c r="K19" s="13">
+        <f>F19-I19</f>
+        <v/>
+      </c>
+      <c r="L19" s="13">
+        <f>N(H19)-I19</f>
+        <v/>
+      </c>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Вн-6</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>4200×4820</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5">
+      <c r="F20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
         <f>4.2*4.82*1</f>
         <v/>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="J18" s="3">
-        <f>MIN(F18,N(H18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="5">
-        <f>ROUND(G18/F18*J18,2)</f>
-        <v/>
-      </c>
-      <c r="L18" s="3">
-        <f>F18-J18</f>
-        <v/>
-      </c>
-      <c r="M18" s="3">
-        <f>N(H18)-J18</f>
-        <v/>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="H20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3">
+        <f>MIN(F20,N(H20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="5">
+        <f>ROUND(G20/F20*I20,2)</f>
+        <v/>
+      </c>
+      <c r="K20" s="3">
+        <f>F20-I20</f>
+        <v/>
+      </c>
+      <c r="L20" s="3">
+        <f>N(H20)-I20</f>
+        <v/>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Вн-13</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>3200×4820</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="F21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
         <f>3.2*4.82*1</f>
         <v/>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="J19" s="3">
-        <f>MIN(F19,N(H19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="5">
-        <f>ROUND(G19/F19*J19,2)</f>
-        <v/>
-      </c>
-      <c r="L19" s="3">
-        <f>F19-J19</f>
-        <v/>
-      </c>
-      <c r="M19" s="3">
-        <f>N(H19)-J19</f>
-        <v/>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="H21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <f>MIN(F21,N(H21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="5">
+        <f>ROUND(G21/F21*I21,2)</f>
+        <v/>
+      </c>
+      <c r="K21" s="3">
+        <f>F21-I21</f>
+        <v/>
+      </c>
+      <c r="L21" s="3">
+        <f>N(H21)-I21</f>
+        <v/>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Вн-16</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>1200×4820</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E22" s="13" t="n">
         <v>68</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="13">
+      <c r="F22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14">
         <f>1.2*4.82*1</f>
         <v/>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H22" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="13" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="J20" s="12">
-        <f>MIN(F20,N(H20))</f>
-        <v/>
-      </c>
-      <c r="K20" s="13">
-        <f>ROUND(G20/F20*J20,2)</f>
-        <v/>
-      </c>
-      <c r="L20" s="12">
-        <f>F20-J20</f>
-        <v/>
-      </c>
-      <c r="M20" s="12">
-        <f>N(H20)-J20</f>
-        <v/>
-      </c>
-      <c r="N20" s="14" t="inlineStr">
-        <is>
-          <t>по чертежу и КП 3 шт., в ВДЦ 1; размер по КП 1060×5180, 1240×4800, 1370×5200 — отличается от ВДЦ более чем на 5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="I22" s="13">
+        <f>MIN(F22,N(H22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="14">
+        <f>ROUND(G22/F22*I22,2)</f>
+        <v/>
+      </c>
+      <c r="K22" s="13">
+        <f>F22-I22</f>
+        <v/>
+      </c>
+      <c r="L22" s="13">
+        <f>N(H22)-I22</f>
+        <v/>
+      </c>
+      <c r="M22" s="15" t="inlineStr">
+        <is>
+          <t>по чертежу и КП 3 шт., в ВДЦ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Вн-17</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>19.68</v>
-      </c>
-      <c r="J21" s="12" t="n">
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="13" t="n">
+      <c r="J23" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="K23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="12">
-        <f>N(H21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="14" t="inlineStr">
+      <c r="L23" s="13">
+        <f>N(H23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="15" t="inlineStr">
         <is>
           <t>в ВДЦ лит. В нет</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
+    <row r="24">
+      <c r="A24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Вн-19</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>3000×4820</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G24" s="5">
         <f>3*4.82*2</f>
         <v/>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="5" t="n">
-        <v>24.67</v>
-      </c>
-      <c r="J22" s="3">
-        <f>MIN(F22,N(H22))</f>
-        <v/>
-      </c>
-      <c r="K22" s="5">
-        <f>ROUND(G22/F22*J22,2)</f>
-        <v/>
-      </c>
-      <c r="L22" s="3">
-        <f>F22-J22</f>
-        <v/>
-      </c>
-      <c r="M22" s="3">
-        <f>N(H22)-J22</f>
-        <v/>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 2570×4800 — отличается от ВДЦ более чем на 5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="I24" s="3">
+        <f>MIN(F24,N(H24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="5">
+        <f>ROUND(G24/F24*I24,2)</f>
+        <v/>
+      </c>
+      <c r="K24" s="3">
+        <f>F24-I24</f>
+        <v/>
+      </c>
+      <c r="L24" s="3">
+        <f>N(H24)-I24</f>
+        <v/>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>В</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Вн-22</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>2150×2720</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E25" s="13" t="n">
         <v>74</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G25" s="14">
         <f>2.15*2.72*4</f>
         <v/>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="13" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="J23" s="12">
-        <f>MIN(F23,N(H23))</f>
-        <v/>
-      </c>
-      <c r="K23" s="13">
-        <f>ROUND(G23/F23*J23,2)</f>
-        <v/>
-      </c>
-      <c r="L23" s="12">
-        <f>F23-J23</f>
-        <v/>
-      </c>
-      <c r="M23" s="12">
-        <f>N(H23)-J23</f>
-        <v/>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>в ВДЦ 4, в спецификации 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>4200×4820</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13">
-        <f>4.2*4.82*1</f>
-        <v/>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="13" t="n">
-        <v>61.63</v>
-      </c>
-      <c r="J24" s="12">
-        <f>MIN(F24,N(H24))</f>
-        <v/>
-      </c>
-      <c r="K24" s="13">
-        <f>ROUND(G24/F24*J24,2)</f>
-        <v/>
-      </c>
-      <c r="L24" s="12">
-        <f>F24-J24</f>
-        <v/>
-      </c>
-      <c r="M24" s="12">
-        <f>N(H24)-J24</f>
-        <v/>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>2 шт. перенесены из КП лит. А и Б; в ВДЦ лит. Г — 1 шт., зато в ВДЦ А и Б по 4 шт. (не закрыто по 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Вн-10</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>4160×4820</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5">
-        <f>4.16*4.82*1</f>
-        <v/>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="J25" s="3">
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="13">
         <f>MIN(F25,N(H25))</f>
         <v/>
       </c>
-      <c r="K25" s="5">
-        <f>ROUND(G25/F25*J25,2)</f>
-        <v/>
-      </c>
-      <c r="L25" s="3">
-        <f>F25-J25</f>
-        <v/>
-      </c>
-      <c r="M25" s="3">
-        <f>N(H25)-J25</f>
-        <v/>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
+      <c r="J25" s="14">
+        <f>ROUND(G25/F25*I25,2)</f>
+        <v/>
+      </c>
+      <c r="K25" s="13">
+        <f>F25-I25</f>
+        <v/>
+      </c>
+      <c r="L25" s="13">
+        <f>N(H25)-I25</f>
+        <v/>
+      </c>
+      <c r="M25" s="15" t="inlineStr">
+        <is>
+          <t>КП на 11 шт. распределён по позициям ВДЦ: А5, Б5, В1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -2797,55 +2628,52 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Вн-11</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2450×4820</t>
+          <t>4200×4820</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="5">
-        <f>2.45*4.82</f>
+        <f>4.2*4.82*1</f>
         <v/>
       </c>
       <c r="H26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="I26" s="3">
         <f>MIN(F26,N(H26))</f>
         <v/>
       </c>
-      <c r="K26" s="5">
-        <f>ROUND(G26/F26*J26,2)</f>
+      <c r="J26" s="5">
+        <f>ROUND(G26/F26*I26,2)</f>
+        <v/>
+      </c>
+      <c r="K26" s="3">
+        <f>F26-I26</f>
         <v/>
       </c>
       <c r="L26" s="3">
-        <f>F26-J26</f>
-        <v/>
-      </c>
-      <c r="M26" s="3">
-        <f>N(H26)-J26</f>
-        <v/>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 2310×4800 — отличается от ВДЦ более чем на 5%</t>
+        <f>N(H26)-I26</f>
+        <v/>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>на чертеже 3 шт., 2 из них закрываются по лит. А и Б</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -2854,55 +2682,52 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Вн-12</t>
+          <t>Вн-10</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3370×4820</t>
+          <t>4160×4820</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="5">
-        <f>3.37*4.82</f>
+        <f>4.16*4.82*1</f>
         <v/>
       </c>
       <c r="H27" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="I27" s="3">
         <f>MIN(F27,N(H27))</f>
         <v/>
       </c>
-      <c r="K27" s="5">
-        <f>ROUND(G27/F27*J27,2)</f>
+      <c r="J27" s="5">
+        <f>ROUND(G27/F27*I27,2)</f>
+        <v/>
+      </c>
+      <c r="K27" s="3">
+        <f>F27-I27</f>
         <v/>
       </c>
       <c r="L27" s="3">
-        <f>F27-J27</f>
-        <v/>
-      </c>
-      <c r="M27" s="3">
-        <f>N(H27)-J27</f>
-        <v/>
-      </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
+        <f>N(H27)-I27</f>
+        <v/>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -2911,55 +2736,52 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-11</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>4200×4820</t>
+          <t>2450×4820</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="5">
-        <f>4.2*4.82</f>
+        <f>2.45*4.82</f>
         <v/>
       </c>
       <c r="H28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="5" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="J28" s="3">
+      <c r="I28" s="3">
         <f>MIN(F28,N(H28))</f>
         <v/>
       </c>
-      <c r="K28" s="5">
-        <f>ROUND(G28/F28*J28,2)</f>
+      <c r="J28" s="5">
+        <f>ROUND(G28/F28*I28,2)</f>
+        <v/>
+      </c>
+      <c r="K28" s="3">
+        <f>F28-I28</f>
         <v/>
       </c>
       <c r="L28" s="3">
-        <f>F28-J28</f>
-        <v/>
-      </c>
-      <c r="M28" s="3">
-        <f>N(H28)-J28</f>
-        <v/>
-      </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
+        <f>N(H28)-I28</f>
+        <v/>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -2968,55 +2790,52 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Вн-20</t>
+          <t>Вн-12</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3900×4820</t>
+          <t>3370×4820</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="5">
-        <f>3.9*4.82</f>
+        <f>3.37*4.82</f>
         <v/>
       </c>
       <c r="H29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="I29" s="3">
         <f>MIN(F29,N(H29))</f>
         <v/>
       </c>
-      <c r="K29" s="5">
-        <f>ROUND(G29/F29*J29,2)</f>
+      <c r="J29" s="5">
+        <f>ROUND(G29/F29*I29,2)</f>
+        <v/>
+      </c>
+      <c r="K29" s="3">
+        <f>F29-I29</f>
         <v/>
       </c>
       <c r="L29" s="3">
-        <f>F29-J29</f>
-        <v/>
-      </c>
-      <c r="M29" s="3">
-        <f>N(H29)-J29</f>
-        <v/>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
+        <f>N(H29)-I29</f>
+        <v/>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -3025,222 +2844,212 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Вн-21</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2920×4820</t>
+          <t>4200×4820</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="5">
-        <f>2.92*4.82</f>
+        <f>4.2*4.82</f>
         <v/>
       </c>
       <c r="H30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="J30" s="3">
+      <c r="I30" s="3">
         <f>MIN(F30,N(H30))</f>
         <v/>
       </c>
-      <c r="K30" s="5">
-        <f>ROUND(G30/F30*J30,2)</f>
+      <c r="J30" s="5">
+        <f>ROUND(G30/F30*I30,2)</f>
+        <v/>
+      </c>
+      <c r="K30" s="3">
+        <f>F30-I30</f>
         <v/>
       </c>
       <c r="L30" s="3">
-        <f>F30-J30</f>
-        <v/>
-      </c>
-      <c r="M30" s="3">
-        <f>N(H30)-J30</f>
-        <v/>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
+        <f>N(H30)-I30</f>
+        <v/>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="A31" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Г</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>2150×2720</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="13">
-        <f>2.15*2.72*4</f>
-        <v/>
-      </c>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="12">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Вн-20</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>3900×4820</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5">
+        <f>3.9*4.82</f>
+        <v/>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
         <f>MIN(F31,N(H31))</f>
         <v/>
       </c>
-      <c r="K31" s="13">
-        <f>ROUND(G31/F31*J31,2)</f>
-        <v/>
-      </c>
-      <c r="L31" s="12">
-        <f>F31-J31</f>
-        <v/>
-      </c>
-      <c r="M31" s="12">
-        <f>N(H31)-J31</f>
-        <v/>
-      </c>
-      <c r="N31" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
+      <c r="J31" s="5">
+        <f>ROUND(G31/F31*I31,2)</f>
+        <v/>
+      </c>
+      <c r="K31" s="3">
+        <f>F31-I31</f>
+        <v/>
+      </c>
+      <c r="L31" s="3">
+        <f>N(H31)-I31</f>
+        <v/>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Д</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-21</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>4200×4820</t>
+          <t>2920×4820</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5">
-        <f>4.2*4.82*2</f>
+        <f>2.92*4.82</f>
         <v/>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>39.98</v>
-      </c>
-      <c r="J32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3">
         <f>MIN(F32,N(H32))</f>
         <v/>
       </c>
-      <c r="K32" s="5">
-        <f>ROUND(G32/F32*J32,2)</f>
+      <c r="J32" s="5">
+        <f>ROUND(G32/F32*I32,2)</f>
+        <v/>
+      </c>
+      <c r="K32" s="3">
+        <f>F32-I32</f>
         <v/>
       </c>
       <c r="L32" s="3">
-        <f>F32-J32</f>
-        <v/>
-      </c>
-      <c r="M32" s="3">
-        <f>N(H32)-J32</f>
-        <v/>
-      </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает</t>
+        <f>N(H32)-I32</f>
+        <v/>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Д</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Вн-7</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>3020×4820</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5">
-        <f>3.02*4.82*1</f>
-        <v/>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="A33" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>2150×2720</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="14">
+        <f>2.15*2.72*4</f>
+        <v/>
+      </c>
+      <c r="H33" s="13" t="n"/>
+      <c r="I33" s="13">
         <f>MIN(F33,N(H33))</f>
         <v/>
       </c>
-      <c r="K33" s="5">
-        <f>ROUND(G33/F33*J33,2)</f>
-        <v/>
-      </c>
-      <c r="L33" s="3">
-        <f>F33-J33</f>
-        <v/>
-      </c>
-      <c r="M33" s="3">
-        <f>N(H33)-J33</f>
-        <v/>
-      </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 4160×4800 — отличается от ВДЦ более чем на 5%</t>
+      <c r="J33" s="14">
+        <f>ROUND(G33/F33*I33,2)</f>
+        <v/>
+      </c>
+      <c r="K33" s="13">
+        <f>F33-I33</f>
+        <v/>
+      </c>
+      <c r="L33" s="13">
+        <f>N(H33)-I33</f>
+        <v/>
+      </c>
+      <c r="M33" s="15" t="inlineStr">
+        <is>
+          <t>КП на 11 шт. распределён по позициям ВДЦ: А5, Б5, В1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -3249,444 +3058,1906 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Вн-9</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3870×4820</t>
+          <t>4200×4820</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="5">
-        <f>3.87*4.82</f>
+        <f>4.2*4.82*2</f>
         <v/>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>19.68</v>
-      </c>
-      <c r="J34" s="3">
+        <v>2</v>
+      </c>
+      <c r="I34" s="3">
         <f>MIN(F34,N(H34))</f>
         <v/>
       </c>
-      <c r="K34" s="5">
-        <f>ROUND(G34/F34*J34,2)</f>
+      <c r="J34" s="5">
+        <f>ROUND(G34/F34*I34,2)</f>
+        <v/>
+      </c>
+      <c r="K34" s="3">
+        <f>F34-I34</f>
         <v/>
       </c>
       <c r="L34" s="3">
-        <f>F34-J34</f>
-        <v/>
-      </c>
-      <c r="M34" s="3">
-        <f>N(H34)-J34</f>
-        <v/>
-      </c>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 4100×4800 — отличается от ВДЦ более чем на 5%</t>
+        <f>N(H34)-I34</f>
+        <v/>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Вн-7</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>3020×4820</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5">
+        <f>3.02*4.82*1</f>
+        <v/>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3">
+        <f>MIN(F35,N(H35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="5">
+        <f>ROUND(G35/F35*I35,2)</f>
+        <v/>
+      </c>
+      <c r="K35" s="3">
+        <f>F35-I35</f>
+        <v/>
+      </c>
+      <c r="L35" s="3">
+        <f>N(H35)-I35</f>
+        <v/>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>3870×4820</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5">
+        <f>3.87*4.82</f>
+        <v/>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3">
+        <f>MIN(F36,N(H36))</f>
+        <v/>
+      </c>
+      <c r="J36" s="5">
+        <f>ROUND(G36/F36*I36,2)</f>
+        <v/>
+      </c>
+      <c r="K36" s="3">
+        <f>F36-I36</f>
+        <v/>
+      </c>
+      <c r="L36" s="3">
+        <f>N(H36)-I36</f>
+        <v/>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Д</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Вн-17</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>4200×4820</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5">
+      <c r="F37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5">
         <f>4.2*4.82</f>
         <v/>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="J35" s="3">
-        <f>MIN(F35,N(H35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="5">
-        <f>ROUND(G35/F35*J35,2)</f>
-        <v/>
-      </c>
-      <c r="L35" s="3">
-        <f>F35-J35</f>
-        <v/>
-      </c>
-      <c r="M35" s="3">
-        <f>N(H35)-J35</f>
-        <v/>
-      </c>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>кол-во совпадает; размер по КП 3780×4800 — отличается от ВДЦ более чем на 5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n">
+      <c r="H37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="3">
+        <f>MIN(F37,N(H37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="5">
+        <f>ROUND(G37/F37*I37,2)</f>
+        <v/>
+      </c>
+      <c r="K37" s="3">
+        <f>F37-I37</f>
+        <v/>
+      </c>
+      <c r="L37" s="3">
+        <f>N(H37)-I37</f>
+        <v/>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Ж</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Вн-1</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>4750×3870</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>136</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="13">
+      <c r="F38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="14">
         <f>4.75*3.87</f>
         <v/>
       </c>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="12">
-        <f>MIN(F36,N(H36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="13">
-        <f>ROUND(G36/F36*J36,2)</f>
-        <v/>
-      </c>
-      <c r="L36" s="12">
-        <f>F36-J36</f>
-        <v/>
-      </c>
-      <c r="M36" s="12">
-        <f>N(H36)-J36</f>
-        <v/>
-      </c>
-      <c r="N36" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="13">
+        <f>MIN(F38,N(H38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="14">
+        <f>ROUND(G38/F38*I38,2)</f>
+        <v/>
+      </c>
+      <c r="K38" s="13">
+        <f>F38-I38</f>
+        <v/>
+      </c>
+      <c r="L38" s="13">
+        <f>N(H38)-I38</f>
+        <v/>
+      </c>
+      <c r="M38" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Ж</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Вн-2</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>4750×3870</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E39" s="13" t="n">
         <v>138</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="13">
+      <c r="F39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="14">
         <f>4.75*3.87</f>
         <v/>
       </c>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="12">
-        <f>MIN(F37,N(H37))</f>
-        <v/>
-      </c>
-      <c r="K37" s="13">
-        <f>ROUND(G37/F37*J37,2)</f>
-        <v/>
-      </c>
-      <c r="L37" s="12">
-        <f>F37-J37</f>
-        <v/>
-      </c>
-      <c r="M37" s="12">
-        <f>N(H37)-J37</f>
-        <v/>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n">
+      <c r="H39" s="13" t="n"/>
+      <c r="I39" s="13">
+        <f>MIN(F39,N(H39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="14">
+        <f>ROUND(G39/F39*I39,2)</f>
+        <v/>
+      </c>
+      <c r="K39" s="13">
+        <f>F39-I39</f>
+        <v/>
+      </c>
+      <c r="L39" s="13">
+        <f>N(H39)-I39</f>
+        <v/>
+      </c>
+      <c r="M39" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Ж</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Вн-3</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>6100×3870</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E40" s="13" t="n">
         <v>140</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="13">
+      <c r="F40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="14">
         <f>6.1*3.87</f>
         <v/>
       </c>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="12">
-        <f>MIN(F38,N(H38))</f>
-        <v/>
-      </c>
-      <c r="K38" s="13">
-        <f>ROUND(G38/F38*J38,2)</f>
-        <v/>
-      </c>
-      <c r="L38" s="12">
-        <f>F38-J38</f>
-        <v/>
-      </c>
-      <c r="M38" s="12">
-        <f>N(H38)-J38</f>
-        <v/>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="H40" s="13" t="n"/>
+      <c r="I40" s="13">
+        <f>MIN(F40,N(H40))</f>
+        <v/>
+      </c>
+      <c r="J40" s="14">
+        <f>ROUND(G40/F40*I40,2)</f>
+        <v/>
+      </c>
+      <c r="K40" s="13">
+        <f>F40-I40</f>
+        <v/>
+      </c>
+      <c r="L40" s="13">
+        <f>N(H40)-I40</f>
+        <v/>
+      </c>
+      <c r="M40" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Ж</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Вн-4</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>5400×3470</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E41" s="13" t="n">
         <v>142</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="13">
+      <c r="F41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="14">
         <f>5.4*3.47*1</f>
         <v/>
       </c>
-      <c r="H39" s="12" t="n"/>
-      <c r="I39" s="13" t="n"/>
-      <c r="J39" s="12">
-        <f>MIN(F39,N(H39))</f>
-        <v/>
-      </c>
-      <c r="K39" s="13">
-        <f>ROUND(G39/F39*J39,2)</f>
-        <v/>
-      </c>
-      <c r="L39" s="12">
-        <f>F39-J39</f>
-        <v/>
-      </c>
-      <c r="M39" s="12">
-        <f>N(H39)-J39</f>
-        <v/>
-      </c>
-      <c r="N39" s="14" t="inlineStr">
-        <is>
-          <t>нет в спецификации (нет в КП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="13">
+        <f>MIN(F41,N(H41))</f>
+        <v/>
+      </c>
+      <c r="J41" s="14">
+        <f>ROUND(G41/F41*I41,2)</f>
+        <v/>
+      </c>
+      <c r="K41" s="13">
+        <f>F41-I41</f>
+        <v/>
+      </c>
+      <c r="L41" s="13">
+        <f>N(H41)-I41</f>
+        <v/>
+      </c>
+      <c r="M41" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Ж</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Вн-5</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>7800×3470</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E42" s="13" t="n">
         <v>144</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="13">
+      <c r="F42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="14">
         <f>7.8*3.4</f>
         <v/>
       </c>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="13" t="n"/>
-      <c r="J40" s="12">
-        <f>MIN(F40,N(H40))</f>
-        <v/>
-      </c>
-      <c r="K40" s="13">
-        <f>ROUND(G40/F40*J40,2)</f>
-        <v/>
-      </c>
-      <c r="L40" s="12">
-        <f>F40-J40</f>
-        <v/>
-      </c>
-      <c r="M40" s="12">
-        <f>N(H40)-J40</f>
-        <v/>
-      </c>
-      <c r="N40" s="14" t="inlineStr">
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="13">
+        <f>MIN(F42,N(H42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="14">
+        <f>ROUND(G42/F42*I42,2)</f>
+        <v/>
+      </c>
+      <c r="K42" s="13">
+        <f>F42-I42</f>
+        <v/>
+      </c>
+      <c r="L42" s="13">
+        <f>N(H42)-I42</f>
+        <v/>
+      </c>
+      <c r="M42" s="15" t="inlineStr">
         <is>
           <t>в ВДЦ площадь =7.8*3.4 (26,52), а в названии 7800х3470 (27,07)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="8">
-        <f>SUM(F4:F40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="10">
-        <f>SUM(G4:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="8">
-        <f>SUM(H4:H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="10">
-        <f>SUM(I4:I40)</f>
-        <v/>
-      </c>
-      <c r="J41" s="8">
-        <f>SUM(J4:J40)</f>
-        <v/>
-      </c>
-      <c r="K41" s="10">
-        <f>SUM(K4:K40)</f>
-        <v/>
-      </c>
-      <c r="L41" s="8">
-        <f>SUM(L4:L40)</f>
-        <v/>
-      </c>
-      <c r="M41" s="8">
-        <f>SUM(M4:M40)</f>
-        <v/>
-      </c>
-      <c r="N41" s="11" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Вариант: 2 шт. Вн-6 лит. Г закрыть по строкам ВДЦ лит. А и Б (там не закрыто по 1 шт.) — дополнительно, м²:</t>
-        </is>
-      </c>
-      <c r="K43" s="16">
-        <f>ROUND(4.2*4.82*2,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>Итого к закрытию с этим вариантом, м²:</t>
-        </is>
-      </c>
-      <c r="K44" s="16">
-        <f>K41+K43</f>
-        <v/>
-      </c>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Итого витражи</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="8">
+        <f>SUM(F6:F42)</f>
+        <v/>
+      </c>
+      <c r="G43" s="10">
+        <f>SUM(G6:G42)</f>
+        <v/>
+      </c>
+      <c r="H43" s="8">
+        <f>SUM(H6:H42)</f>
+        <v/>
+      </c>
+      <c r="I43" s="8">
+        <f>SUM(I6:I42)</f>
+        <v/>
+      </c>
+      <c r="J43" s="10">
+        <f>SUM(J6:J42)</f>
+        <v/>
+      </c>
+      <c r="K43" s="8">
+        <f>SUM(K6:K42)</f>
+        <v/>
+      </c>
+      <c r="L43" s="8">
+        <f>SUM(L6:L42)</f>
+        <v/>
+      </c>
+      <c r="M43" s="11" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>2. Двери (КП от 13.04.2026; марка — по чертежу у витража). Излишек КП одного литера закрывает свободные строки ВДЦ других литеров</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="62" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Литер</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Размер по ВДЦ, мм</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Строка ВДЦ</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>По ВДЦ, шт</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>По ВДЦ, м²</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>По КП (свой литер), шт</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>К закрытию, шт</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>К закрытию, м²</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Не закрыто по ВДЦ, шт</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Сверх ВДЦ, шт</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Д17* (П)</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2410×1300</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G47" s="5">
+        <f>2.41*1.3*6</f>
+        <v/>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" s="5">
+        <f>ROUND(G47/F47*I47,2)</f>
+        <v/>
+      </c>
+      <c r="K47" s="3">
+        <f>F47-I47</f>
+        <v/>
+      </c>
+      <c r="L47" s="3">
+        <f>MAX(0,N(H47)-F47)</f>
+        <v/>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>6 — КП лит. А</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Д18 (П)</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>2100×1000</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="14">
+        <f>2.1*1</f>
+        <v/>
+      </c>
+      <c r="H48" s="13" t="n"/>
+      <c r="I48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="14">
+        <f>ROUND(G48/F48*I48,2)</f>
+        <v/>
+      </c>
+      <c r="K48" s="13">
+        <f>F48-I48</f>
+        <v/>
+      </c>
+      <c r="L48" s="13">
+        <f>MAX(0,N(H48)-F48)</f>
+        <v/>
+      </c>
+      <c r="M48" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>Д21 (П)</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>2100×1200</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="14">
+        <f>2.1*1.2</f>
+        <v/>
+      </c>
+      <c r="H49" s="13" t="n"/>
+      <c r="I49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="14">
+        <f>ROUND(G49/F49*I49,2)</f>
+        <v/>
+      </c>
+      <c r="K49" s="13">
+        <f>F49-I49</f>
+        <v/>
+      </c>
+      <c r="L49" s="13">
+        <f>MAX(0,N(H49)-F49)</f>
+        <v/>
+      </c>
+      <c r="M49" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Д22 (П)</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>2100×1300</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="14">
+        <f>2.1*1.3</f>
+        <v/>
+      </c>
+      <c r="H50" s="13" t="n"/>
+      <c r="I50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="14">
+        <f>ROUND(G50/F50*I50,2)</f>
+        <v/>
+      </c>
+      <c r="K50" s="13">
+        <f>F50-I50</f>
+        <v/>
+      </c>
+      <c r="L50" s="13">
+        <f>MAX(0,N(H50)-F50)</f>
+        <v/>
+      </c>
+      <c r="M50" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Д17* (П)</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2410×1300</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" s="5">
+        <f>2.41*1.3*6</f>
+        <v/>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J51" s="5">
+        <f>ROUND(G51/F51*I51,2)</f>
+        <v/>
+      </c>
+      <c r="K51" s="3">
+        <f>F51-I51</f>
+        <v/>
+      </c>
+      <c r="L51" s="3">
+        <f>MAX(0,N(H51)-F51)</f>
+        <v/>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>6 — КП лит. Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Д18 (П)</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>2100×1000</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="14">
+        <f>2.1*1</f>
+        <v/>
+      </c>
+      <c r="H52" s="13" t="n"/>
+      <c r="I52" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="14">
+        <f>ROUND(G52/F52*I52,2)</f>
+        <v/>
+      </c>
+      <c r="K52" s="13">
+        <f>F52-I52</f>
+        <v/>
+      </c>
+      <c r="L52" s="13">
+        <f>MAX(0,N(H52)-F52)</f>
+        <v/>
+      </c>
+      <c r="M52" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>Д21 (П)</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>2100×1200</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="14">
+        <f>2.1*1.2</f>
+        <v/>
+      </c>
+      <c r="H53" s="13" t="n"/>
+      <c r="I53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="14">
+        <f>ROUND(G53/F53*I53,2)</f>
+        <v/>
+      </c>
+      <c r="K53" s="13">
+        <f>F53-I53</f>
+        <v/>
+      </c>
+      <c r="L53" s="13">
+        <f>MAX(0,N(H53)-F53)</f>
+        <v/>
+      </c>
+      <c r="M53" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Д22 (П)</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>2100×1300</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="14">
+        <f>2.1*1.3</f>
+        <v/>
+      </c>
+      <c r="H54" s="13" t="n"/>
+      <c r="I54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="14">
+        <f>ROUND(G54/F54*I54,2)</f>
+        <v/>
+      </c>
+      <c r="K54" s="13">
+        <f>F54-I54</f>
+        <v/>
+      </c>
+      <c r="L54" s="13">
+        <f>MAX(0,N(H54)-F54)</f>
+        <v/>
+      </c>
+      <c r="M54" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Д17* (П)</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2410×1300</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="5">
+        <f>2.41*1.3*3</f>
+        <v/>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="5">
+        <f>ROUND(G55/F55*I55,2)</f>
+        <v/>
+      </c>
+      <c r="K55" s="3">
+        <f>F55-I55</f>
+        <v/>
+      </c>
+      <c r="L55" s="3">
+        <f>MAX(0,N(H55)-F55)</f>
+        <v/>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>3 — КП лит. В</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>Д18 (П)</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>2100×1000</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="14">
+        <f>2.1*1</f>
+        <v/>
+      </c>
+      <c r="H56" s="13" t="n"/>
+      <c r="I56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="14">
+        <f>ROUND(G56/F56*I56,2)</f>
+        <v/>
+      </c>
+      <c r="K56" s="13">
+        <f>F56-I56</f>
+        <v/>
+      </c>
+      <c r="L56" s="13">
+        <f>MAX(0,N(H56)-F56)</f>
+        <v/>
+      </c>
+      <c r="M56" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Д35 (Л)</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2410×1300</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5">
+        <f>2.41*1.3</f>
+        <v/>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="5">
+        <f>ROUND(G57/F57*I57,2)</f>
+        <v/>
+      </c>
+      <c r="K57" s="3">
+        <f>F57-I57</f>
+        <v/>
+      </c>
+      <c r="L57" s="3">
+        <f>MAX(0,N(H57)-F57)</f>
+        <v/>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>1 — КП лит. В</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>Д36 (Л)</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>2100×1400</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="14">
+        <f>2.1*1.4</f>
+        <v/>
+      </c>
+      <c r="H58" s="13" t="n"/>
+      <c r="I58" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="14">
+        <f>ROUND(G58/F58*I58,2)</f>
+        <v/>
+      </c>
+      <c r="K58" s="13">
+        <f>F58-I58</f>
+        <v/>
+      </c>
+      <c r="L58" s="13">
+        <f>MAX(0,N(H58)-F58)</f>
+        <v/>
+      </c>
+      <c r="M58" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Д37 (Л)</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>2100×1400</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="14">
+        <f>2.1*1.4</f>
+        <v/>
+      </c>
+      <c r="H59" s="13" t="n"/>
+      <c r="I59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="14">
+        <f>ROUND(G59/F59*I59,2)</f>
+        <v/>
+      </c>
+      <c r="K59" s="13">
+        <f>F59-I59</f>
+        <v/>
+      </c>
+      <c r="L59" s="13">
+        <f>MAX(0,N(H59)-F59)</f>
+        <v/>
+      </c>
+      <c r="M59" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Д17* (П)</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2410×1300</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" s="5">
+        <f>2.41*1.3*3</f>
+        <v/>
+      </c>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" s="5">
+        <f>ROUND(G60/F60*I60,2)</f>
+        <v/>
+      </c>
+      <c r="K60" s="3">
+        <f>F60-I60</f>
+        <v/>
+      </c>
+      <c r="L60" s="3">
+        <f>MAX(0,N(H60)-F60)</f>
+        <v/>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>3 — излишек КП лит. А</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Д18 (П)</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>2100×1000</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="n">
+        <v>107</v>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="14">
+        <f>2.1*1</f>
+        <v/>
+      </c>
+      <c r="H61" s="13" t="n"/>
+      <c r="I61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="14">
+        <f>ROUND(G61/F61*I61,2)</f>
+        <v/>
+      </c>
+      <c r="K61" s="13">
+        <f>F61-I61</f>
+        <v/>
+      </c>
+      <c r="L61" s="13">
+        <f>MAX(0,N(H61)-F61)</f>
+        <v/>
+      </c>
+      <c r="M61" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>Д22 (П)</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>2100×1300</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>109</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="14">
+        <f>2.1*1.3</f>
+        <v/>
+      </c>
+      <c r="H62" s="13" t="n"/>
+      <c r="I62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="14">
+        <f>ROUND(G62/F62*I62,2)</f>
+        <v/>
+      </c>
+      <c r="K62" s="13">
+        <f>F62-I62</f>
+        <v/>
+      </c>
+      <c r="L62" s="13">
+        <f>MAX(0,N(H62)-F62)</f>
+        <v/>
+      </c>
+      <c r="M62" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>Д35 (Л)</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>2410×1300</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>111</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="14">
+        <f>2.41*1.3*3</f>
+        <v/>
+      </c>
+      <c r="H63" s="13" t="n"/>
+      <c r="I63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="14">
+        <f>ROUND(G63/F63*I63,2)</f>
+        <v/>
+      </c>
+      <c r="K63" s="13">
+        <f>F63-I63</f>
+        <v/>
+      </c>
+      <c r="L63" s="13">
+        <f>MAX(0,N(H63)-F63)</f>
+        <v/>
+      </c>
+      <c r="M63" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Д37 (Л)</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>2100×1400</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>113</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="14">
+        <f>2.1*1.4</f>
+        <v/>
+      </c>
+      <c r="H64" s="13" t="n"/>
+      <c r="I64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="14">
+        <f>ROUND(G64/F64*I64,2)</f>
+        <v/>
+      </c>
+      <c r="K64" s="13">
+        <f>F64-I64</f>
+        <v/>
+      </c>
+      <c r="L64" s="13">
+        <f>MAX(0,N(H64)-F64)</f>
+        <v/>
+      </c>
+      <c r="M64" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Д17* (П)</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2410×1300</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G65" s="5">
+        <f>2.41*1.3*6</f>
+        <v/>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J65" s="5">
+        <f>ROUND(G65/F65*I65,2)</f>
+        <v/>
+      </c>
+      <c r="K65" s="3">
+        <f>F65-I65</f>
+        <v/>
+      </c>
+      <c r="L65" s="3">
+        <f>MAX(0,N(H65)-F65)</f>
+        <v/>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>4 — КП лит. Д; 1 — излишек КП лит. А; 1 — излишек КП лит. Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>Д18 (П)</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>2100×1000</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>127</v>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="14">
+        <f>2.1*1</f>
+        <v/>
+      </c>
+      <c r="H66" s="13" t="n"/>
+      <c r="I66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="14">
+        <f>ROUND(G66/F66*I66,2)</f>
+        <v/>
+      </c>
+      <c r="K66" s="13">
+        <f>F66-I66</f>
+        <v/>
+      </c>
+      <c r="L66" s="13">
+        <f>MAX(0,N(H66)-F66)</f>
+        <v/>
+      </c>
+      <c r="M66" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>Д19 (П)</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>2100×1000</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="14">
+        <f>2.1*1</f>
+        <v/>
+      </c>
+      <c r="H67" s="13" t="n"/>
+      <c r="I67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="14">
+        <f>ROUND(G67/F67*I67,2)</f>
+        <v/>
+      </c>
+      <c r="K67" s="13">
+        <f>F67-I67</f>
+        <v/>
+      </c>
+      <c r="L67" s="13">
+        <f>MAX(0,N(H67)-F67)</f>
+        <v/>
+      </c>
+      <c r="M67" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Д22 (П)</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>2100×1300</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="14">
+        <f>2.1*1.3</f>
+        <v/>
+      </c>
+      <c r="H68" s="13" t="n"/>
+      <c r="I68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="14">
+        <f>ROUND(G68/F68*I68,2)</f>
+        <v/>
+      </c>
+      <c r="K68" s="13">
+        <f>F68-I68</f>
+        <v/>
+      </c>
+      <c r="L68" s="13">
+        <f>MAX(0,N(H68)-F68)</f>
+        <v/>
+      </c>
+      <c r="M68" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Д35 (Л)</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>2410×1300</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="14">
+        <f>2.41*1.3</f>
+        <v/>
+      </c>
+      <c r="H69" s="13" t="n"/>
+      <c r="I69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="14">
+        <f>ROUND(G69/F69*I69,2)</f>
+        <v/>
+      </c>
+      <c r="K69" s="13">
+        <f>F69-I69</f>
+        <v/>
+      </c>
+      <c r="L69" s="13">
+        <f>MAX(0,N(H69)-F69)</f>
+        <v/>
+      </c>
+      <c r="M69" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="n"/>
+      <c r="E70" s="13" t="n"/>
+      <c r="F70" s="13" t="n"/>
+      <c r="G70" s="14" t="n"/>
+      <c r="H70" s="13" t="n"/>
+      <c r="I70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="13" t="n"/>
+      <c r="M70" s="15" t="inlineStr">
+        <is>
+          <t>3 шт. из КП лит. Б — свободных строк ВДЦ Д17* больше нет, закрыть нельзя</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="n"/>
+      <c r="E71" s="13" t="n"/>
+      <c r="F71" s="13" t="n"/>
+      <c r="G71" s="14" t="n"/>
+      <c r="H71" s="13" t="n"/>
+      <c r="I71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="13" t="n"/>
+      <c r="M71" s="15" t="inlineStr">
+        <is>
+          <t>1 шт. из КП лит. В — свободных строк ВДЦ Д17* больше нет, закрыть нельзя</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Итого двери</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="8">
+        <f>SUM(F47:F71)</f>
+        <v/>
+      </c>
+      <c r="G72" s="10">
+        <f>SUM(G47:G71)</f>
+        <v/>
+      </c>
+      <c r="H72" s="8">
+        <f>SUM(H47:H71)</f>
+        <v/>
+      </c>
+      <c r="I72" s="8">
+        <f>SUM(I47:I71)</f>
+        <v/>
+      </c>
+      <c r="J72" s="10">
+        <f>SUM(J47:J71)</f>
+        <v/>
+      </c>
+      <c r="K72" s="8">
+        <f>SUM(K47:K71)</f>
+        <v/>
+      </c>
+      <c r="L72" s="8">
+        <f>SUM(L47:L71)</f>
+        <v/>
+      </c>
+      <c r="M72" s="11" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="n"/>
+      <c r="B74" s="16" t="n"/>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>ВСЕГО к закрытию (витражи + двери)</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="n"/>
+      <c r="E74" s="16" t="n"/>
+      <c r="F74" s="16" t="n"/>
+      <c r="G74" s="16" t="n"/>
+      <c r="H74" s="16" t="n"/>
+      <c r="I74" s="17">
+        <f>I43+I72</f>
+        <v/>
+      </c>
+      <c r="J74" s="18">
+        <f>J43+J72</f>
+        <v/>
+      </c>
+      <c r="K74" s="16" t="n"/>
+      <c r="L74" s="16" t="n"/>
+      <c r="M74" s="16" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B43:J43"/>
-    <mergeCell ref="B44:J44"/>
+  <mergeCells count="1">
+    <mergeCell ref="C74:H74"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
@@ -3763,17 +5034,17 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Литер А</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="19" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="19" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="22" t="n"/>
+      <c r="H4" s="20" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -3812,11 +5083,11 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Вн-8</t>
+          <t>Вн-6 (устан. в лит. Г, КП 1-18 №6)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2600</v>
+        <v>4200</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4820</v>
@@ -3829,7 +5100,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>12.34</v>
+        <v>19.82</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -3843,11 +5114,11 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Вн-14</t>
+          <t>Вн-8</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2485</v>
+        <v>2600</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>4820</v>
@@ -3860,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>11.14</v>
+        <v>12.34</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -3874,11 +5145,11 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Вн-15</t>
+          <t>Вн-14</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1400</v>
+        <v>2485</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>4820</v>
@@ -3891,7 +5162,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>5.62</v>
+        <v>11.14</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -3905,95 +5176,95 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Вн-22</t>
+          <t>Вн-15</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2150</v>
+        <v>1400</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2720</v>
+        <v>4820</v>
       </c>
       <c r="E9" s="4">
         <f>ROUND(G9/F9,2)</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2150</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2720</v>
+      </c>
+      <c r="E10" s="4">
+        <f>ROUND(G10/F10,2)</f>
+        <v/>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>28.57</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Итого литер А</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="8">
-        <f>SUM(F5:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="10">
-        <f>SUM(G5:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="8">
+        <f>SUM(F5:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="10">
+        <f>SUM(G5:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Литер Б</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="19" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E12" s="4">
-        <f>ROUND(G12/F12,2)</f>
-        <v/>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -4001,11 +5272,11 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Вн-15</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1400</v>
+        <v>4200</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>4820</v>
@@ -4015,10 +5286,10 @@
         <v/>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>6</v>
+        <v>58.46</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -4032,7 +5303,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-6 (устан. в лит. Г, КП 1-18 №8)</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -4049,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>19.49</v>
+        <v>21.36</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -4063,11 +5334,11 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Вн-18</t>
+          <t>Вн-15</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2600</v>
+        <v>1400</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>4820</v>
@@ -4080,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>11.9</v>
+        <v>6</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -4094,126 +5365,126 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Вн-22</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2150</v>
+        <v>4200</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2720</v>
+        <v>4820</v>
       </c>
       <c r="E16" s="4">
         <f>ROUND(G16/F16,2)</f>
         <v/>
       </c>
       <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Вн-18</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E17" s="4">
+        <f>ROUND(G17/F17,2)</f>
+        <v/>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2150</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2720</v>
+      </c>
+      <c r="E18" s="4">
+        <f>ROUND(G18/F18,2)</f>
+        <v/>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>28.57</v>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Итого литер Б</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="8">
-        <f>SUM(F12:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="10">
-        <f>SUM(G12:G16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="8">
+        <f>SUM(F13:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>SUM(G13:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Литер В</t>
         </is>
       </c>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="19" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E19" s="4">
-        <f>ROUND(G19/F19,2)</f>
-        <v/>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Вн-13</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E20" s="4">
-        <f>ROUND(G20/F20,2)</f>
-        <v/>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="20" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -4221,11 +5492,11 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Вн-16</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>4820</v>
@@ -4235,10 +5506,10 @@
         <v/>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>18.57</v>
+        <v>19.63</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -4252,11 +5523,11 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Вн-17</t>
+          <t>Вн-13</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4200</v>
+        <v>3200</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>4820</v>
@@ -4269,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>19.68</v>
+        <v>14.74</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -4283,11 +5554,11 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Вн-19</t>
+          <t>Вн-16</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>4820</v>
@@ -4297,10 +5568,10 @@
         <v/>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>24.67</v>
+        <v>18.57</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -4314,14 +5585,14 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Вн-22</t>
+          <t>Вн-17</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2150</v>
+        <v>4200</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2720</v>
+        <v>4820</v>
       </c>
       <c r="E24" s="4">
         <f>ROUND(G24/F24,2)</f>
@@ -4331,109 +5602,109 @@
         <v>1</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E25" s="4">
+        <f>ROUND(G25/F25,2)</f>
+        <v/>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>-6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2150</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2720</v>
+      </c>
+      <c r="E26" s="4">
+        <f>ROUND(G26/F26,2)</f>
+        <v/>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>5.71</v>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Итого литер В</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="8">
-        <f>SUM(F19:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="10">
-        <f>SUM(G19:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="8">
+        <f>SUM(F21:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="10">
+        <f>SUM(G21:G26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n"/>
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Литер Г</t>
         </is>
       </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="19" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E27" s="4">
-        <f>ROUND(G27/F27,2)</f>
-        <v/>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6 (из КП лит. А, 4130)</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E28" s="4">
-        <f>ROUND(G28/F28,2)</f>
-        <v/>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>-6.000</t>
-        </is>
-      </c>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="20" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -4441,7 +5712,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Вн-6 (из КП лит. Б, 4450)</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -4458,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>21.36</v>
+        <v>20.45</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -4663,28 +5934,28 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="8">
-        <f>SUM(F27:F35)</f>
+        <f>SUM(F29:F35)</f>
         <v/>
       </c>
       <c r="G36" s="10">
-        <f>SUM(G27:G35)</f>
+        <f>SUM(G29:G35)</f>
         <v/>
       </c>
       <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>Литер Д</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="20" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="21" t="n"/>
-      <c r="H37" s="19" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="21" t="n"/>
+      <c r="F37" s="20" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="20" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -4832,7 +6103,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>ВСЕГО</t>
         </is>
@@ -4840,29 +6111,761 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="4" t="n"/>
-      <c r="F43" s="22">
-        <f>F10+F17+F25+F36+F42</f>
-        <v/>
-      </c>
-      <c r="G43" s="23">
-        <f>G10+G17+G25+G36+G42</f>
+      <c r="F43" s="23">
+        <f>F11+F19+F27+F36+F42</f>
+        <v/>
+      </c>
+      <c r="G43" s="24">
+        <f>G11+G19+G27+G36+G42</f>
         <v/>
       </c>
       <c r="H43" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B20:H20"/>
     <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Двери в составе витражей по КП от 13.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Марка двери — по чертежу у витража; двери Вн-22 (КП №15, 11 шт.) распределены как сами Вн-22: А5, Б5, В1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Литер</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Витраж</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Марка двери</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>КП</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Кол-во, шт</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Площадь по размерам КП, м²</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Площадь в КП, м²</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>№9 А</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="4">
+        <f>ROUND(F4*G4*H4/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Вн-14</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>№9 А</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4">
+        <f>ROUND(F5*G5*H5/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>№9 А</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1106</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <f>ROUND(F6*G6*H6/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>№15 Вн-22</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>2193</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4">
+        <f>ROUND(F7*G7*H7/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>14.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>№11 Б</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="4">
+        <f>ROUND(F8*G8*H8/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Вн-15</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>№11 Б</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4">
+        <f>ROUND(F9*G9*H9/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Вн-18</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>№11 Б</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4">
+        <f>ROUND(F10*G10*H10/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>№15 Вн-22</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2193</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="4">
+        <f>ROUND(F11*G11*H11/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>14.65</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>№12 В</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4">
+        <f>ROUND(F12*G12*H12/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Вн-16</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Д35</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>№12 В</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1176</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <f>ROUND(F13*G13*H13/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Вн-19</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>№12 В</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="4">
+        <f>ROUND(F14*G14*H14/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>№15 Вн-22</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>2193</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
+        <f>ROUND(F15*G15*H15/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Вн-6</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>№14 (Д)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="4">
+        <f>ROUND(F16*G16*H16/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Вн-9</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>№14 (Д)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4">
+        <f>ROUND(F17*G17*H17/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Вн-10</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Д17*</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>№14 (Д)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>2433</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4">
+        <f>ROUND(F18*G18*H18/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="8">
+        <f>SUM(H4:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="25">
+        <f>SUM(I4:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="25">
+        <f>SUM(J4:J18)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4882,7 +6885,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Витражи на чертежах, входящие в КП (координаты — точка выноски, мм)</t>
         </is>
@@ -4961,10 +6964,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="26" t="n">
         <v>129957</v>
       </c>
-      <c r="G4" s="25" t="n">
+      <c r="G4" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4997,10 +7000,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="26" t="n">
         <v>140357</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -5033,10 +7036,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <v>150757</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -5065,10 +7068,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <v>144757</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -5101,10 +7104,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <v>134299</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -5137,10 +7140,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <v>136557</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -5173,10 +7176,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>118357</v>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5209,10 +7212,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <v>96357</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5245,10 +7248,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="26" t="n">
         <v>106757</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5281,10 +7284,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <v>103802</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="26" t="n">
         <v>-240189</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -5313,10 +7316,10 @@
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="26" t="n">
         <v>111957</v>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -5349,10 +7352,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F15" s="26" t="n">
         <v>101557</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5385,10 +7388,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F16" s="25" t="n">
+      <c r="F16" s="26" t="n">
         <v>85312</v>
       </c>
-      <c r="G16" s="25" t="n">
+      <c r="G16" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -5417,10 +7420,10 @@
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="26" t="n">
         <v>62827</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -5453,10 +7456,10 @@
           <t>Д35</t>
         </is>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="26" t="n">
         <v>75379</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -5489,10 +7492,10 @@
           <t>Д35</t>
         </is>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <v>58219</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <v>-240238</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -5525,10 +7528,10 @@
           <t>Д35</t>
         </is>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="26" t="n">
         <v>60392</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="26" t="n">
         <v>-240238</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -5561,10 +7564,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="26" t="n">
         <v>78410</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="26" t="n">
         <v>-240123</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5593,10 +7596,10 @@
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="25" t="n">
+      <c r="F22" s="26" t="n">
         <v>66863</v>
       </c>
-      <c r="G22" s="25" t="n">
+      <c r="G22" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5629,10 +7632,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F23" s="25" t="n">
+      <c r="F23" s="26" t="n">
         <v>72058</v>
       </c>
-      <c r="G23" s="25" t="n">
+      <c r="G23" s="26" t="n">
         <v>-240209</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5665,15 +7668,15 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F24" s="25" t="n">
+      <c r="F24" s="26" t="n">
         <v>38425</v>
       </c>
-      <c r="G24" s="25" t="n">
+      <c r="G24" s="26" t="n">
         <v>-227349</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>1 по лит. Г, 2 записаны в лит. А и Б</t>
         </is>
       </c>
     </row>
@@ -5701,15 +7704,15 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="F25" s="26" t="n">
         <v>43228</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="26" t="n">
         <v>-240130</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>1 по лит. Г, 2 записаны в лит. А и Б</t>
         </is>
       </c>
     </row>
@@ -5737,15 +7740,15 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F26" s="25" t="n">
+      <c r="F26" s="26" t="n">
         <v>53628</v>
       </c>
-      <c r="G26" s="25" t="n">
+      <c r="G26" s="26" t="n">
         <v>-240130</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>1 по лит. Г, 2 записаны в лит. А и Б</t>
         </is>
       </c>
     </row>
@@ -5773,10 +7776,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="F27" s="26" t="n">
         <v>38425</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="26" t="n">
         <v>-203499</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -5805,10 +7808,10 @@
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="25" t="n">
+      <c r="F28" s="26" t="n">
         <v>38425</v>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="26" t="n">
         <v>-213004</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -5841,10 +7844,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="F29" s="26" t="n">
         <v>38425</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="26" t="n">
         <v>-217364</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -5873,10 +7876,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="25" t="n">
+      <c r="F30" s="26" t="n">
         <v>38425</v>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="26" t="n">
         <v>-237749</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -5905,10 +7908,10 @@
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="25" t="n">
+      <c r="F31" s="26" t="n">
         <v>47835</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="26" t="n">
         <v>-240108</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -5937,10 +7940,10 @@
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="25" t="n">
+      <c r="F32" s="26" t="n">
         <v>38425</v>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="26" t="n">
         <v>-221999</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -5969,10 +7972,10 @@
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="25" t="n">
+      <c r="F33" s="26" t="n">
         <v>38425</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="26" t="n">
         <v>-231909</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -6001,10 +8004,10 @@
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="25" t="n">
+      <c r="F34" s="26" t="n">
         <v>38538</v>
       </c>
-      <c r="G34" s="25" t="n">
+      <c r="G34" s="26" t="n">
         <v>-179543</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -6033,10 +8036,10 @@
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="25" t="n">
+      <c r="F35" s="26" t="n">
         <v>38538</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="26" t="n">
         <v>-169143</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -6065,10 +8068,10 @@
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="25" t="n">
+      <c r="F36" s="26" t="n">
         <v>38538</v>
       </c>
-      <c r="G36" s="25" t="n">
+      <c r="G36" s="26" t="n">
         <v>-174933</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -6101,10 +8104,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F37" s="25" t="n">
+      <c r="F37" s="26" t="n">
         <v>38538</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G37" s="26" t="n">
         <v>-195128</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -6133,10 +8136,10 @@
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="25" t="n">
+      <c r="F38" s="26" t="n">
         <v>38538</v>
       </c>
-      <c r="G38" s="25" t="n">
+      <c r="G38" s="26" t="n">
         <v>-189943</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -6169,10 +8172,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F39" s="25" t="n">
+      <c r="F39" s="26" t="n">
         <v>112864</v>
       </c>
-      <c r="G39" s="25" t="n">
+      <c r="G39" s="26" t="n">
         <v>2824</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -6205,10 +8208,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F40" s="25" t="n">
+      <c r="F40" s="26" t="n">
         <v>106184</v>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G40" s="26" t="n">
         <v>2691</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -6241,10 +8244,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F41" s="25" t="n">
+      <c r="F41" s="26" t="n">
         <v>100327</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="26" t="n">
         <v>2943</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -6277,10 +8280,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F42" s="25" t="n">
+      <c r="F42" s="26" t="n">
         <v>93122</v>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="26" t="n">
         <v>2886</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -6313,10 +8316,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F43" s="25" t="n">
+      <c r="F43" s="26" t="n">
         <v>86467</v>
       </c>
-      <c r="G43" s="25" t="n">
+      <c r="G43" s="26" t="n">
         <v>2773</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -6349,10 +8352,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F44" s="25" t="n">
+      <c r="F44" s="26" t="n">
         <v>79305</v>
       </c>
-      <c r="G44" s="25" t="n">
+      <c r="G44" s="26" t="n">
         <v>3099</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -6385,10 +8388,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F45" s="25" t="n">
+      <c r="F45" s="26" t="n">
         <v>72445</v>
       </c>
-      <c r="G45" s="25" t="n">
+      <c r="G45" s="26" t="n">
         <v>3048</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -6421,10 +8424,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F46" s="25" t="n">
+      <c r="F46" s="26" t="n">
         <v>64804</v>
       </c>
-      <c r="G46" s="25" t="n">
+      <c r="G46" s="26" t="n">
         <v>2917</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6457,10 +8460,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F47" s="25" t="n">
+      <c r="F47" s="26" t="n">
         <v>59604</v>
       </c>
-      <c r="G47" s="25" t="n">
+      <c r="G47" s="26" t="n">
         <v>2985</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -6493,10 +8496,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F48" s="25" t="n">
+      <c r="F48" s="26" t="n">
         <v>53064</v>
       </c>
-      <c r="G48" s="25" t="n">
+      <c r="G48" s="26" t="n">
         <v>2948</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -6529,10 +8532,10 @@
           <t>Д35</t>
         </is>
       </c>
-      <c r="F49" s="25" t="n">
+      <c r="F49" s="26" t="n">
         <v>45611</v>
       </c>
-      <c r="G49" s="25" t="n">
+      <c r="G49" s="26" t="n">
         <v>3036</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -6565,10 +8568,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F50" s="25" t="n">
+      <c r="F50" s="26" t="n">
         <v>39399</v>
       </c>
-      <c r="G50" s="25" t="n">
+      <c r="G50" s="26" t="n">
         <v>2969</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -6601,10 +8604,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F51" s="25" t="n">
+      <c r="F51" s="26" t="n">
         <v>33459</v>
       </c>
-      <c r="G51" s="25" t="n">
+      <c r="G51" s="26" t="n">
         <v>3046</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -6637,10 +8640,10 @@
           <t>Д17*</t>
         </is>
       </c>
-      <c r="F52" s="25" t="n">
+      <c r="F52" s="26" t="n">
         <v>26027</v>
       </c>
-      <c r="G52" s="25" t="n">
+      <c r="G52" s="26" t="n">
         <v>2978</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -6654,7 +8657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7170,13 +9173,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7193,7 +9196,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Сверка с КП. В спецификации площадь по КП = ширина × высота из КП (как в таблице заказчика)</t>
         </is>
@@ -7207,7 +9210,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>1. Позиции КП на витражи</t>
         </is>
@@ -7249,17 +9252,17 @@
           <t>Кол-во, шт</t>
         </is>
       </c>
-      <c r="H4" s="26" t="inlineStr">
+      <c r="H4" s="27" t="inlineStr">
         <is>
           <t>Площадь по размерам КП, м²</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
         <is>
           <t>Площадь в КП, м²</t>
         </is>
       </c>
-      <c r="J4" s="26" t="inlineStr">
+      <c r="J4" s="27" t="inlineStr">
         <is>
           <t>Разница, м²</t>
         </is>
@@ -8599,7 +10602,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Г (перенос из А)</t>
+          <t>А (установлен в лит. Г)</t>
         </is>
       </c>
     </row>
@@ -8685,7 +10688,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Г (перенос из Б)</t>
+          <t>Б (установлен в лит. Г)</t>
         </is>
       </c>
     </row>
@@ -9120,48 +11123,48 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="n"/>
+      <c r="A48" s="16" t="n"/>
       <c r="B48" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="27" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
       <c r="G48" s="8">
         <f>SUM(G5:G47)</f>
         <v/>
       </c>
-      <c r="H48" s="28">
+      <c r="H48" s="25">
         <f>SUM(H5:H47)</f>
         <v/>
       </c>
-      <c r="I48" s="28">
+      <c r="I48" s="25">
         <f>SUM(I5:I47)</f>
         <v/>
       </c>
-      <c r="J48" s="28">
+      <c r="J48" s="25">
         <f>SUM(J5:J47)</f>
         <v/>
       </c>
-      <c r="K48" s="27" t="n"/>
+      <c r="K48" s="16" t="n"/>
     </row>
     <row r="49">
-      <c r="H49" s="29" t="n"/>
-      <c r="I49" s="29" t="n"/>
-      <c r="J49" s="29" t="n"/>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="28" t="n"/>
+      <c r="J49" s="28" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>2. Двери к витражам (КП от 13.04.2026) — в спецификацию не добавлены, для справки</t>
         </is>
       </c>
-      <c r="H50" s="29" t="n"/>
-      <c r="I50" s="29" t="n"/>
-      <c r="J50" s="29" t="n"/>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="28" t="n"/>
+      <c r="J50" s="28" t="n"/>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -9199,17 +11202,17 @@
           <t>Кол-во, шт</t>
         </is>
       </c>
-      <c r="H51" s="26" t="inlineStr">
+      <c r="H51" s="27" t="inlineStr">
         <is>
           <t>Площадь по размерам, м²</t>
         </is>
       </c>
-      <c r="I51" s="26" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
         <is>
           <t>Площадь в КП, м²</t>
         </is>
       </c>
-      <c r="J51" s="29" t="n"/>
+      <c r="J51" s="28" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -9246,7 +11249,7 @@
       <c r="I52" s="4" t="n">
         <v>9.75</v>
       </c>
-      <c r="J52" s="29" t="n"/>
+      <c r="J52" s="28" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -9283,7 +11286,7 @@
       <c r="I53" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J53" s="29" t="n"/>
+      <c r="J53" s="28" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -9320,7 +11323,7 @@
       <c r="I54" s="4" t="n">
         <v>2.69</v>
       </c>
-      <c r="J54" s="29" t="n"/>
+      <c r="J54" s="28" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -9357,7 +11360,7 @@
       <c r="I55" s="4" t="n">
         <v>9.75</v>
       </c>
-      <c r="J55" s="29" t="n"/>
+      <c r="J55" s="28" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -9394,7 +11397,7 @@
       <c r="I56" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J56" s="29" t="n"/>
+      <c r="J56" s="28" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -9431,7 +11434,7 @@
       <c r="I57" s="4" t="n">
         <v>2.89</v>
       </c>
-      <c r="J57" s="29" t="n"/>
+      <c r="J57" s="28" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -9468,7 +11471,7 @@
       <c r="I58" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J58" s="29" t="n"/>
+      <c r="J58" s="28" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -9505,7 +11508,7 @@
       <c r="I59" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="J59" s="29" t="n"/>
+      <c r="J59" s="28" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -9542,7 +11545,7 @@
       <c r="I60" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J60" s="29" t="n"/>
+      <c r="J60" s="28" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -9579,7 +11582,7 @@
       <c r="I61" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J61" s="29" t="n"/>
+      <c r="J61" s="28" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -9616,7 +11619,7 @@
       <c r="I62" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="J62" s="29" t="n"/>
+      <c r="J62" s="28" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -9653,7 +11656,7 @@
       <c r="I63" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="J63" s="29" t="n"/>
+      <c r="J63" s="28" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -9690,862 +11693,32 @@
       <c r="I64" s="4" t="n">
         <v>32.23</v>
       </c>
-      <c r="J64" s="29" t="n"/>
+      <c r="J64" s="28" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="27" t="n"/>
+      <c r="A65" s="16" t="n"/>
       <c r="B65" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C65" s="27" t="n"/>
-      <c r="D65" s="27" t="n"/>
-      <c r="E65" s="27" t="n"/>
-      <c r="F65" s="27" t="n"/>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="16" t="n"/>
+      <c r="F65" s="16" t="n"/>
       <c r="G65" s="8">
         <f>SUM(G52:G64)</f>
         <v/>
       </c>
-      <c r="H65" s="28">
+      <c r="H65" s="25">
         <f>SUM(H52:H64)</f>
         <v/>
       </c>
-      <c r="I65" s="28">
+      <c r="I65" s="25">
         <f>SUM(I52:I64)</f>
         <v/>
       </c>
-      <c r="J65" s="29" t="n"/>
-    </row>
-    <row r="66">
-      <c r="H66" s="29" t="n"/>
-      <c r="I66" s="29" t="n"/>
-      <c r="J66" s="29" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="24" t="inlineStr">
-        <is>
-          <t>3. Что поправлено в спецификации</t>
-        </is>
-      </c>
-      <c r="H67" s="29" t="n"/>
-      <c r="I67" s="29" t="n"/>
-      <c r="J67" s="29" t="n"/>
-    </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Литер</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Марка</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Было, м²</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Стало (по КП), м²</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Разница, м²</t>
-        </is>
-      </c>
-      <c r="H68" s="29" t="n"/>
-      <c r="I68" s="29" t="n"/>
-      <c r="J68" s="29" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>59.68</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="F69" s="4">
-        <f>ROUND(E69-D69,2)</f>
-        <v/>
-      </c>
-      <c r="H69" s="29" t="n"/>
-      <c r="I69" s="29" t="n"/>
-      <c r="J69" s="29" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Вн-8</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="F70" s="4">
-        <f>ROUND(E70-D70,2)</f>
-        <v/>
-      </c>
-      <c r="H70" s="29" t="n"/>
-      <c r="I70" s="29" t="n"/>
-      <c r="J70" s="29" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Вн-14</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="F71" s="4">
-        <f>ROUND(E71-D71,2)</f>
-        <v/>
-      </c>
-      <c r="H71" s="29" t="n"/>
-      <c r="I71" s="29" t="n"/>
-      <c r="J71" s="29" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Вн-15</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="F72" s="4">
-        <f>ROUND(E72-D72,2)</f>
-        <v/>
-      </c>
-      <c r="H72" s="29" t="n"/>
-      <c r="I72" s="29" t="n"/>
-      <c r="J72" s="29" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="F73" s="4">
-        <f>ROUND(E73-D73,2)</f>
-        <v/>
-      </c>
-      <c r="H73" s="29" t="n"/>
-      <c r="I73" s="29" t="n"/>
-      <c r="J73" s="29" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>59.86</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="F74" s="4">
-        <f>ROUND(E74-D74,2)</f>
-        <v/>
-      </c>
-      <c r="H74" s="29" t="n"/>
-      <c r="I74" s="29" t="n"/>
-      <c r="J74" s="29" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Вн-15</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F75" s="4">
-        <f>ROUND(E75-D75,2)</f>
-        <v/>
-      </c>
-      <c r="H75" s="29" t="n"/>
-      <c r="I75" s="29" t="n"/>
-      <c r="J75" s="29" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>Вн-17</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="F76" s="4">
-        <f>ROUND(E76-D76,2)</f>
-        <v/>
-      </c>
-      <c r="H76" s="29" t="n"/>
-      <c r="I76" s="29" t="n"/>
-      <c r="J76" s="29" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Вн-18</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F77" s="4">
-        <f>ROUND(E77-D77,2)</f>
-        <v/>
-      </c>
-      <c r="H77" s="29" t="n"/>
-      <c r="I77" s="29" t="n"/>
-      <c r="J77" s="29" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="F78" s="4">
-        <f>ROUND(E78-D78,2)</f>
-        <v/>
-      </c>
-      <c r="H78" s="29" t="n"/>
-      <c r="I78" s="29" t="n"/>
-      <c r="J78" s="29" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="F79" s="4">
-        <f>ROUND(E79-D79,2)</f>
-        <v/>
-      </c>
-      <c r="H79" s="29" t="n"/>
-      <c r="I79" s="29" t="n"/>
-      <c r="J79" s="29" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>Вн-13</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="F80" s="4">
-        <f>ROUND(E80-D80,2)</f>
-        <v/>
-      </c>
-      <c r="H80" s="29" t="n"/>
-      <c r="I80" s="29" t="n"/>
-      <c r="J80" s="29" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>Вн-16</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="F81" s="4">
-        <f>ROUND(E81-D81,2)</f>
-        <v/>
-      </c>
-      <c r="H81" s="29" t="n"/>
-      <c r="I81" s="29" t="n"/>
-      <c r="J81" s="29" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>Вн-17</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>19.68</v>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>19.68</v>
-      </c>
-      <c r="F82" s="4">
-        <f>ROUND(E82-D82,2)</f>
-        <v/>
-      </c>
-      <c r="H82" s="29" t="n"/>
-      <c r="I82" s="29" t="n"/>
-      <c r="J82" s="29" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>Вн-19</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>24.67</v>
-      </c>
-      <c r="E83" s="4" t="n">
-        <v>24.67</v>
-      </c>
-      <c r="F83" s="4">
-        <f>ROUND(E83-D83,2)</f>
-        <v/>
-      </c>
-      <c r="H83" s="29" t="n"/>
-      <c r="I83" s="29" t="n"/>
-      <c r="J83" s="29" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>Вн-22</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="F84" s="4">
-        <f>ROUND(E84-D84,2)</f>
-        <v/>
-      </c>
-      <c r="H84" s="29" t="n"/>
-      <c r="I84" s="29" t="n"/>
-      <c r="J84" s="29" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>61.63</v>
-      </c>
-      <c r="F85" s="4">
-        <f>ROUND(E85-D85,2)</f>
-        <v/>
-      </c>
-      <c r="H85" s="29" t="n"/>
-      <c r="I85" s="29" t="n"/>
-      <c r="J85" s="29" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>Вн-10</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="F86" s="4">
-        <f>ROUND(E86-D86,2)</f>
-        <v/>
-      </c>
-      <c r="H86" s="29" t="n"/>
-      <c r="I86" s="29" t="n"/>
-      <c r="J86" s="29" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>Вн-11</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="E87" s="4" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="F87" s="4">
-        <f>ROUND(E87-D87,2)</f>
-        <v/>
-      </c>
-      <c r="H87" s="29" t="n"/>
-      <c r="I87" s="29" t="n"/>
-      <c r="J87" s="29" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>Вн-12</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E88" s="4" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F88" s="4">
-        <f>ROUND(E88-D88,2)</f>
-        <v/>
-      </c>
-      <c r="H88" s="29" t="n"/>
-      <c r="I88" s="29" t="n"/>
-      <c r="J88" s="29" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>Вн-17</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="F89" s="4">
-        <f>ROUND(E89-D89,2)</f>
-        <v/>
-      </c>
-      <c r="H89" s="29" t="n"/>
-      <c r="I89" s="29" t="n"/>
-      <c r="J89" s="29" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>Вн-20</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="F90" s="4">
-        <f>ROUND(E90-D90,2)</f>
-        <v/>
-      </c>
-      <c r="H90" s="29" t="n"/>
-      <c r="I90" s="29" t="n"/>
-      <c r="J90" s="29" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>Вн-21</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="F91" s="4">
-        <f>ROUND(E91-D91,2)</f>
-        <v/>
-      </c>
-      <c r="H91" s="29" t="n"/>
-      <c r="I91" s="29" t="n"/>
-      <c r="J91" s="29" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Д</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>Вн-6</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>39.98</v>
-      </c>
-      <c r="E92" s="4" t="n">
-        <v>39.98</v>
-      </c>
-      <c r="F92" s="4">
-        <f>ROUND(E92-D92,2)</f>
-        <v/>
-      </c>
-      <c r="H92" s="29" t="n"/>
-      <c r="I92" s="29" t="n"/>
-      <c r="J92" s="29" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>Д</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>Вн-7</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="F93" s="4">
-        <f>ROUND(E93-D93,2)</f>
-        <v/>
-      </c>
-      <c r="H93" s="29" t="n"/>
-      <c r="I93" s="29" t="n"/>
-      <c r="J93" s="29" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>Д</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>Вн-9</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>19.68</v>
-      </c>
-      <c r="E94" s="4" t="n">
-        <v>19.68</v>
-      </c>
-      <c r="F94" s="4">
-        <f>ROUND(E94-D94,2)</f>
-        <v/>
-      </c>
-      <c r="H94" s="29" t="n"/>
-      <c r="I94" s="29" t="n"/>
-      <c r="J94" s="29" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Д</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>Вн-17</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="F95" s="4">
-        <f>ROUND(E95-D95,2)</f>
-        <v/>
-      </c>
-      <c r="H95" s="29" t="n"/>
-      <c r="I95" s="29" t="n"/>
-      <c r="J95" s="29" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="27" t="n"/>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="C96" s="27" t="n"/>
-      <c r="D96" s="28">
-        <f>SUM(D69:D95)</f>
-        <v/>
-      </c>
-      <c r="E96" s="28">
-        <f>SUM(E69:E95)</f>
-        <v/>
-      </c>
-      <c r="F96" s="28">
-        <f>SUM(F69:F95)</f>
-        <v/>
-      </c>
-      <c r="H96" s="29" t="n"/>
-      <c r="I96" s="29" t="n"/>
-      <c r="J96" s="29" t="n"/>
+      <c r="J65" s="28" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -1453,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3566,7 +3566,7 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>2. Двери (КП от 13.04.2026; марка — по чертежу у витража). Излишек КП одного литера закрывает свободные строки ВДЦ других литеров</t>
+          <t>2. Двери (КП от 13.04.2026: в КП указаны литер и витраж; марка ВДЦ — по типу и размеру двери из КП)</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>По КП (свой литер), шт</t>
+          <t>По КП, шт</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3638,55 +3638,55 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="A47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>Д17* (П)</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>2410×1300</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="14">
         <f>2.41*1.3*6</f>
         <v/>
       </c>
-      <c r="H47" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" s="5">
+      <c r="H47" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" s="14">
         <f>ROUND(G47/F47*I47,2)</f>
         <v/>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="13">
         <f>F47-I47</f>
         <v/>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="13">
         <f>MAX(0,N(H47)-F47)</f>
         <v/>
       </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>6 — КП лит. А</t>
+      <c r="M47" s="15" t="inlineStr">
+        <is>
+          <t>КП: Вн-6 — 3, Вн-14 — 1</t>
         </is>
       </c>
     </row>
@@ -3793,106 +3793,108 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="n">
+      <c r="A50" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Д22 (П)</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>2100×1300</t>
         </is>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="F50" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="14">
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5">
         <f>2.1*1.3</f>
         <v/>
       </c>
-      <c r="H50" s="13" t="n"/>
-      <c r="I50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="14">
+      <c r="H50" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="5">
         <f>ROUND(G50/F50*I50,2)</f>
         <v/>
       </c>
-      <c r="K50" s="13">
+      <c r="K50" s="3">
         <f>F50-I50</f>
         <v/>
       </c>
-      <c r="L50" s="13">
+      <c r="L50" s="3">
         <f>MAX(0,N(H50)-F50)</f>
         <v/>
       </c>
-      <c r="M50" s="15" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>КП: Вн-22 — 5; сверх ВДЦ 4 шт.; на чертеже у Вн-22 стоит марка Д-17*, по размеру КП (1336×2193) это Д22</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>Д17* (П)</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>2410×1300</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="13" t="n">
         <v>57</v>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F51" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="14">
         <f>2.41*1.3*6</f>
         <v/>
       </c>
-      <c r="H51" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" s="5">
+      <c r="H51" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I51" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="14">
         <f>ROUND(G51/F51*I51,2)</f>
         <v/>
       </c>
-      <c r="K51" s="3">
+      <c r="K51" s="13">
         <f>F51-I51</f>
         <v/>
       </c>
-      <c r="L51" s="3">
+      <c r="L51" s="13">
         <f>MAX(0,N(H51)-F51)</f>
         <v/>
       </c>
-      <c r="M51" s="6" t="inlineStr">
-        <is>
-          <t>6 — КП лит. Б</t>
+      <c r="M51" s="15" t="inlineStr">
+        <is>
+          <t>КП: Вн-6 — 3, Вн-18 — 1</t>
         </is>
       </c>
     </row>
@@ -3999,53 +4001,55 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="n">
+      <c r="A54" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Д22 (П)</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>2100×1300</t>
         </is>
       </c>
-      <c r="E54" s="13" t="n">
+      <c r="E54" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="F54" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="14">
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5">
         <f>2.1*1.3</f>
         <v/>
       </c>
-      <c r="H54" s="13" t="n"/>
-      <c r="I54" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="14">
+      <c r="H54" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="5">
         <f>ROUND(G54/F54*I54,2)</f>
         <v/>
       </c>
-      <c r="K54" s="13">
+      <c r="K54" s="3">
         <f>F54-I54</f>
         <v/>
       </c>
-      <c r="L54" s="13">
+      <c r="L54" s="3">
         <f>MAX(0,N(H54)-F54)</f>
         <v/>
       </c>
-      <c r="M54" s="15" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>КП: Вн-22 — 5; сверх ВДЦ 4 шт.; на чертеже у Вн-22 стоит марка Д-17*, по размеру КП (1336×2193) это Д22</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4083,7 @@
         <v/>
       </c>
       <c r="H55" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>3</v>
@@ -4098,7 +4102,7 @@
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>3 — КП лит. В</t>
+          <t>КП: Вн-6 — 1, Вн-19 — 2</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4206,7 @@
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>1 — КП лит. В</t>
+          <t>КП: Вн-16 — 1</t>
         </is>
       </c>
     </row>
@@ -4309,53 +4313,53 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>Г</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>Д17* (П)</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>2410×1300</t>
         </is>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="13" t="n">
         <v>105</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="F60" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="14">
         <f>2.41*1.3*3</f>
         <v/>
       </c>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="5">
+      <c r="H60" s="13" t="n"/>
+      <c r="I60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="14">
         <f>ROUND(G60/F60*I60,2)</f>
         <v/>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="13">
         <f>F60-I60</f>
         <v/>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="13">
         <f>MAX(0,N(H60)-F60)</f>
         <v/>
       </c>
-      <c r="M60" s="6" t="inlineStr">
-        <is>
-          <t>3 — излишек КП лит. А</t>
+      <c r="M60" s="15" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
         </is>
       </c>
     </row>
@@ -4564,55 +4568,55 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>Д</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>Д17* (П)</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>2410×1300</t>
         </is>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="13" t="n">
         <v>125</v>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="F65" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G65" s="5">
+      <c r="G65" s="14">
         <f>2.41*1.3*6</f>
         <v/>
       </c>
-      <c r="H65" s="3" t="n">
+      <c r="H65" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I65" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J65" s="5">
+      <c r="I65" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" s="14">
         <f>ROUND(G65/F65*I65,2)</f>
         <v/>
       </c>
-      <c r="K65" s="3">
+      <c r="K65" s="13">
         <f>F65-I65</f>
         <v/>
       </c>
-      <c r="L65" s="3">
+      <c r="L65" s="13">
         <f>MAX(0,N(H65)-F65)</f>
         <v/>
       </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>4 — КП лит. Д; 1 — излишек КП лит. А; 1 — излишек КП лит. Б</t>
+      <c r="M65" s="15" t="inlineStr">
+        <is>
+          <t>КП: Вн-10 — 1, Вн-6 — 2, Вн-9 — 1</t>
         </is>
       </c>
     </row>
@@ -4826,19 +4830,21 @@
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>А</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д35</t>
         </is>
       </c>
       <c r="D70" s="13" t="n"/>
       <c r="E70" s="13" t="n"/>
       <c r="F70" s="13" t="n"/>
       <c r="G70" s="14" t="n"/>
-      <c r="H70" s="13" t="n"/>
+      <c r="H70" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="I70" s="13" t="n">
         <v>0</v>
       </c>
@@ -4848,10 +4854,13 @@
       <c r="K70" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L70" s="13" t="n"/>
+      <c r="L70" s="13">
+        <f>H70</f>
+        <v/>
+      </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>3 шт. из КП лит. Б — свободных строк ВДЦ Д17* больше нет, закрыть нельзя</t>
+          <t>КП: Вн-15 — 1 шт. (однопольная) — в ВДЦ лит. А строки Д35 нет, закрыть нельзя</t>
         </is>
       </c>
     </row>
@@ -4861,19 +4870,21 @@
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д35</t>
         </is>
       </c>
       <c r="D71" s="13" t="n"/>
       <c r="E71" s="13" t="n"/>
       <c r="F71" s="13" t="n"/>
       <c r="G71" s="14" t="n"/>
-      <c r="H71" s="13" t="n"/>
+      <c r="H71" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="I71" s="13" t="n">
         <v>0</v>
       </c>
@@ -4883,81 +4894,124 @@
       <c r="K71" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="13" t="n"/>
+      <c r="L71" s="13">
+        <f>H71</f>
+        <v/>
+      </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>1 шт. из КП лит. В — свободных строк ВДЦ Д17* больше нет, закрыть нельзя</t>
+          <t>КП: Вн-15 — 1 шт. (однопольная) — в ВДЦ лит. Б строки Д35 нет, закрыть нельзя</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="n"/>
-      <c r="B72" s="7" t="n"/>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="A72" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>Д22</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="n"/>
+      <c r="E72" s="13" t="n"/>
+      <c r="F72" s="13" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="13">
+        <f>H72</f>
+        <v/>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>КП: Вн-22 — 1 шт. (двупольная) — в ВДЦ лит. В строки Д22 нет, закрыть нельзя</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Итого двери</t>
         </is>
       </c>
-      <c r="D72" s="7" t="n"/>
-      <c r="E72" s="7" t="n"/>
-      <c r="F72" s="8">
-        <f>SUM(F47:F71)</f>
-        <v/>
-      </c>
-      <c r="G72" s="10">
-        <f>SUM(G47:G71)</f>
-        <v/>
-      </c>
-      <c r="H72" s="8">
-        <f>SUM(H47:H71)</f>
-        <v/>
-      </c>
-      <c r="I72" s="8">
-        <f>SUM(I47:I71)</f>
-        <v/>
-      </c>
-      <c r="J72" s="10">
-        <f>SUM(J47:J71)</f>
-        <v/>
-      </c>
-      <c r="K72" s="8">
-        <f>SUM(K47:K71)</f>
-        <v/>
-      </c>
-      <c r="L72" s="8">
-        <f>SUM(L47:L71)</f>
-        <v/>
-      </c>
-      <c r="M72" s="11" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="16" t="n"/>
-      <c r="B74" s="16" t="n"/>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="8">
+        <f>SUM(F47:F72)</f>
+        <v/>
+      </c>
+      <c r="G73" s="10">
+        <f>SUM(G47:G72)</f>
+        <v/>
+      </c>
+      <c r="H73" s="8">
+        <f>SUM(H47:H72)</f>
+        <v/>
+      </c>
+      <c r="I73" s="8">
+        <f>SUM(I47:I72)</f>
+        <v/>
+      </c>
+      <c r="J73" s="10">
+        <f>SUM(J47:J72)</f>
+        <v/>
+      </c>
+      <c r="K73" s="8">
+        <f>SUM(K47:K72)</f>
+        <v/>
+      </c>
+      <c r="L73" s="8">
+        <f>SUM(L47:L72)</f>
+        <v/>
+      </c>
+      <c r="M73" s="11" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="n"/>
+      <c r="B75" s="16" t="n"/>
+      <c r="C75" s="17" t="inlineStr">
         <is>
           <t>ВСЕГО к закрытию (витражи + двери)</t>
         </is>
       </c>
-      <c r="D74" s="16" t="n"/>
-      <c r="E74" s="16" t="n"/>
-      <c r="F74" s="16" t="n"/>
-      <c r="G74" s="16" t="n"/>
-      <c r="H74" s="16" t="n"/>
-      <c r="I74" s="17">
-        <f>I43+I72</f>
-        <v/>
-      </c>
-      <c r="J74" s="18">
-        <f>J43+J72</f>
-        <v/>
-      </c>
-      <c r="K74" s="16" t="n"/>
-      <c r="L74" s="16" t="n"/>
-      <c r="M74" s="16" t="n"/>
+      <c r="D75" s="16" t="n"/>
+      <c r="E75" s="16" t="n"/>
+      <c r="F75" s="16" t="n"/>
+      <c r="G75" s="16" t="n"/>
+      <c r="H75" s="16" t="n"/>
+      <c r="I75" s="17">
+        <f>I43+I73</f>
+        <v/>
+      </c>
+      <c r="J75" s="18">
+        <f>J43+J73</f>
+        <v/>
+      </c>
+      <c r="K75" s="16" t="n"/>
+      <c r="L75" s="16" t="n"/>
+      <c r="M75" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C74:H74"/>
+    <mergeCell ref="C75:H75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
@@ -6139,19 +6193,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6164,7 +6219,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Марка двери — по чертежу у витража; двери Вн-22 (КП №15, 11 шт.) распределены как сами Вн-22: А5, Б5, В1</t>
+          <t>Литер и витраж — как подписано в КП; марка ВДЦ — по типу и размеру. Двери Вн-22 (КП №15, 11 шт.) — как сами Вн-22: А5, Б5, В1</t>
         </is>
       </c>
     </row>
@@ -6186,35 +6241,40 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Марка двери</t>
+          <t>Марка по ВДЦ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>КП</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Ширина, мм</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Высота, мм</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Кол-во, шт</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Площадь по размерам КП, м²</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Площадь в КП, м²</t>
         </is>
@@ -6241,23 +6301,28 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>№9 А</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="G4" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="H4" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="I4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="4">
-        <f>ROUND(F4*G4*H4/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="4">
+        <f>ROUND(G4*H4*I4/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K4" s="4" t="n">
         <v>9.75</v>
       </c>
     </row>
@@ -6282,23 +6347,28 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>№9 А</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4">
-        <f>ROUND(F5*G5*H5/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J5" s="4" t="n">
+      <c r="I5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
+        <f>ROUND(G5*H5*I5/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -6318,28 +6388,33 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д35</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>однопольная</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>№9 А</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="G6" s="3" t="n">
         <v>1106</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4">
-        <f>ROUND(F6*G6*H6/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J6" s="4" t="n">
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4">
+        <f>ROUND(G6*H6*I6/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K6" s="4" t="n">
         <v>2.69</v>
       </c>
     </row>
@@ -6359,28 +6434,33 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д22</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>№15 Вн-22</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>2193</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="I7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="4">
-        <f>ROUND(F7*G7*H7/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="4">
+        <f>ROUND(G7*H7*I7/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K7" s="4" t="n">
         <v>14.65</v>
       </c>
     </row>
@@ -6405,23 +6485,28 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
           <t>№11 Б</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="G8" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="H8" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="I8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="4">
-        <f>ROUND(F8*G8*H8/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="4">
+        <f>ROUND(G8*H8*I8/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K8" s="4" t="n">
         <v>9.75</v>
       </c>
     </row>
@@ -6441,28 +6526,33 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д35</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t>однопольная</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
           <t>№11 Б</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="G9" s="3" t="n">
         <v>1186</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="H9" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="4">
-        <f>ROUND(F9*G9*H9/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J9" s="4" t="n">
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <f>ROUND(G9*H9*I9/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>2.89</v>
       </c>
     </row>
@@ -6487,23 +6577,28 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>№11 Б</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="4">
-        <f>ROUND(F10*G10*H10/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J10" s="4" t="n">
+      <c r="I10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4">
+        <f>ROUND(G10*H10*I10/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -6523,28 +6618,33 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д22</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>№15 Вн-22</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="G11" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="H11" s="3" t="n">
         <v>2193</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="I11" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="4">
-        <f>ROUND(F11*G11*H11/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="4">
+        <f>ROUND(G11*H11*I11/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>14.65</v>
       </c>
     </row>
@@ -6569,23 +6669,28 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>№12 В</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="G12" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H12" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="4">
-        <f>ROUND(F12*G12*H12/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J12" s="4" t="n">
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <f>ROUND(G12*H12*I12/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -6610,23 +6715,28 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>однопольная</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>№12 В</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="G13" s="3" t="n">
         <v>1176</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4">
-        <f>ROUND(F13*G13*H13/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J13" s="4" t="n">
+      <c r="I13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <f>ROUND(G13*H13*I13/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>2.86</v>
       </c>
     </row>
@@ -6651,23 +6761,28 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t>№12 В</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="G14" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="H14" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="I14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="4">
-        <f>ROUND(F14*G14*H14/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="4">
+        <f>ROUND(G14*H14*I14/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -6687,28 +6802,33 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д22</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>№15 Вн-22</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="G15" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="H15" s="3" t="n">
         <v>2193</v>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4">
-        <f>ROUND(F15*G15*H15/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J15" s="4" t="n">
+      <c r="I15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
+        <f>ROUND(G15*H15*I15/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>2.93</v>
       </c>
     </row>
@@ -6733,23 +6853,28 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>№14 (Д)</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="G16" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="I16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="4">
-        <f>ROUND(F16*G16*H16/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="4">
+        <f>ROUND(G16*H16*I16/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K16" s="4" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -6774,23 +6899,28 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>№14 (Д)</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="G17" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="4">
-        <f>ROUND(F17*G17*H17/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J17" s="4" t="n">
+      <c r="I17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
+        <f>ROUND(G17*H17*I17/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K17" s="4" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -6815,23 +6945,28 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
           <t>№14 (Д)</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="G18" s="3" t="n">
         <v>1336</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="H18" s="3" t="n">
         <v>2433</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="4">
-        <f>ROUND(F18*G18*H18/1000000,2)</f>
-        <v/>
-      </c>
-      <c r="J18" s="4" t="n">
+      <c r="I18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
+        <f>ROUND(G18*H18*I18/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K18" s="4" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -6847,16 +6982,17 @@
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8">
-        <f>SUM(H4:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="25">
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="8">
         <f>SUM(I4:I18)</f>
         <v/>
       </c>
       <c r="J19" s="25">
         <f>SUM(J4:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="25">
+        <f>SUM(K4:K18)</f>
         <v/>
       </c>
     </row>

--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -1453,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5008,6 +5008,13 @@
       <c r="K75" s="16" t="n"/>
       <c r="L75" s="16" t="n"/>
       <c r="M75" s="16" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Двери закрываются отдельными строками ВДЦ; площадь витражей — полным габаритом по ВДЦ, без вычета площади дверей.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -3822,7 +3822,7 @@
         <v/>
       </c>
       <c r="H50" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>1</v>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>КП: Вн-22 — 5; сверх ВДЦ 4 шт.; на чертеже у Вн-22 стоит марка Д-17*, по размеру КП (1336×2193) это Д22</t>
+          <t>КП: Вн-22 — 1; на чертеже у Вн-22 стоит марка Д-17*, по размеру КП (1336×2193) это Д22</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
         <v/>
       </c>
       <c r="H54" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>1</v>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>КП: Вн-22 — 5; сверх ВДЦ 4 шт.; на чертеже у Вн-22 стоит марка Д-17*, по размеру КП (1336×2193) это Д22</t>
+          <t>КП: Вн-22 — 1; на чертеже у Вн-22 стоит марка Д-17*, по размеру КП (1336×2193) это Д22</t>
         </is>
       </c>
     </row>
@@ -4341,9 +4341,11 @@
         <f>2.41*1.3*3</f>
         <v/>
       </c>
-      <c r="H60" s="13" t="n"/>
+      <c r="H60" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="I60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="14">
         <f>ROUND(G60/F60*I60,2)</f>
@@ -4359,7 +4361,7 @@
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>нет в КП</t>
+          <t>КП: Вн-10 — 1</t>
         </is>
       </c>
     </row>
@@ -4415,53 +4417,55 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="n">
+      <c r="A62" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Г</t>
         </is>
       </c>
-      <c r="C62" s="13" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Д22 (П)</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>2100×1300</t>
         </is>
       </c>
-      <c r="E62" s="13" t="n">
+      <c r="E62" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="F62" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="14">
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5">
         <f>2.1*1.3</f>
         <v/>
       </c>
-      <c r="H62" s="13" t="n"/>
-      <c r="I62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="14">
+      <c r="H62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="5">
         <f>ROUND(G62/F62*I62,2)</f>
         <v/>
       </c>
-      <c r="K62" s="13">
+      <c r="K62" s="3">
         <f>F62-I62</f>
         <v/>
       </c>
-      <c r="L62" s="13">
+      <c r="L62" s="3">
         <f>MAX(0,N(H62)-F62)</f>
         <v/>
       </c>
-      <c r="M62" s="15" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>КП: Вн-22 — 1; на чертеже у Вн-22 стоит марка Д-17*, по размеру КП (1336×2193) это Д22</t>
         </is>
       </c>
     </row>
@@ -4597,10 +4601,10 @@
         <v/>
       </c>
       <c r="H65" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I65" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J65" s="14">
         <f>ROUND(G65/F65*I65,2)</f>
@@ -4616,7 +4620,7 @@
       </c>
       <c r="M65" s="15" t="inlineStr">
         <is>
-          <t>КП: Вн-10 — 1, Вн-6 — 2, Вн-9 — 1</t>
+          <t>КП: Вн-6 — 2, Вн-9 — 1</t>
         </is>
       </c>
     </row>
@@ -4723,53 +4727,55 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="n">
+      <c r="A68" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Д</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Д22 (П)</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>2100×1300</t>
         </is>
       </c>
-      <c r="E68" s="13" t="n">
+      <c r="E68" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="F68" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="14">
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5">
         <f>2.1*1.3</f>
         <v/>
       </c>
-      <c r="H68" s="13" t="n"/>
-      <c r="I68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="14">
+      <c r="H68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="5">
         <f>ROUND(G68/F68*I68,2)</f>
         <v/>
       </c>
-      <c r="K68" s="13">
+      <c r="K68" s="3">
         <f>F68-I68</f>
         <v/>
       </c>
-      <c r="L68" s="13">
+      <c r="L68" s="3">
         <f>MAX(0,N(H68)-F68)</f>
         <v/>
       </c>
-      <c r="M68" s="15" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>КП: Вн-22 — 1; на чертеже у Вн-22 стоит марка Д-17*, по размеру КП (1336×2193) это Д22</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4916,7 @@
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>без литера</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
@@ -4923,7 +4929,7 @@
       <c r="F72" s="13" t="n"/>
       <c r="G72" s="14" t="n"/>
       <c r="H72" s="13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I72" s="13" t="n">
         <v>0</v>
@@ -4940,7 +4946,7 @@
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>КП: Вн-22 — 1 шт. (двупольная) — в ВДЦ лит. В строки Д22 нет, закрыть нельзя</t>
+          <t>КП: Вн-22 — 7 шт. (двупольная) — все строки ВДЦ Д22 уже закрыты, закрыть нельзя</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6226,7 +6232,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Литер и витраж — как подписано в КП; марка ВДЦ — по типу и размеру. Двери Вн-22 (КП №15, 11 шт.) — как сами Вн-22: А5, Б5, В1</t>
+          <t>Литер и витраж — как в КП; марка ВДЦ — по типу и размеру. КП №15 и №14 без литера — по свободным строкам ВДЦ</t>
         </is>
       </c>
     </row>
@@ -6461,14 +6467,14 @@
         <v>2193</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4">
         <f>ROUND(G7*H7*I7/1000000,2)</f>
         <v/>
       </c>
       <c r="K7" s="4" t="n">
-        <v>14.65</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="8">
@@ -6645,14 +6651,14 @@
         <v>2193</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4">
         <f>ROUND(G11*H11*I11/1000000,2)</f>
         <v/>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14.65</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="12">
@@ -6799,17 +6805,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Вн-22</t>
+          <t>Вн-10</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Д22</t>
+          <t>Д17*</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -6819,14 +6825,14 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>№15 Вн-22</t>
+          <t>№14 (шапка нечитаема)</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
         <v>1336</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2193</v>
+        <v>2433</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1</v>
@@ -6836,7 +6842,7 @@
         <v/>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="16">
@@ -6845,17 +6851,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Д</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-22</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д22</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -6865,24 +6871,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>№14 (Д)</t>
+          <t>№15 Вн-22</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
         <v>1336</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2433</v>
+        <v>2193</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4">
         <f>ROUND(G16*H16*I16/1000000,2)</f>
         <v/>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6.5</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="17">
@@ -6896,7 +6902,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Вн-9</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -6911,7 +6917,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>№14 (Д)</t>
+          <t>№14 (шапка нечитаема)</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
@@ -6921,14 +6927,14 @@
         <v>2433</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4">
         <f>ROUND(G17*H17*I17/1000000,2)</f>
         <v/>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="18">
@@ -6942,7 +6948,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Вн-10</t>
+          <t>Вн-9</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -6957,7 +6963,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>№14 (Д)</t>
+          <t>№14 (шапка нечитаема)</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
@@ -6978,28 +6984,120 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Д</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Д22</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>№15 Вн-22</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>2193</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <f>ROUND(G19*H19*I19/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>без литера</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Вн-22</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Д22</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>двупольная</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>№15 Вн-22</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>1336</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>2193</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4">
+        <f>ROUND(G20*H20*I20/1000000,2)</f>
+        <v/>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>20.51</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="8">
-        <f>SUM(I4:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="25">
-        <f>SUM(J4:J18)</f>
-        <v/>
-      </c>
-      <c r="K19" s="25">
-        <f>SUM(K4:K18)</f>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="8">
+        <f>SUM(I4:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="25">
+        <f>SUM(J4:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="25">
+        <f>SUM(K4:K20)</f>
         <v/>
       </c>
     </row>
@@ -11585,12 +11683,12 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>№14 (Д)</t>
+          <t>№14 (шапка нечитаема)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Д</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -11622,7 +11720,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>№14 (Д)</t>
+          <t>№14 (шапка нечитаема)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -11659,7 +11757,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>№14 (Д)</t>
+          <t>№14 (шапка нечитаема)</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">

--- a/Спецификация_витражей.xlsx
+++ b/Спецификация_витражей.xlsx
@@ -1453,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4498,9 +4498,11 @@
         <f>2.41*1.3*3</f>
         <v/>
       </c>
-      <c r="H63" s="13" t="n"/>
+      <c r="H63" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="I63" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="14">
         <f>ROUND(G63/F63*I63,2)</f>
@@ -4516,7 +4518,7 @@
       </c>
       <c r="M63" s="15" t="inlineStr">
         <is>
-          <t>нет в КП</t>
+          <t>КП: Вн-15 (КП №9 А) — 1, Вн-15 (КП №11 Б) — 1</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4838,12 @@
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>без литера</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>Д35</t>
+          <t>Д22</t>
         </is>
       </c>
       <c r="D70" s="13" t="n"/>
@@ -4849,7 +4851,7 @@
       <c r="F70" s="13" t="n"/>
       <c r="G70" s="14" t="n"/>
       <c r="H70" s="13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I70" s="13" t="n">
         <v>0</v>
@@ -4866,157 +4868,77 @@
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>КП: Вн-15 — 1 шт. (однопольная) — в ВДЦ лит. А строки Д35 нет, закрыть нельзя</t>
+          <t>КП: Вн-22 — 7 шт. (двупольная) — все строки ВДЦ Д22 уже закрыты, закрыть нельзя</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>Д35</t>
-        </is>
-      </c>
-      <c r="D71" s="13" t="n"/>
-      <c r="E71" s="13" t="n"/>
-      <c r="F71" s="13" t="n"/>
-      <c r="G71" s="14" t="n"/>
-      <c r="H71" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="13">
-        <f>H71</f>
-        <v/>
-      </c>
-      <c r="M71" s="15" t="inlineStr">
-        <is>
-          <t>КП: Вн-15 — 1 шт. (однопольная) — в ВДЦ лит. Б строки Д35 нет, закрыть нельзя</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>без литера</t>
-        </is>
-      </c>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>Д22</t>
-        </is>
-      </c>
-      <c r="D72" s="13" t="n"/>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
-      <c r="G72" s="14" t="n"/>
-      <c r="H72" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="I72" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="13">
-        <f>H72</f>
-        <v/>
-      </c>
-      <c r="M72" s="15" t="inlineStr">
-        <is>
-          <t>КП: Вн-22 — 7 шт. (двупольная) — все строки ВДЦ Д22 уже закрыты, закрыть нельзя</t>
-        </is>
-      </c>
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Итого двери</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="8">
+        <f>SUM(F47:F70)</f>
+        <v/>
+      </c>
+      <c r="G71" s="10">
+        <f>SUM(G47:G70)</f>
+        <v/>
+      </c>
+      <c r="H71" s="8">
+        <f>SUM(H47:H70)</f>
+        <v/>
+      </c>
+      <c r="I71" s="8">
+        <f>SUM(I47:I70)</f>
+        <v/>
+      </c>
+      <c r="J71" s="10">
+        <f>SUM(J47:J70)</f>
+        <v/>
+      </c>
+      <c r="K71" s="8">
+        <f>SUM(K47:K70)</f>
+        <v/>
+      </c>
+      <c r="L71" s="8">
+        <f>SUM(L47:L70)</f>
+        <v/>
+      </c>
+      <c r="M71" s="11" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="n"/>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>Итого двери</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="n"/>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="8">
-        <f>SUM(F47:F72)</f>
-        <v/>
-      </c>
-      <c r="G73" s="10">
-        <f>SUM(G47:G72)</f>
-        <v/>
-      </c>
-      <c r="H73" s="8">
-        <f>SUM(H47:H72)</f>
-        <v/>
-      </c>
-      <c r="I73" s="8">
-        <f>SUM(I47:I72)</f>
-        <v/>
-      </c>
-      <c r="J73" s="10">
-        <f>SUM(J47:J72)</f>
-        <v/>
-      </c>
-      <c r="K73" s="8">
-        <f>SUM(K47:K72)</f>
-        <v/>
-      </c>
-      <c r="L73" s="8">
-        <f>SUM(L47:L72)</f>
-        <v/>
-      </c>
-      <c r="M73" s="11" t="n"/>
+      <c r="A73" s="16" t="n"/>
+      <c r="B73" s="16" t="n"/>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>ВСЕГО к закрытию (витражи + двери)</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="n"/>
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="16" t="n"/>
+      <c r="G73" s="16" t="n"/>
+      <c r="H73" s="16" t="n"/>
+      <c r="I73" s="17">
+        <f>I43+I71</f>
+        <v/>
+      </c>
+      <c r="J73" s="18">
+        <f>J43+J71</f>
+        <v/>
+      </c>
+      <c r="K73" s="16" t="n"/>
+      <c r="L73" s="16" t="n"/>
+      <c r="M73" s="16" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
-      <c r="B75" s="16" t="n"/>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <t>ВСЕГО к закрытию (витражи + двери)</t>
-        </is>
-      </c>
-      <c r="D75" s="16" t="n"/>
-      <c r="E75" s="16" t="n"/>
-      <c r="F75" s="16" t="n"/>
-      <c r="G75" s="16" t="n"/>
-      <c r="H75" s="16" t="n"/>
-      <c r="I75" s="17">
-        <f>I43+I73</f>
-        <v/>
-      </c>
-      <c r="J75" s="18">
-        <f>J43+J73</f>
-        <v/>
-      </c>
-      <c r="K75" s="16" t="n"/>
-      <c r="L75" s="16" t="n"/>
-      <c r="M75" s="16" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Двери закрываются отдельными строками ВДЦ; площадь витражей — полным габаритом по ВДЦ, без вычета площади дверей.</t>
         </is>
@@ -5024,7 +4946,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C75:H75"/>
+    <mergeCell ref="C73:H73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
@@ -6396,29 +6318,29 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Вн-15</t>
+          <t>Вн-22</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Д35</t>
+          <t>Д22</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>однопольная</t>
+          <t>двупольная</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>№9 А</t>
+          <t>№15 Вн-22</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1106</v>
+        <v>1336</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2433</v>
+        <v>2193</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1</v>
@@ -6428,7 +6350,7 @@
         <v/>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.69</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="7">
@@ -6437,17 +6359,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Вн-22</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Д22</t>
+          <t>Д17*</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -6457,24 +6379,24 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>№15 Вн-22</t>
+          <t>№11 Б</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
         <v>1336</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2193</v>
+        <v>2433</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4">
         <f>ROUND(G7*H7*I7/1000000,2)</f>
         <v/>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.93</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="8">
@@ -6488,7 +6410,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-18</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -6513,14 +6435,14 @@
         <v>2433</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4">
         <f>ROUND(G8*H8*I8/1000000,2)</f>
         <v/>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="9">
@@ -6534,29 +6456,29 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Вн-15</t>
+          <t>Вн-22</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Д35</t>
+          <t>Д22</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>однопольная</t>
+          <t>двупольная</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>№11 Б</t>
+          <t>№15 Вн-22</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1186</v>
+        <v>1336</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2433</v>
+        <v>2193</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>1</v>
@@ -6566,7 +6488,7 @@
         <v/>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="10">
@@ -6575,12 +6497,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Вн-18</t>
+          <t>Вн-6</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -6595,7 +6517,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>№11 Б</t>
+          <t>№12 В</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
@@ -6621,34 +6543,34 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Вн-22</t>
+          <t>Вн-16</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Д22</t>
+          <t>Д35</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>двупольная</t>
+          <t>однопольная</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>№15 Вн-22</t>
+          <t>№12 В</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1336</v>
+        <v>1176</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2193</v>
+        <v>2433</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>1</v>
@@ -6658,7 +6580,7 @@
         <v/>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="12">
@@ -6672,7 +6594,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Вн-6</t>
+          <t>Вн-19</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -6697,14 +6619,14 @@
         <v>2433</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4">
         <f>ROUND(G12*H12*I12/1000000,2)</f>
         <v/>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
@@ -6713,31 +6635,31 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Вн-16</t>
+          <t>Вн-10</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Д35</t>
+          <t>Д17*</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>однопольная</t>
+          <t>двупольная</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>№12 В</t>
+          <t>№14 (шапка нечитаема)</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1176</v>
+        <v>1336</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>2433</v>
@@ -6750,7 +6672,7 @@
         <v/>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="14">
@@ -6759,44 +6681,44 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Вн-19</t>
+          <t>Вн-15</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д35</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>двупольная</t>
+          <t>однопольная</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>№12 В</t>
+          <t>№9 А</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1336</v>
+        <v>1106</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>2433</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4">
         <f>ROUND(G14*H14*I14/1000000,2)</f>
         <v/>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.5</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="15">
@@ -6810,26 +6732,26 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Вн-10</t>
+          <t>Вн-15</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Д17*</t>
+          <t>Д35</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>двупольная</t>
+          <t>однопольная</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>№14 (шапка нечитаема)</t>
+          <t>№11 Б</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1336</v>
+        <v>1186</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>2433</v>
@@ -6842,7 +6764,7 @@
         <v/>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="16">
@@ -11540,7 +11462,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -11651,7 +11573,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
